--- a/nas_bench_201_experiments/gvae/training_metrics_ImageNet.xlsx
+++ b/nas_bench_201_experiments/gvae/training_metrics_ImageNet.xlsx
@@ -480,28 +480,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1183.721224767578</v>
+        <v>2801.515785617188</v>
       </c>
       <c r="C2" t="n">
-        <v>3.884533144073486</v>
+        <v>4.198197200683594</v>
       </c>
       <c r="D2" t="n">
-        <v>1.503675038255692</v>
+        <v>1.287632902497292</v>
       </c>
       <c r="E2" t="n">
-        <v>1179.829180488281</v>
+        <v>2797.311144984375</v>
       </c>
       <c r="F2" t="n">
-        <v>146.430361607911</v>
+        <v>372.5083105389095</v>
       </c>
       <c r="G2" t="n">
-        <v>2.834500013790162</v>
+        <v>3.508739691682974</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4057916095186797</v>
+        <v>0.2551165243035234</v>
       </c>
       <c r="I2" t="n">
-        <v>143.5938328594563</v>
+        <v>368.9982973361988</v>
       </c>
     </row>
     <row r="3">
@@ -509,28 +509,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>51.84198704138183</v>
+        <v>128.5947166054688</v>
       </c>
       <c r="C3" t="n">
-        <v>1.98940984173584</v>
+        <v>2.871527238471985</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2843617694797516</v>
+        <v>0.1369786202707291</v>
       </c>
       <c r="E3" t="n">
-        <v>49.85115535809326</v>
+        <v>125.7225045698242</v>
       </c>
       <c r="F3" t="n">
-        <v>7.474844153032412</v>
+        <v>28.13002957342499</v>
       </c>
       <c r="G3" t="n">
-        <v>1.622649655124297</v>
+        <v>2.101129527613156</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2348094590093339</v>
+        <v>0.07197490459554153</v>
       </c>
       <c r="I3" t="n">
-        <v>5.851020485503055</v>
+        <v>26.02854004391644</v>
       </c>
     </row>
     <row r="4">
@@ -538,28 +538,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>6.131342146514893</v>
+        <v>9.699583636901856</v>
       </c>
       <c r="C4" t="n">
-        <v>1.604460258117676</v>
+        <v>1.722261684623718</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3983071308288574</v>
+        <v>0.06993138160991669</v>
       </c>
       <c r="E4" t="n">
-        <v>4.524890360839843</v>
+        <v>7.976972363700867</v>
       </c>
       <c r="F4" t="n">
-        <v>1.748540618859146</v>
+        <v>2.11990063284583</v>
       </c>
       <c r="G4" t="n">
-        <v>1.595185845306608</v>
+        <v>1.608609964338057</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4139774199002719</v>
+        <v>0.07638901985148622</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1512848905521349</v>
+        <v>0.5109086907473902</v>
       </c>
     </row>
     <row r="5">
@@ -567,28 +567,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.130299715606689</v>
+        <v>2.296721165008545</v>
       </c>
       <c r="C5" t="n">
-        <v>1.576335505058289</v>
+        <v>1.601168305328369</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4422980299339295</v>
+        <v>0.1124622907476425</v>
       </c>
       <c r="E5" t="n">
-        <v>2.551752693435669</v>
+        <v>0.6949905266189575</v>
       </c>
       <c r="F5" t="n">
-        <v>1.597249292347209</v>
+        <v>1.600274871130752</v>
       </c>
       <c r="G5" t="n">
-        <v>1.541688885369853</v>
+        <v>1.589703478789835</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4755082474408298</v>
+        <v>0.117592615690842</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05318287597249033</v>
+        <v>0.009983415467084231</v>
       </c>
     </row>
     <row r="6">
@@ -596,28 +596,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.237334351875305</v>
+        <v>2.222959441864014</v>
       </c>
       <c r="C6" t="n">
-        <v>1.49202885105896</v>
+        <v>1.556639057861328</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4843445083656311</v>
+        <v>0.1366257630290985</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7428837871627808</v>
+        <v>0.6656372465648651</v>
       </c>
       <c r="F6" t="n">
-        <v>1.447812526121031</v>
+        <v>1.55383834380699</v>
       </c>
       <c r="G6" t="n">
-        <v>1.417240300933066</v>
+        <v>1.512621279486241</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4772558674240579</v>
+        <v>0.1572094164236918</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02818597194275304</v>
+        <v>0.04043101599491634</v>
       </c>
     </row>
     <row r="7">
@@ -625,28 +625,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.608992503242493</v>
+        <v>1.720973150306702</v>
       </c>
       <c r="C7" t="n">
-        <v>1.349537651100159</v>
+        <v>1.446998984138489</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5929721484260559</v>
+        <v>0.2312540395908356</v>
       </c>
       <c r="E7" t="n">
-        <v>0.25648999559021</v>
+        <v>0.2728178882849217</v>
       </c>
       <c r="F7" t="n">
-        <v>1.268739761715029</v>
+        <v>1.43995005868193</v>
       </c>
       <c r="G7" t="n">
-        <v>1.24712817164852</v>
+        <v>1.362890479724131</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6358027719323437</v>
+        <v>0.2854906148583815</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0184325704339521</v>
+        <v>0.07563212526953045</v>
       </c>
     </row>
     <row r="8">
@@ -654,28 +654,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.393865072563171</v>
+        <v>1.480035564117432</v>
       </c>
       <c r="C8" t="n">
-        <v>1.212700583816528</v>
+        <v>1.307733510749817</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6792539282608032</v>
+        <v>0.3472624597072601</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1777682239038348</v>
+        <v>0.1705657246141434</v>
       </c>
       <c r="F8" t="n">
-        <v>1.294308297552448</v>
+        <v>1.225447659834757</v>
       </c>
       <c r="G8" t="n">
-        <v>1.153589862742587</v>
+        <v>1.204883051198614</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6919829383993227</v>
+        <v>0.4101286262575215</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1372585166181281</v>
+        <v>0.0185139709544561</v>
       </c>
     </row>
     <row r="9">
@@ -683,28 +683,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.220858082229614</v>
+        <v>1.306333124755859</v>
       </c>
       <c r="C9" t="n">
-        <v>1.059741723144531</v>
+        <v>1.162930836349487</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7111044295043946</v>
+        <v>0.4256981279850006</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1575608446712494</v>
+        <v>0.1412737946691513</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9826929429265843</v>
+        <v>1.288960190231609</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9006123273174292</v>
+        <v>1.102458276935347</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8106654929920277</v>
+        <v>0.4195620385293665</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07802728679110137</v>
+        <v>0.1844041058007889</v>
       </c>
     </row>
     <row r="10">
@@ -712,28 +712,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.9815757383880616</v>
+        <v>1.116477310432434</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8727195670356751</v>
+        <v>1.003371771896362</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8070110370407104</v>
+        <v>0.5081096513786316</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1048211219875813</v>
+        <v>0.1105650024447441</v>
       </c>
       <c r="F10" t="n">
-        <v>1.020887052581128</v>
+        <v>0.9302772812353262</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8991392443814052</v>
+        <v>0.8616335271583295</v>
       </c>
       <c r="H10" t="n">
-        <v>0.798975631447834</v>
+        <v>0.6009281080504226</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1177529393265337</v>
+        <v>0.0656391100048241</v>
       </c>
     </row>
     <row r="11">
@@ -741,28 +741,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7844790427360535</v>
+        <v>0.9292545829582214</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7004164584770203</v>
+        <v>0.830780207950592</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8712361288414001</v>
+        <v>0.6032256715431213</v>
       </c>
       <c r="E11" t="n">
-        <v>0.07970640665531159</v>
+        <v>0.09545825383019448</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5845095033318922</v>
+        <v>0.9926630602497456</v>
       </c>
       <c r="G11" t="n">
-        <v>0.549699894199558</v>
+        <v>0.8284553548523497</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9055551491826044</v>
+        <v>0.6652694756521875</v>
       </c>
       <c r="I11" t="n">
-        <v>0.030281840544589</v>
+        <v>0.1608813520288778</v>
       </c>
     </row>
     <row r="12">
@@ -770,28 +770,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.6204359659252167</v>
+        <v>0.7793988951454163</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5380070531082153</v>
+        <v>0.6827873304634094</v>
       </c>
       <c r="D12" t="n">
-        <v>1.011449747673035</v>
+        <v>0.7115946207466125</v>
       </c>
       <c r="E12" t="n">
-        <v>0.07737166540765762</v>
+        <v>0.09305358091640473</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6838013854929129</v>
+        <v>0.5760834678895711</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5080659181064339</v>
+        <v>0.5207580203022109</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9521064533961733</v>
+        <v>0.826509935350247</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1709749304285641</v>
+        <v>0.05119290013978376</v>
       </c>
     </row>
     <row r="13">
@@ -799,28 +799,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.510084899597168</v>
+        <v>0.6283616788024903</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4158121377468109</v>
+        <v>0.5354795071525573</v>
       </c>
       <c r="D13" t="n">
-        <v>1.135949541023254</v>
+        <v>0.8440609264831543</v>
       </c>
       <c r="E13" t="n">
-        <v>0.08859301765537261</v>
+        <v>0.08866187084603309</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3209321380828372</v>
+        <v>0.6866567498552468</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2745478125361401</v>
+        <v>0.5928381502997817</v>
       </c>
       <c r="H13" t="n">
-        <v>1.193794968909968</v>
+        <v>0.8964186354406896</v>
       </c>
       <c r="I13" t="n">
-        <v>0.04041534866147096</v>
+        <v>0.08933650298229438</v>
       </c>
     </row>
     <row r="14">
@@ -828,28 +828,28 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.399669352022171</v>
+        <v>0.5116122150840759</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3201889451026916</v>
+        <v>0.4262277646427154</v>
       </c>
       <c r="D14" t="n">
-        <v>1.214685765411377</v>
+        <v>0.9627423443717956</v>
       </c>
       <c r="E14" t="n">
-        <v>0.07340697760546207</v>
+        <v>0.0805707392988205</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5499203068591643</v>
+        <v>0.3714720205809514</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4023651178587125</v>
+        <v>0.3323994426120553</v>
       </c>
       <c r="H14" t="n">
-        <v>1.246435542052177</v>
+        <v>1.020682270126281</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1413230134213729</v>
+        <v>0.03396917092250767</v>
       </c>
     </row>
     <row r="15">
@@ -857,28 +857,28 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3487868951072693</v>
+        <v>0.4289197656059265</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2724526189804077</v>
+        <v>0.3387451519727707</v>
       </c>
       <c r="D15" t="n">
-        <v>1.300111164680481</v>
+        <v>1.061892309288025</v>
       </c>
       <c r="E15" t="n">
-        <v>0.06983371792840957</v>
+        <v>0.08486515096604824</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2256998011416362</v>
+        <v>0.4350926274634885</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1865074102174594</v>
+        <v>0.3073323148440381</v>
       </c>
       <c r="H15" t="n">
-        <v>1.307856040506534</v>
+        <v>1.027232309593462</v>
       </c>
       <c r="I15" t="n">
-        <v>0.03265311123593596</v>
+        <v>0.1226241495252434</v>
       </c>
     </row>
     <row r="16">
@@ -886,28 +886,28 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.29490018247509</v>
+        <v>0.3576055741729736</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2257116540193558</v>
+        <v>0.2726797831039429</v>
       </c>
       <c r="D16" t="n">
-        <v>1.269265629920959</v>
+        <v>1.108627074966431</v>
       </c>
       <c r="E16" t="n">
-        <v>0.06284219822287559</v>
+        <v>0.07938265709686279</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3904901645350806</v>
+        <v>0.2277341939856528</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2405141619552796</v>
+        <v>0.1951778380964164</v>
       </c>
       <c r="H16" t="n">
-        <v>1.332744348768698</v>
+        <v>1.152744808119234</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1433122843999847</v>
+        <v>0.02679263172820089</v>
       </c>
     </row>
     <row r="17">
@@ -915,28 +915,28 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.2647625493812561</v>
+        <v>0.3146253357934952</v>
       </c>
       <c r="C17" t="n">
-        <v>0.198848430478096</v>
+        <v>0.234800779706955</v>
       </c>
       <c r="D17" t="n">
-        <v>1.273387432060242</v>
+        <v>1.142367228858948</v>
       </c>
       <c r="E17" t="n">
-        <v>0.05954718284893036</v>
+        <v>0.07411271908175945</v>
       </c>
       <c r="F17" t="n">
-        <v>0.176954338557374</v>
+        <v>0.3808548011495861</v>
       </c>
       <c r="G17" t="n">
-        <v>0.154477970780984</v>
+        <v>0.2337685555268267</v>
       </c>
       <c r="H17" t="n">
-        <v>1.300618647268896</v>
+        <v>1.074823594816746</v>
       </c>
       <c r="I17" t="n">
-        <v>0.01597327360710157</v>
+        <v>0.1417121283469348</v>
       </c>
     </row>
     <row r="18">
@@ -944,28 +944,28 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.2212978436717987</v>
+        <v>0.2753546911811829</v>
       </c>
       <c r="C18" t="n">
-        <v>0.166302058506012</v>
+        <v>0.2009617556257248</v>
       </c>
       <c r="D18" t="n">
-        <v>1.214400356285095</v>
+        <v>1.111296039299011</v>
       </c>
       <c r="E18" t="n">
-        <v>0.04892378171396256</v>
+        <v>0.06883645791244507</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2612592697279683</v>
+        <v>0.1725985908566641</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2017047451341716</v>
+        <v>0.1487589954979851</v>
       </c>
       <c r="H18" t="n">
-        <v>1.275299118354698</v>
+        <v>1.149628152528361</v>
       </c>
       <c r="I18" t="n">
-        <v>0.05317803211668187</v>
+        <v>0.01809145496425874</v>
       </c>
     </row>
     <row r="19">
@@ -973,28 +973,28 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.1888253595056534</v>
+        <v>0.2331935564002991</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1391326544208527</v>
+        <v>0.1727317498502731</v>
       </c>
       <c r="D19" t="n">
-        <v>1.176301206695557</v>
+        <v>1.101381476448059</v>
       </c>
       <c r="E19" t="n">
-        <v>0.04381119706320763</v>
+        <v>0.05495489808511734</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1134446840365015</v>
+        <v>0.2943905694099663</v>
       </c>
       <c r="G19" t="n">
-        <v>0.09224290739167573</v>
+        <v>0.2193966490428949</v>
       </c>
       <c r="H19" t="n">
-        <v>1.179772282720196</v>
+        <v>1.094606521903593</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01530291556777223</v>
+        <v>0.06952088551070133</v>
       </c>
     </row>
     <row r="20">
@@ -1002,28 +1002,28 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.1513562018890381</v>
+        <v>0.2054132023506164</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1081551804270744</v>
+        <v>0.1492149172725677</v>
       </c>
       <c r="D20" t="n">
-        <v>1.148389870063782</v>
+        <v>1.062867902191162</v>
       </c>
       <c r="E20" t="n">
-        <v>0.03745907172632217</v>
+        <v>0.05088394373893738</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1286813525780185</v>
+        <v>0.1269086543697906</v>
       </c>
       <c r="G20" t="n">
-        <v>0.09955740768261874</v>
+        <v>0.1020528677105904</v>
       </c>
       <c r="H20" t="n">
-        <v>1.063164955632333</v>
+        <v>1.027246739230381</v>
       </c>
       <c r="I20" t="n">
-        <v>0.02380812105320115</v>
+        <v>0.01971955431579668</v>
       </c>
     </row>
     <row r="21">
@@ -1031,28 +1031,28 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.1256515584378242</v>
+        <v>0.1722458827409744</v>
       </c>
       <c r="C21" t="n">
-        <v>0.08618276281070709</v>
+        <v>0.1234522266731262</v>
       </c>
       <c r="D21" t="n">
-        <v>1.065388721046448</v>
+        <v>1.021360656646729</v>
       </c>
       <c r="E21" t="n">
-        <v>0.03414185281962157</v>
+        <v>0.04368685431075096</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1150524232515892</v>
+        <v>0.2122405539542971</v>
       </c>
       <c r="G21" t="n">
-        <v>0.08571589437579252</v>
+        <v>0.1281065746125739</v>
       </c>
       <c r="H21" t="n">
-        <v>1.096758741616814</v>
+        <v>0.9434870625320111</v>
       </c>
       <c r="I21" t="n">
-        <v>0.02385273544449013</v>
+        <v>0.07941654508741995</v>
       </c>
     </row>
     <row r="22">
@@ -1060,28 +1060,28 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>0.1055682743191719</v>
+        <v>0.1478328801832199</v>
       </c>
       <c r="C22" t="n">
-        <v>0.06927024042892456</v>
+        <v>0.1046468336567879</v>
       </c>
       <c r="D22" t="n">
-        <v>1.066124374252319</v>
+        <v>0.9847029998435974</v>
       </c>
       <c r="E22" t="n">
-        <v>0.03096741229486465</v>
+        <v>0.03826253172135353</v>
       </c>
       <c r="F22" t="n">
-        <v>0.09553511699397256</v>
+        <v>0.09973549900105494</v>
       </c>
       <c r="G22" t="n">
-        <v>0.05716121312504297</v>
+        <v>0.06723771052298305</v>
       </c>
       <c r="H22" t="n">
-        <v>1.03953941915397</v>
+        <v>0.9250754694720855</v>
       </c>
       <c r="I22" t="n">
-        <v>0.03317620620192264</v>
+        <v>0.02787241141933212</v>
       </c>
     </row>
     <row r="23">
@@ -1089,28 +1089,28 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>0.0883425799999237</v>
+        <v>0.1232481318941116</v>
       </c>
       <c r="C23" t="n">
-        <v>0.05548068667304516</v>
+        <v>0.08088255692505837</v>
       </c>
       <c r="D23" t="n">
-        <v>1.037852922950745</v>
+        <v>0.9616136911392212</v>
       </c>
       <c r="E23" t="n">
-        <v>0.02767262744736671</v>
+        <v>0.03755750710093975</v>
       </c>
       <c r="F23" t="n">
-        <v>0.06219587946161749</v>
+        <v>0.1173936784257702</v>
       </c>
       <c r="G23" t="n">
-        <v>0.03332107978120908</v>
+        <v>0.07276081298877519</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8828763269483557</v>
+        <v>0.8749971550440516</v>
       </c>
       <c r="I23" t="n">
-        <v>0.02446041804335732</v>
+        <v>0.04025788106668442</v>
       </c>
     </row>
     <row r="24">
@@ -1118,28 +1118,28 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>0.07663747533655167</v>
+        <v>0.106100627705574</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04200573050582409</v>
+        <v>0.06837650827407837</v>
       </c>
       <c r="D24" t="n">
-        <v>1.015651361686706</v>
+        <v>0.9276466688117981</v>
       </c>
       <c r="E24" t="n">
-        <v>0.02955348780477047</v>
+        <v>0.03308588712692261</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0833080380659119</v>
+        <v>0.09022188516318506</v>
       </c>
       <c r="G24" t="n">
-        <v>0.04766627919153716</v>
+        <v>0.06592606343997438</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9949018585701362</v>
+        <v>0.9279321042942962</v>
       </c>
       <c r="I24" t="n">
-        <v>0.03066724975032771</v>
+        <v>0.01965616084222012</v>
       </c>
     </row>
     <row r="25">
@@ -1147,28 +1147,28 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>0.06602129202985764</v>
+        <v>0.0923797856016159</v>
       </c>
       <c r="C25" t="n">
-        <v>0.03508914161324501</v>
+        <v>0.05492721653676033</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9672912681427002</v>
+        <v>0.9222091367073059</v>
       </c>
       <c r="E25" t="n">
-        <v>0.02609569436872005</v>
+        <v>0.03284152420854568</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0470312651651524</v>
+        <v>0.1140680070554452</v>
       </c>
       <c r="G25" t="n">
-        <v>0.03065359708353221</v>
+        <v>0.04784902303657369</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9013601302906117</v>
+        <v>0.9476518024161433</v>
       </c>
       <c r="I25" t="n">
-        <v>0.01187086795023711</v>
+        <v>0.06148072443598635</v>
       </c>
     </row>
     <row r="26">
@@ -1176,28 +1176,28 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>0.05678033411836624</v>
+        <v>0.07866384909534455</v>
       </c>
       <c r="C26" t="n">
-        <v>0.02771030781507492</v>
+        <v>0.0441304281835556</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9181773237304688</v>
+        <v>0.881550722946167</v>
       </c>
       <c r="E26" t="n">
-        <v>0.02447913961851597</v>
+        <v>0.03012566708660126</v>
       </c>
       <c r="F26" t="n">
-        <v>0.07909880790294287</v>
+        <v>0.0641175613422281</v>
       </c>
       <c r="G26" t="n">
-        <v>0.05686203392085788</v>
+        <v>0.03672188706343559</v>
       </c>
       <c r="H26" t="n">
-        <v>0.926102790649719</v>
+        <v>0.8757307983533787</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0176062606406348</v>
+        <v>0.02301701992409848</v>
       </c>
     </row>
     <row r="27">
@@ -1205,28 +1205,28 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>0.054341414747715</v>
+        <v>0.06879638511753082</v>
       </c>
       <c r="C27" t="n">
-        <v>0.01909978549849987</v>
+        <v>0.03923519348144532</v>
       </c>
       <c r="D27" t="n">
-        <v>0.8863020509033203</v>
+        <v>0.8742204827461243</v>
       </c>
       <c r="E27" t="n">
-        <v>0.03081011877608299</v>
+        <v>0.02519008904027939</v>
       </c>
       <c r="F27" t="n">
-        <v>0.04996906812632453</v>
+        <v>0.05434653928919678</v>
       </c>
       <c r="G27" t="n">
-        <v>0.03362298127986964</v>
+        <v>0.02828266460320884</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8592452287712844</v>
+        <v>0.8320984819157089</v>
       </c>
       <c r="I27" t="n">
-        <v>0.01204986095829558</v>
+        <v>0.02190338253598131</v>
       </c>
     </row>
     <row r="28">
@@ -1234,28 +1234,28 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>0.04451423580944538</v>
+        <v>0.06506300870513916</v>
       </c>
       <c r="C28" t="n">
-        <v>0.01677751677149534</v>
+        <v>0.02902293869161606</v>
       </c>
       <c r="D28" t="n">
-        <v>0.8424216785240173</v>
+        <v>0.8437274398803711</v>
       </c>
       <c r="E28" t="n">
-        <v>0.02352461106994748</v>
+        <v>0.03182143284416199</v>
       </c>
       <c r="F28" t="n">
-        <v>0.02800018146852879</v>
+        <v>0.0650195587109197</v>
       </c>
       <c r="G28" t="n">
-        <v>0.007247313936294146</v>
+        <v>0.02349142612959296</v>
       </c>
       <c r="H28" t="n">
-        <v>0.870473056407387</v>
+        <v>0.8117460279402492</v>
       </c>
       <c r="I28" t="n">
-        <v>0.01640050223221787</v>
+        <v>0.03746940274587657</v>
       </c>
     </row>
     <row r="29">
@@ -1263,28 +1263,28 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>0.04411240012168884</v>
+        <v>0.05377949655056</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0142639862434864</v>
+        <v>0.02452250190353394</v>
       </c>
       <c r="D29" t="n">
-        <v>0.7978330489349366</v>
+        <v>0.8036354398727417</v>
       </c>
       <c r="E29" t="n">
-        <v>0.02585924864143133</v>
+        <v>0.02523881723046303</v>
       </c>
       <c r="F29" t="n">
-        <v>0.02426208780005842</v>
+        <v>0.06815647874629129</v>
       </c>
       <c r="G29" t="n">
-        <v>0.01047383063732605</v>
+        <v>0.01214727245502137</v>
       </c>
       <c r="H29" t="n">
-        <v>0.7909849782013387</v>
+        <v>0.7053266469339368</v>
       </c>
       <c r="I29" t="n">
-        <v>0.009833331831334368</v>
+        <v>0.05248257361607684</v>
       </c>
     </row>
     <row r="30">
@@ -1292,28 +1292,28 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>0.0357277525138855</v>
+        <v>0.04786262300562859</v>
       </c>
       <c r="C30" t="n">
-        <v>0.007671792581692338</v>
+        <v>0.02133850892496109</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7340492292137146</v>
+        <v>0.7796098132705689</v>
       </c>
       <c r="E30" t="n">
-        <v>0.02438571375656128</v>
+        <v>0.02262606527918577</v>
       </c>
       <c r="F30" t="n">
-        <v>0.03548800696337787</v>
+        <v>0.02361016490853727</v>
       </c>
       <c r="G30" t="n">
-        <v>0.02018777054040214</v>
+        <v>0.01478110237001498</v>
       </c>
       <c r="H30" t="n">
-        <v>0.7251731417307457</v>
+        <v>0.836432756611418</v>
       </c>
       <c r="I30" t="n">
-        <v>0.01167437071816276</v>
+        <v>0.004646898920497391</v>
       </c>
     </row>
     <row r="31">
@@ -1321,28 +1321,28 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>0.03173398470544815</v>
+        <v>0.04409832788467407</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0117203526597023</v>
+        <v>0.01566595345032215</v>
       </c>
       <c r="D31" t="n">
-        <v>0.687652443195343</v>
+        <v>0.7450112461013794</v>
       </c>
       <c r="E31" t="n">
-        <v>0.01657537011373043</v>
+        <v>0.02470731824743748</v>
       </c>
       <c r="F31" t="n">
-        <v>0.01656232007273259</v>
+        <v>0.08605313886534331</v>
       </c>
       <c r="G31" t="n">
-        <v>0.004750215874477419</v>
+        <v>0.01078554271588172</v>
       </c>
       <c r="H31" t="n">
-        <v>0.6510646528676517</v>
+        <v>0.7995273996449606</v>
       </c>
       <c r="I31" t="n">
-        <v>0.008556781052437051</v>
+        <v>0.07126995857300611</v>
       </c>
     </row>
     <row r="32">
@@ -1350,28 +1350,28 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>0.02731603466451168</v>
+        <v>0.04078943452215195</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0066355857475698</v>
+        <v>0.01568102884075046</v>
       </c>
       <c r="D32" t="n">
-        <v>0.6479140297737122</v>
+        <v>0.7036118940505981</v>
       </c>
       <c r="E32" t="n">
-        <v>0.01744087881815434</v>
+        <v>0.02159034634560347</v>
       </c>
       <c r="F32" t="n">
-        <v>0.02301451800770899</v>
+        <v>0.03882880720335741</v>
       </c>
       <c r="G32" t="n">
-        <v>0.001666634766017292</v>
+        <v>0.00566129770962488</v>
       </c>
       <c r="H32" t="n">
-        <v>0.6065799527144937</v>
+        <v>0.6742056144820147</v>
       </c>
       <c r="I32" t="n">
-        <v>0.01831498361443326</v>
+        <v>0.0297964820993812</v>
       </c>
     </row>
     <row r="33">
@@ -1379,28 +1379,28 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>0.02918464653468132</v>
+        <v>0.03576394287347794</v>
       </c>
       <c r="C33" t="n">
-        <v>0.007769101857453584</v>
+        <v>0.01429586565110087</v>
       </c>
       <c r="D33" t="n">
-        <v>0.6205867830429077</v>
+        <v>0.6473557966079712</v>
       </c>
       <c r="E33" t="n">
-        <v>0.01831261062192917</v>
+        <v>0.0182312985547781</v>
       </c>
       <c r="F33" t="n">
-        <v>0.02178204032423835</v>
+        <v>0.02613035314684494</v>
       </c>
       <c r="G33" t="n">
-        <v>0.006296019551281925</v>
+        <v>0.01203848310653576</v>
       </c>
       <c r="H33" t="n">
-        <v>0.5885930238034558</v>
+        <v>0.6452346286688115</v>
       </c>
       <c r="I33" t="n">
-        <v>0.01254305580281463</v>
+        <v>0.01086569704601562</v>
       </c>
     </row>
     <row r="34">
@@ -1408,28 +1408,28 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>0.02424287102472782</v>
+        <v>0.03014598210930824</v>
       </c>
       <c r="C34" t="n">
-        <v>0.00571787028029561</v>
+        <v>0.007246975962519646</v>
       </c>
       <c r="D34" t="n">
-        <v>0.5816479067382813</v>
+        <v>0.6202552660484314</v>
       </c>
       <c r="E34" t="n">
-        <v>0.01561676127433777</v>
+        <v>0.01979772974252701</v>
       </c>
       <c r="F34" t="n">
-        <v>0.02607731738752195</v>
+        <v>0.02658688127484057</v>
       </c>
       <c r="G34" t="n">
-        <v>0.001623428609886102</v>
+        <v>0.009091946570230056</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5292049270780791</v>
+        <v>0.6003831081755981</v>
       </c>
       <c r="I34" t="n">
-        <v>0.02180786394919793</v>
+        <v>0.01449301915671707</v>
       </c>
     </row>
     <row r="35">
@@ -1437,28 +1437,28 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>0.0241489354429245</v>
+        <v>0.02622945692682266</v>
       </c>
       <c r="C35" t="n">
-        <v>0.006609172161340713</v>
+        <v>0.006245839105665684</v>
       </c>
       <c r="D35" t="n">
-        <v>0.5521787458534241</v>
+        <v>0.5818068117179871</v>
       </c>
       <c r="E35" t="n">
-        <v>0.01477886978417635</v>
+        <v>0.01707458389139175</v>
       </c>
       <c r="F35" t="n">
-        <v>0.01411506958330144</v>
+        <v>0.02702926245176189</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0006490145289972667</v>
+        <v>0.006170715049067193</v>
       </c>
       <c r="H35" t="n">
-        <v>0.5181874457346868</v>
+        <v>0.5902208398022426</v>
       </c>
       <c r="I35" t="n">
-        <v>0.01087511781323549</v>
+        <v>0.01790744337668038</v>
       </c>
     </row>
     <row r="36">
@@ -1466,28 +1466,28 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>0.02008838251566887</v>
+        <v>0.02669391036713123</v>
       </c>
       <c r="C36" t="n">
-        <v>0.004563639694675803</v>
+        <v>0.008410953006342054</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4957948105926513</v>
+        <v>0.5578503577594757</v>
       </c>
       <c r="E36" t="n">
-        <v>0.01304576892089844</v>
+        <v>0.01549370578193665</v>
       </c>
       <c r="F36" t="n">
-        <v>0.02542985426125285</v>
+        <v>0.02167958304456163</v>
       </c>
       <c r="G36" t="n">
-        <v>0.002705877780182011</v>
+        <v>0.007433114128573197</v>
       </c>
       <c r="H36" t="n">
-        <v>0.4814795085111995</v>
+        <v>0.5310397399385834</v>
       </c>
       <c r="I36" t="n">
-        <v>0.02031657916151874</v>
+        <v>0.01159127020749581</v>
       </c>
     </row>
     <row r="37">
@@ -1495,28 +1495,28 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>0.01960647313380241</v>
+        <v>0.02386739094948769</v>
       </c>
       <c r="C37" t="n">
-        <v>0.001971566689319909</v>
+        <v>0.00595164274430275</v>
       </c>
       <c r="D37" t="n">
-        <v>0.4982906083507538</v>
+        <v>0.5233570670242309</v>
       </c>
       <c r="E37" t="n">
-        <v>0.01514345351588726</v>
+        <v>0.01529896275937557</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0195290631594267</v>
+        <v>0.02670295337236336</v>
       </c>
       <c r="G37" t="n">
-        <v>0.001505633727958818</v>
+        <v>0.00791875365762979</v>
       </c>
       <c r="H37" t="n">
-        <v>0.5096226091252649</v>
+        <v>0.4959442247438197</v>
       </c>
       <c r="I37" t="n">
-        <v>0.01547531642353992</v>
+        <v>0.01630447876881231</v>
       </c>
     </row>
     <row r="38">
@@ -1524,28 +1524,28 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>0.01833146453666687</v>
+        <v>0.02260878234505653</v>
       </c>
       <c r="C38" t="n">
-        <v>0.001736817742906511</v>
+        <v>0.003425638859540224</v>
       </c>
       <c r="D38" t="n">
-        <v>0.4914938780117035</v>
+        <v>0.5097674082260132</v>
       </c>
       <c r="E38" t="n">
-        <v>0.01413717740058899</v>
+        <v>0.01663430661487579</v>
       </c>
       <c r="F38" t="n">
-        <v>0.02258907967835033</v>
+        <v>0.02226999886066548</v>
       </c>
       <c r="G38" t="n">
-        <v>0.001684022625698594</v>
+        <v>0.001371092309607086</v>
       </c>
       <c r="H38" t="n">
-        <v>0.4558551879672009</v>
+        <v>0.4634487947670904</v>
       </c>
       <c r="I38" t="n">
-        <v>0.01862578108299031</v>
+        <v>0.01858166249149873</v>
       </c>
     </row>
     <row r="39">
@@ -1553,28 +1553,28 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>0.0192258744519949</v>
+        <v>0.02118666721338034</v>
       </c>
       <c r="C39" t="n">
-        <v>0.004969430950671434</v>
+        <v>0.002593398402992636</v>
       </c>
       <c r="D39" t="n">
-        <v>0.458818970993042</v>
+        <v>0.4907111116657257</v>
       </c>
       <c r="E39" t="n">
-        <v>0.01196234897273779</v>
+        <v>0.0161397135180831</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0257826893909137</v>
+        <v>0.01674617583621871</v>
       </c>
       <c r="G39" t="n">
-        <v>0.00173445369947252</v>
+        <v>0.002164594095631777</v>
       </c>
       <c r="H39" t="n">
-        <v>0.4420582784661267</v>
+        <v>0.4593257764229767</v>
       </c>
       <c r="I39" t="n">
-        <v>0.02183794442521709</v>
+        <v>0.01228495321007139</v>
       </c>
     </row>
     <row r="40">
@@ -1582,28 +1582,28 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>0.02106726478213072</v>
+        <v>0.01989102551841736</v>
       </c>
       <c r="C40" t="n">
-        <v>0.008920890215098858</v>
+        <v>0.002382651829048991</v>
       </c>
       <c r="D40" t="n">
-        <v>0.4397019571685791</v>
+        <v>0.4707548523845673</v>
       </c>
       <c r="E40" t="n">
-        <v>0.009947865019530058</v>
+        <v>0.01515459931457043</v>
       </c>
       <c r="F40" t="n">
-        <v>0.00836658143291028</v>
+        <v>0.03039010384537851</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0002502926516388034</v>
+        <v>0.003736665077692849</v>
       </c>
       <c r="H40" t="n">
-        <v>0.4111171914372125</v>
+        <v>0.4683773674817109</v>
       </c>
       <c r="I40" t="n">
-        <v>0.006060702823540029</v>
+        <v>0.0243115518477914</v>
       </c>
     </row>
     <row r="41">
@@ -1611,28 +1611,28 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>0.01649401701509953</v>
+        <v>0.01992486591297388</v>
       </c>
       <c r="C41" t="n">
-        <v>0.00444512064962089</v>
+        <v>0.004339875364344567</v>
       </c>
       <c r="D41" t="n">
-        <v>0.41342952044487</v>
+        <v>0.4540593857002258</v>
       </c>
       <c r="E41" t="n">
-        <v>0.009981748841255904</v>
+        <v>0.01331469360405207</v>
       </c>
       <c r="F41" t="n">
-        <v>0.01047904148606696</v>
+        <v>0.03406062156423854</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0002943815907416334</v>
+        <v>0.003539380662775253</v>
       </c>
       <c r="H41" t="n">
-        <v>0.3978652876878057</v>
+        <v>0.431117762074385</v>
       </c>
       <c r="I41" t="n">
-        <v>0.008195333488552937</v>
+        <v>0.02836565229841197</v>
       </c>
     </row>
     <row r="42">
@@ -1640,28 +1640,28 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>0.01552010438036919</v>
+        <v>0.01760652629601955</v>
       </c>
       <c r="C42" t="n">
-        <v>0.004030635773252696</v>
+        <v>0.001776618570201099</v>
       </c>
       <c r="D42" t="n">
-        <v>0.3966359754543304</v>
+        <v>0.4347919414367676</v>
       </c>
       <c r="E42" t="n">
-        <v>0.009506288709044457</v>
+        <v>0.01365594816923141</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0133938986196093</v>
+        <v>0.01542248064326958</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0006340990748049823</v>
+        <v>0.001740211631744176</v>
       </c>
       <c r="H42" t="n">
-        <v>0.3828879036308308</v>
+        <v>0.4471322170070101</v>
       </c>
       <c r="I42" t="n">
-        <v>0.01084536011842783</v>
+        <v>0.01144660814466231</v>
       </c>
     </row>
     <row r="43">
@@ -1669,28 +1669,28 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>0.01526836198830605</v>
+        <v>0.01677435512191057</v>
       </c>
       <c r="C43" t="n">
-        <v>0.003970092891611159</v>
+        <v>0.001510686784788966</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3923700071296692</v>
+        <v>0.4183129337425232</v>
       </c>
       <c r="E43" t="n">
-        <v>0.009336419260919094</v>
+        <v>0.01317210369879007</v>
       </c>
       <c r="F43" t="n">
-        <v>0.02102313414313276</v>
+        <v>0.0107154319629219</v>
       </c>
       <c r="G43" t="n">
-        <v>0.001185498060104034</v>
+        <v>0.001182975430082572</v>
       </c>
       <c r="H43" t="n">
-        <v>0.4442308977513679</v>
+        <v>0.4499087462923071</v>
       </c>
       <c r="I43" t="n">
-        <v>0.01761648156028393</v>
+        <v>0.007282912904673164</v>
       </c>
     </row>
     <row r="44">
@@ -1698,28 +1698,28 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>0.01733469862651825</v>
+        <v>0.01511583016431332</v>
       </c>
       <c r="C44" t="n">
-        <v>0.006753825173854828</v>
+        <v>0.001187203839696944</v>
       </c>
       <c r="D44" t="n">
-        <v>0.380659242099762</v>
+        <v>0.4036045931625366</v>
       </c>
       <c r="E44" t="n">
-        <v>0.008677577374994755</v>
+        <v>0.01191060340428352</v>
       </c>
       <c r="F44" t="n">
-        <v>0.01575488658205623</v>
+        <v>0.0133148742209494</v>
       </c>
       <c r="G44" t="n">
-        <v>0.009090295384955543</v>
+        <v>0.0008088450126014164</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3881490894165164</v>
+        <v>0.3842103078100849</v>
       </c>
       <c r="I44" t="n">
-        <v>0.004723845839828593</v>
+        <v>0.01058497766680031</v>
       </c>
     </row>
     <row r="45">
@@ -1727,28 +1727,28 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>0.01308483933496475</v>
+        <v>0.01756622532951832</v>
       </c>
       <c r="C45" t="n">
-        <v>0.003665255201173946</v>
+        <v>0.005228457485834137</v>
       </c>
       <c r="D45" t="n">
-        <v>0.365796716085434</v>
+        <v>0.3952973809776306</v>
       </c>
       <c r="E45" t="n">
-        <v>0.007590600558340549</v>
+        <v>0.01036128081059456</v>
       </c>
       <c r="F45" t="n">
-        <v>0.01517221909107528</v>
+        <v>0.0117658840530046</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0009376852825051553</v>
+        <v>0.0002508040360873186</v>
       </c>
       <c r="H45" t="n">
-        <v>0.358520143069023</v>
+        <v>0.3680755195240407</v>
       </c>
       <c r="I45" t="n">
-        <v>0.01244193304822359</v>
+        <v>0.009674702349618734</v>
       </c>
     </row>
     <row r="46">
@@ -1756,28 +1756,28 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>0.01197551711136103</v>
+        <v>0.01360489166003466</v>
       </c>
       <c r="C46" t="n">
-        <v>0.00068152494193241</v>
+        <v>0.0009614504405520857</v>
       </c>
       <c r="D46" t="n">
-        <v>0.3624747080535889</v>
+        <v>0.3734914213123322</v>
       </c>
       <c r="E46" t="n">
-        <v>0.009481618806660175</v>
+        <v>0.01077598427802324</v>
       </c>
       <c r="F46" t="n">
-        <v>0.01137577453843921</v>
+        <v>0.01811411828872236</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0008093568916488774</v>
+        <v>0.0008287221322604873</v>
       </c>
       <c r="H46" t="n">
-        <v>0.3559318032914235</v>
+        <v>0.3938109432017434</v>
       </c>
       <c r="I46" t="n">
-        <v>0.008786758661185062</v>
+        <v>0.01531634173205587</v>
       </c>
     </row>
     <row r="47">
@@ -1785,28 +1785,28 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>0.01190183493000269</v>
+        <v>0.01391118803977966</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0006635482421275228</v>
+        <v>0.002864521379828453</v>
       </c>
       <c r="D47" t="n">
-        <v>0.3685635004940033</v>
+        <v>0.3690911385784149</v>
       </c>
       <c r="E47" t="n">
-        <v>0.009395469301640987</v>
+        <v>0.009201210995554925</v>
       </c>
       <c r="F47" t="n">
-        <v>0.02127369227298029</v>
+        <v>0.01610853552076887</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0007495973029456498</v>
+        <v>0.0009339784980230459</v>
       </c>
       <c r="H47" t="n">
-        <v>0.3913494990758756</v>
+        <v>0.3699693533763606</v>
       </c>
       <c r="I47" t="n">
-        <v>0.0185673476670539</v>
+        <v>0.01332471023965475</v>
       </c>
     </row>
     <row r="48">
@@ -1814,28 +1814,28 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>0.01433494724148512</v>
+        <v>0.01257653056168556</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0047859563851282</v>
+        <v>0.000853763900835067</v>
       </c>
       <c r="D48" t="n">
-        <v>0.3620840274372101</v>
+        <v>0.3671672391586304</v>
       </c>
       <c r="E48" t="n">
-        <v>0.007738570849865675</v>
+        <v>0.009886930428445339</v>
       </c>
       <c r="F48" t="n">
-        <v>0.01774056995041413</v>
+        <v>0.009545771751558896</v>
       </c>
       <c r="G48" t="n">
-        <v>0.001113152981752478</v>
+        <v>0.0009522568069468291</v>
       </c>
       <c r="H48" t="n">
-        <v>0.369666224791992</v>
+        <v>0.3422217301287814</v>
       </c>
       <c r="I48" t="n">
-        <v>0.01477908578748415</v>
+        <v>0.006882406312996615</v>
       </c>
     </row>
     <row r="49">
@@ -1843,28 +1843,28 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>0.01308206604009867</v>
+        <v>0.01234290491306782</v>
       </c>
       <c r="C49" t="n">
-        <v>0.003717428137035109</v>
+        <v>0.0007429401794448495</v>
       </c>
       <c r="D49" t="n">
-        <v>0.3540552171993256</v>
+        <v>0.3570678370285034</v>
       </c>
       <c r="E49" t="n">
-        <v>0.007594361690819264</v>
+        <v>0.009814625531017781</v>
       </c>
       <c r="F49" t="n">
-        <v>0.01043789983196807</v>
+        <v>0.01626387411761926</v>
       </c>
       <c r="G49" t="n">
-        <v>0.0004525273495074969</v>
+        <v>0.0008967079120562039</v>
       </c>
       <c r="H49" t="n">
-        <v>0.3671969978202614</v>
+        <v>0.369067855276058</v>
       </c>
       <c r="I49" t="n">
-        <v>0.008149387431718396</v>
+        <v>0.01352182680993154</v>
       </c>
     </row>
     <row r="50">
@@ -1872,28 +1872,28 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>0.01089192160278559</v>
+        <v>0.01202647205889225</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0005814134084805847</v>
+        <v>0.0007760330836772918</v>
       </c>
       <c r="D50" t="n">
-        <v>0.3544094161987305</v>
+        <v>0.360497412612915</v>
       </c>
       <c r="E50" t="n">
-        <v>0.008538461195766926</v>
+        <v>0.009447951905429363</v>
       </c>
       <c r="F50" t="n">
-        <v>0.01037019368473799</v>
+        <v>0.06787453758094283</v>
       </c>
       <c r="G50" t="n">
-        <v>0.0004606946610802326</v>
+        <v>0.06036734434923379</v>
       </c>
       <c r="H50" t="n">
-        <v>0.3623700758275161</v>
+        <v>0.3680044805400718</v>
       </c>
       <c r="I50" t="n">
-        <v>0.008097648762263734</v>
+        <v>0.005667171176358887</v>
       </c>
     </row>
     <row r="51">
@@ -1901,28 +1901,28 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>0.01103003937673569</v>
+        <v>0.01318404745179415</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0007272360869050026</v>
+        <v>0.003546592910606414</v>
       </c>
       <c r="D51" t="n">
-        <v>0.3656248077259064</v>
+        <v>0.3415479417705536</v>
       </c>
       <c r="E51" t="n">
-        <v>0.008474679289489985</v>
+        <v>0.007929714852511883</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1407396516529615</v>
+        <v>0.01056816765719487</v>
       </c>
       <c r="G51" t="n">
-        <v>0.1326143485667461</v>
+        <v>0.0003675532238641496</v>
       </c>
       <c r="H51" t="n">
-        <v>0.4124794704295683</v>
+        <v>0.3473533246839999</v>
       </c>
       <c r="I51" t="n">
-        <v>0.006062904187184903</v>
+        <v>0.008463847663672868</v>
       </c>
     </row>
     <row r="52">
@@ -1930,28 +1930,28 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>0.02112077792745829</v>
+        <v>0.01261311922752857</v>
       </c>
       <c r="C52" t="n">
-        <v>0.01349384085786156</v>
+        <v>0.003527996639639139</v>
       </c>
       <c r="D52" t="n">
-        <v>0.3414610905303955</v>
+        <v>0.3476461915187836</v>
       </c>
       <c r="E52" t="n">
-        <v>0.005919631964623928</v>
+        <v>0.007346891659021378</v>
       </c>
       <c r="F52" t="n">
-        <v>0.007868218404190769</v>
+        <v>0.009736875771844173</v>
       </c>
       <c r="G52" t="n">
-        <v>0.0002985731115983267</v>
+        <v>0.0002496835387799567</v>
       </c>
       <c r="H52" t="n">
-        <v>0.3147215786357494</v>
+        <v>0.3229121348500057</v>
       </c>
       <c r="I52" t="n">
-        <v>0.005996037404771536</v>
+        <v>0.007872631536587028</v>
       </c>
     </row>
     <row r="53">
@@ -1959,28 +1959,28 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>0.01310720088398457</v>
+        <v>0.0103166771350503</v>
       </c>
       <c r="C53" t="n">
-        <v>0.004868281434375793</v>
+        <v>0.0006248763764146716</v>
       </c>
       <c r="D53" t="n">
-        <v>0.3355856951580047</v>
+        <v>0.342946542219162</v>
       </c>
       <c r="E53" t="n">
-        <v>0.006560991037786007</v>
+        <v>0.007977068056613208</v>
       </c>
       <c r="F53" t="n">
-        <v>0.00919094343698579</v>
+        <v>0.01701755975152793</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0006369890654793839</v>
+        <v>0.0007545156353441953</v>
       </c>
       <c r="H53" t="n">
-        <v>0.344264742207955</v>
+        <v>0.3677092346709471</v>
       </c>
       <c r="I53" t="n">
-        <v>0.00683263072856439</v>
+        <v>0.01442449790600317</v>
       </c>
     </row>
     <row r="54">
@@ -1988,28 +1988,28 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>0.01309460709351301</v>
+        <v>0.01096888979041576</v>
       </c>
       <c r="C54" t="n">
-        <v>0.00511005626061</v>
+        <v>0.002794269742026925</v>
       </c>
       <c r="D54" t="n">
-        <v>0.3366850780448913</v>
+        <v>0.3345775045585632</v>
       </c>
       <c r="E54" t="n">
-        <v>0.006301125533133745</v>
+        <v>0.006501732618838549</v>
       </c>
       <c r="F54" t="n">
-        <v>0.009245867285555378</v>
+        <v>0.005487073808665376</v>
       </c>
       <c r="G54" t="n">
-        <v>0.0001352163811660938</v>
+        <v>0.001356431929771386</v>
       </c>
       <c r="H54" t="n">
-        <v>0.3224381808783452</v>
+        <v>0.3399961518599586</v>
       </c>
       <c r="I54" t="n">
-        <v>0.007498459972009719</v>
+        <v>0.002430661167679005</v>
       </c>
     </row>
     <row r="55">
@@ -2017,28 +2017,28 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>0.00972385770970583</v>
+        <v>0.009395465668380261</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0004249382463674992</v>
+        <v>0.001048630602899007</v>
       </c>
       <c r="D55" t="n">
-        <v>0.3553400555133819</v>
+        <v>0.3294946347408295</v>
       </c>
       <c r="E55" t="n">
-        <v>0.007522219243556261</v>
+        <v>0.006699361905872822</v>
       </c>
       <c r="F55" t="n">
-        <v>0.01732855013749436</v>
+        <v>0.008845322019136457</v>
       </c>
       <c r="G55" t="n">
-        <v>0.001128300454537422</v>
+        <v>0.0001284668515510417</v>
       </c>
       <c r="H55" t="n">
-        <v>0.3689032539944081</v>
+        <v>0.3084366621609418</v>
       </c>
       <c r="I55" t="n">
-        <v>0.01435573363497391</v>
+        <v>0.007174671868691874</v>
       </c>
     </row>
     <row r="56">
@@ -2046,28 +2046,28 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>0.01314311903050542</v>
+        <v>0.00910783186262846</v>
       </c>
       <c r="C56" t="n">
-        <v>0.004767265441546217</v>
+        <v>0.0004515291961282492</v>
       </c>
       <c r="D56" t="n">
-        <v>0.3562712500991821</v>
+        <v>0.3252755517082214</v>
       </c>
       <c r="E56" t="n">
-        <v>0.006594497217267752</v>
+        <v>0.007029924959003926</v>
       </c>
       <c r="F56" t="n">
-        <v>0.009128712343377157</v>
+        <v>0.009921297419931722</v>
       </c>
       <c r="G56" t="n">
-        <v>0.0001369393175770947</v>
+        <v>0.0006865616151903487</v>
       </c>
       <c r="H56" t="n">
-        <v>0.3214756750574314</v>
+        <v>0.338041308248996</v>
       </c>
       <c r="I56" t="n">
-        <v>0.007384394731579218</v>
+        <v>0.007544529380802472</v>
       </c>
     </row>
     <row r="57">
@@ -2075,28 +2075,28 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>0.01199700978147984</v>
+        <v>0.009250756518959999</v>
       </c>
       <c r="C57" t="n">
-        <v>0.004445896459318697</v>
+        <v>0.0004977456665709615</v>
       </c>
       <c r="D57" t="n">
-        <v>0.3408219199066162</v>
+        <v>0.3338433036117553</v>
       </c>
       <c r="E57" t="n">
-        <v>0.005847003497362137</v>
+        <v>0.007083794370770454</v>
       </c>
       <c r="F57" t="n">
-        <v>0.008474816333557225</v>
+        <v>0.0115264276305721</v>
       </c>
       <c r="G57" t="n">
-        <v>0.0004221345652365787</v>
+        <v>0.003717323470447474</v>
       </c>
       <c r="H57" t="n">
-        <v>0.3512402477719461</v>
+        <v>0.3471649367949313</v>
       </c>
       <c r="I57" t="n">
-        <v>0.006296480537329908</v>
+        <v>0.006073279494805592</v>
       </c>
     </row>
     <row r="58">
@@ -2104,28 +2104,28 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>0.01338711946928501</v>
+        <v>0.01091589297646284</v>
       </c>
       <c r="C58" t="n">
-        <v>0.005870083191469312</v>
+        <v>0.003370851875340566</v>
       </c>
       <c r="D58" t="n">
-        <v>0.3466616812591553</v>
+        <v>0.3257796683273315</v>
       </c>
       <c r="E58" t="n">
-        <v>0.005783727928698063</v>
+        <v>0.00591614288046956</v>
       </c>
       <c r="F58" t="n">
-        <v>0.007726913938939961</v>
+        <v>0.009067508511026473</v>
       </c>
       <c r="G58" t="n">
-        <v>0.0002854899315525843</v>
+        <v>0.0002992459836049039</v>
       </c>
       <c r="H58" t="n">
-        <v>0.3495878149109602</v>
+        <v>0.3201469457052271</v>
       </c>
       <c r="I58" t="n">
-        <v>0.005693484925973376</v>
+        <v>0.007167527721085712</v>
       </c>
     </row>
     <row r="59">
@@ -2133,28 +2133,28 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>0.008853685813367367</v>
+        <v>0.01104814559644461</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0003780890929326415</v>
+        <v>0.003664785655079409</v>
       </c>
       <c r="D59" t="n">
-        <v>0.3507136616153717</v>
+        <v>0.3257974304027557</v>
       </c>
       <c r="E59" t="n">
-        <v>0.006722028437972069</v>
+        <v>0.005754372797638178</v>
       </c>
       <c r="F59" t="n">
-        <v>0.01446367150029778</v>
+        <v>0.009305121420197444</v>
       </c>
       <c r="G59" t="n">
-        <v>0.0007413232350854133</v>
+        <v>0.0001741836515128412</v>
       </c>
       <c r="H59" t="n">
-        <v>0.3597704984099402</v>
+        <v>0.3207249978413201</v>
       </c>
       <c r="I59" t="n">
-        <v>0.01192349572992636</v>
+        <v>0.007527312783047338</v>
       </c>
     </row>
     <row r="60">
@@ -2162,28 +2162,28 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>0.00945649965262413</v>
+        <v>0.009093827992498875</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0009089847180843353</v>
+        <v>0.002057497360364534</v>
       </c>
       <c r="D60" t="n">
-        <v>0.3619874533805847</v>
+        <v>0.3244459436836243</v>
       </c>
       <c r="E60" t="n">
-        <v>0.006737577737748623</v>
+        <v>0.005414101059883833</v>
       </c>
       <c r="F60" t="n">
-        <v>0.2145613263491511</v>
+        <v>0.01297727426389448</v>
       </c>
       <c r="G60" t="n">
-        <v>0.2031047749918009</v>
+        <v>0.0002513124167052786</v>
       </c>
       <c r="H60" t="n">
-        <v>0.3942916176447472</v>
+        <v>0.3034414119938264</v>
       </c>
       <c r="I60" t="n">
-        <v>0.009485093789390891</v>
+        <v>0.01120875491750036</v>
       </c>
     </row>
     <row r="61">
@@ -2191,28 +2191,28 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>0.01451124830132723</v>
+        <v>0.008453780023396015</v>
       </c>
       <c r="C61" t="n">
-        <v>0.007043962925933301</v>
+        <v>0.0004036587510369718</v>
       </c>
       <c r="D61" t="n">
-        <v>0.3584669437599182</v>
+        <v>0.3216472985115051</v>
       </c>
       <c r="E61" t="n">
-        <v>0.005674950594007969</v>
+        <v>0.006441884770005941</v>
       </c>
       <c r="F61" t="n">
-        <v>0.008153273681509893</v>
+        <v>0.0090532218370143</v>
       </c>
       <c r="G61" t="n">
-        <v>0.000380216594382841</v>
+        <v>9.297928942646983e-05</v>
       </c>
       <c r="H61" t="n">
-        <v>0.3509126762659281</v>
+        <v>0.3261761277943218</v>
       </c>
       <c r="I61" t="n">
-        <v>0.00601849364891624</v>
+        <v>0.007329361834039161</v>
       </c>
     </row>
     <row r="62">
@@ -2220,28 +2220,28 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>0.00889875193297863</v>
+        <v>0.0122953394254744</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0003209137636721134</v>
+        <v>0.005417064500496723</v>
       </c>
       <c r="D62" t="n">
-        <v>0.3687656640033722</v>
+        <v>0.3314291217384339</v>
       </c>
       <c r="E62" t="n">
-        <v>0.006734009887248277</v>
+        <v>0.005221129498302937</v>
       </c>
       <c r="F62" t="n">
-        <v>0.01371022846014961</v>
+        <v>0.007228739453482686</v>
       </c>
       <c r="G62" t="n">
-        <v>0.001028627265673161</v>
+        <v>0.0001466574086923514</v>
       </c>
       <c r="H62" t="n">
-        <v>0.4142789102300734</v>
+        <v>0.3032997223564696</v>
       </c>
       <c r="I62" t="n">
-        <v>0.01061020680021063</v>
+        <v>0.005565583500403419</v>
       </c>
     </row>
     <row r="63">
@@ -2249,28 +2249,28 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>0.008735592995285988</v>
+        <v>0.007865716569542885</v>
       </c>
       <c r="C63" t="n">
-        <v>0.0004076535412333906</v>
+        <v>0.0004865095863267779</v>
       </c>
       <c r="D63" t="n">
-        <v>0.3790755437850952</v>
+        <v>0.3239231209526062</v>
       </c>
       <c r="E63" t="n">
-        <v>0.006432561725437641</v>
+        <v>0.005759591429919005</v>
       </c>
       <c r="F63" t="n">
-        <v>0.008490911812915012</v>
+        <v>0.008669882840059127</v>
       </c>
       <c r="G63" t="n">
-        <v>0.0003288719350062645</v>
+        <v>0.0002920554830088033</v>
       </c>
       <c r="H63" t="n">
-        <v>0.3716053293890899</v>
+        <v>0.3681861998011977</v>
       </c>
       <c r="I63" t="n">
-        <v>0.006304013328885031</v>
+        <v>0.006536896483605001</v>
       </c>
     </row>
     <row r="64">
@@ -2278,28 +2278,28 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>0.01127190081402659</v>
+        <v>0.00795036942344904</v>
       </c>
       <c r="C64" t="n">
-        <v>0.003730665563486516</v>
+        <v>0.0003159660041704774</v>
       </c>
       <c r="D64" t="n">
-        <v>0.3878707157611847</v>
+        <v>0.3333271867542267</v>
       </c>
       <c r="E64" t="n">
-        <v>0.005601881573945284</v>
+        <v>0.005967767558723689</v>
       </c>
       <c r="F64" t="n">
-        <v>0.007787917818248175</v>
+        <v>0.006656080165005867</v>
       </c>
       <c r="G64" t="n">
-        <v>8.313370780065219e-05</v>
+        <v>0.0003387618160462478</v>
       </c>
       <c r="H64" t="n">
-        <v>0.3578507788885282</v>
+        <v>0.3405607692413579</v>
       </c>
       <c r="I64" t="n">
-        <v>0.005915530248139461</v>
+        <v>0.004614514500923685</v>
       </c>
     </row>
     <row r="65">
@@ -2307,28 +2307,28 @@
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>0.01188451181069016</v>
+        <v>0.00817199557673931</v>
       </c>
       <c r="C65" t="n">
-        <v>0.004952055171188898</v>
+        <v>0.0004358268001377582</v>
       </c>
       <c r="D65" t="n">
-        <v>0.3728212743930817</v>
+        <v>0.34439558344841</v>
       </c>
       <c r="E65" t="n">
-        <v>0.005068350348517298</v>
+        <v>0.006014190885096788</v>
       </c>
       <c r="F65" t="n">
-        <v>0.01127033325425709</v>
+        <v>0.08060996261107785</v>
       </c>
       <c r="G65" t="n">
-        <v>0.0005083499252902524</v>
+        <v>0.07375959719569221</v>
       </c>
       <c r="H65" t="n">
-        <v>0.3630569914425761</v>
+        <v>0.3497452374578106</v>
       </c>
       <c r="I65" t="n">
-        <v>0.008946698418959708</v>
+        <v>0.005101637836290466</v>
       </c>
     </row>
     <row r="66">
@@ -2336,28 +2336,28 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>0.008397802623659372</v>
+        <v>0.01180206020176411</v>
       </c>
       <c r="C66" t="n">
-        <v>0.0003391389546766877</v>
+        <v>0.005269125980600715</v>
       </c>
       <c r="D66" t="n">
-        <v>0.3797338273792267</v>
+        <v>0.3394123420963288</v>
       </c>
       <c r="E66" t="n">
-        <v>0.006159994553983211</v>
+        <v>0.0048358724873811</v>
       </c>
       <c r="F66" t="n">
-        <v>0.008128492690829429</v>
+        <v>0.04970977412910485</v>
       </c>
       <c r="G66" t="n">
-        <v>0.0002052607157702146</v>
+        <v>0.04308457408823547</v>
       </c>
       <c r="H66" t="n">
-        <v>0.3825632857556833</v>
+        <v>0.3469388745912331</v>
       </c>
       <c r="I66" t="n">
-        <v>0.006010415460792831</v>
+        <v>0.004890505659438026</v>
       </c>
     </row>
     <row r="67">
@@ -2365,28 +2365,28 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>0.01209189057037234</v>
+        <v>0.009018733113229274</v>
       </c>
       <c r="C67" t="n">
-        <v>0.0057448912473768</v>
+        <v>0.002680604323603213</v>
       </c>
       <c r="D67" t="n">
-        <v>0.3793737332992554</v>
+        <v>0.3401641678543091</v>
       </c>
       <c r="E67" t="n">
-        <v>0.004450130668722093</v>
+        <v>0.004637308006197214</v>
       </c>
       <c r="F67" t="n">
-        <v>0.005833185009330171</v>
+        <v>0.007967437667131035</v>
       </c>
       <c r="G67" t="n">
-        <v>0.000203459467593585</v>
+        <v>0.0001464651521440781</v>
       </c>
       <c r="H67" t="n">
-        <v>0.353774022933515</v>
+        <v>0.3544263046250647</v>
       </c>
       <c r="I67" t="n">
-        <v>0.003860855571482008</v>
+        <v>0.006048841082945247</v>
       </c>
     </row>
     <row r="68">
@@ -2394,28 +2394,28 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>0.01040331091171503</v>
+        <v>0.01244020371973515</v>
       </c>
       <c r="C68" t="n">
-        <v>0.003587756955446675</v>
+        <v>0.005746198304977733</v>
       </c>
       <c r="D68" t="n">
-        <v>0.3770138586120605</v>
+        <v>0.3512296343650818</v>
       </c>
       <c r="E68" t="n">
-        <v>0.0049304847663939</v>
+        <v>0.004937857065662742</v>
       </c>
       <c r="F68" t="n">
-        <v>0.007355326325199635</v>
+        <v>0.00625131859339251</v>
       </c>
       <c r="G68" t="n">
-        <v>8.927289719990004e-05</v>
+        <v>7.586615777507631e-05</v>
       </c>
       <c r="H68" t="n">
-        <v>0.352597868699234</v>
+        <v>0.324385147011105</v>
       </c>
       <c r="I68" t="n">
-        <v>0.005503064162549099</v>
+        <v>0.004553526777524933</v>
       </c>
     </row>
     <row r="69">
@@ -2423,28 +2423,28 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>0.007293720196783543</v>
+        <v>0.006976592552065849</v>
       </c>
       <c r="C69" t="n">
-        <v>0.0003133906542882324</v>
+        <v>0.0003157384751029313</v>
       </c>
       <c r="D69" t="n">
-        <v>0.3638519551391601</v>
+        <v>0.3380430499839783</v>
       </c>
       <c r="E69" t="n">
-        <v>0.005161069755166769</v>
+        <v>0.004970638840705156</v>
       </c>
       <c r="F69" t="n">
-        <v>0.00806738837939637</v>
+        <v>0.008271693579159786</v>
       </c>
       <c r="G69" t="n">
-        <v>0.0003374041201258883</v>
+        <v>0.001080408450607271</v>
       </c>
       <c r="H69" t="n">
-        <v>0.3712860220485955</v>
+        <v>0.3702123211180794</v>
       </c>
       <c r="I69" t="n">
-        <v>0.005873554169396349</v>
+        <v>0.005340223514838037</v>
       </c>
     </row>
     <row r="70">
@@ -2452,28 +2452,28 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>0.01145977466905117</v>
+        <v>0.007233162399411202</v>
       </c>
       <c r="C70" t="n">
-        <v>0.004901657651206479</v>
+        <v>0.0003107316500013694</v>
       </c>
       <c r="D70" t="n">
-        <v>0.3692063579883575</v>
+        <v>0.3580913544464112</v>
       </c>
       <c r="E70" t="n">
-        <v>0.004712085102438927</v>
+        <v>0.005131973978608846</v>
       </c>
       <c r="F70" t="n">
-        <v>0.006669973524296459</v>
+        <v>0.01414930231699061</v>
       </c>
       <c r="G70" t="n">
-        <v>0.0002458299541307331</v>
+        <v>0.0009805009136702653</v>
       </c>
       <c r="H70" t="n">
-        <v>0.3611363547602836</v>
+        <v>0.3555826248177502</v>
       </c>
       <c r="I70" t="n">
-        <v>0.004618461882151651</v>
+        <v>0.01139088817031942</v>
       </c>
     </row>
     <row r="71">
@@ -2481,28 +2481,28 @@
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>0.01517184624475241</v>
+        <v>0.007482802115440368</v>
       </c>
       <c r="C71" t="n">
-        <v>0.009010813308378681</v>
+        <v>0.00033718780406937</v>
       </c>
       <c r="D71" t="n">
-        <v>0.3669409651622772</v>
+        <v>0.3611282647304535</v>
       </c>
       <c r="E71" t="n">
-        <v>0.004326328503012658</v>
+        <v>0.005339972986340522</v>
       </c>
       <c r="F71" t="n">
-        <v>0.00699333385225586</v>
+        <v>0.007801357277260324</v>
       </c>
       <c r="G71" t="n">
-        <v>0.0002594715384800644</v>
+        <v>0.0001810080615889439</v>
       </c>
       <c r="H71" t="n">
-        <v>0.3752342745180425</v>
+        <v>0.3551989292728959</v>
       </c>
       <c r="I71" t="n">
-        <v>0.00485769096476316</v>
+        <v>0.005844354544102319</v>
       </c>
     </row>
     <row r="72">
@@ -2510,28 +2510,28 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>0.00736408453631401</v>
+        <v>0.007679746329665184</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0003078105961345136</v>
+        <v>0.001540534946929663</v>
       </c>
       <c r="D72" t="n">
-        <v>0.3800725303096771</v>
+        <v>0.3619877859783173</v>
       </c>
       <c r="E72" t="n">
-        <v>0.005155911297768354</v>
+        <v>0.004329272541463375</v>
       </c>
       <c r="F72" t="n">
-        <v>0.01114281993699648</v>
+        <v>0.007533238537451571</v>
       </c>
       <c r="G72" t="n">
-        <v>0.0002393263020874783</v>
+        <v>0.0001186290054413419</v>
       </c>
       <c r="H72" t="n">
-        <v>0.4133748766765314</v>
+        <v>0.3511777222331546</v>
       </c>
       <c r="I72" t="n">
-        <v>0.008836619225353439</v>
+        <v>0.005658720980108173</v>
       </c>
     </row>
     <row r="73">
@@ -2539,28 +2539,28 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>0.01130236461526155</v>
+        <v>0.007085064191579819</v>
       </c>
       <c r="C73" t="n">
-        <v>0.005257010219184682</v>
+        <v>0.0002704831247776746</v>
       </c>
       <c r="D73" t="n">
-        <v>0.3756292288551331</v>
+        <v>0.3669630946063995</v>
       </c>
       <c r="E73" t="n">
-        <v>0.00416720823341608</v>
+        <v>0.004979765665829181</v>
       </c>
       <c r="F73" t="n">
-        <v>0.009925412748306746</v>
+        <v>0.008906596701829216</v>
       </c>
       <c r="G73" t="n">
-        <v>0.0002682000867240769</v>
+        <v>0.0001979376714286162</v>
       </c>
       <c r="H73" t="n">
-        <v>0.386304234775789</v>
+        <v>0.358005351335734</v>
       </c>
       <c r="I73" t="n">
-        <v>0.007725691488635579</v>
+        <v>0.006918632342627494</v>
       </c>
     </row>
     <row r="74">
@@ -2568,28 +2568,28 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>0.007172167144656181</v>
+        <v>0.007115238355636597</v>
       </c>
       <c r="C74" t="n">
-        <v>0.0002973035712726414</v>
+        <v>0.0002978472095299512</v>
       </c>
       <c r="D74" t="n">
-        <v>0.3836364827575683</v>
+        <v>0.3740334101791382</v>
       </c>
       <c r="E74" t="n">
-        <v>0.004956681208252907</v>
+        <v>0.00494722414329648</v>
       </c>
       <c r="F74" t="n">
-        <v>0.006502458284416071</v>
+        <v>0.006903731508536012</v>
       </c>
       <c r="G74" t="n">
-        <v>0.0006605580946974468</v>
+        <v>0.0001678307212320981</v>
       </c>
       <c r="H74" t="n">
-        <v>0.3720092249286117</v>
+        <v>0.3569226229599211</v>
       </c>
       <c r="I74" t="n">
-        <v>0.003981854134584135</v>
+        <v>0.004951287721349063</v>
       </c>
     </row>
     <row r="75">
@@ -2597,28 +2597,28 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>0.01009940510189533</v>
+        <v>0.007179108911454677</v>
       </c>
       <c r="C75" t="n">
-        <v>0.004614051916128024</v>
+        <v>0.0002825127078816295</v>
       </c>
       <c r="D75" t="n">
-        <v>0.3727933299770355</v>
+        <v>0.386172926197052</v>
       </c>
       <c r="E75" t="n">
-        <v>0.00362138647300005</v>
+        <v>0.004965731599956751</v>
       </c>
       <c r="F75" t="n">
-        <v>0.007975720123100728</v>
+        <v>0.008126301338887039</v>
       </c>
       <c r="G75" t="n">
-        <v>0.0001340793422404312</v>
+        <v>0.0002753690800737425</v>
       </c>
       <c r="H75" t="n">
-        <v>0.3475214684417936</v>
+        <v>0.4034229429180431</v>
       </c>
       <c r="I75" t="n">
-        <v>0.006104033594407129</v>
+        <v>0.005833817538706552</v>
       </c>
     </row>
     <row r="76">
@@ -2626,28 +2626,28 @@
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>0.006757225847989321</v>
+        <v>0.0117475329978466</v>
       </c>
       <c r="C76" t="n">
-        <v>0.0003321160700395703</v>
+        <v>0.006090936708247289</v>
       </c>
       <c r="D76" t="n">
-        <v>0.3791700612697601</v>
+        <v>0.3798112775802612</v>
       </c>
       <c r="E76" t="n">
-        <v>0.004529259540915489</v>
+        <v>0.003757540145665407</v>
       </c>
       <c r="F76" t="n">
-        <v>0.009992222580116783</v>
+        <v>0.006236737296410622</v>
       </c>
       <c r="G76" t="n">
-        <v>0.000496529054647193</v>
+        <v>0.000250789818128337</v>
       </c>
       <c r="H76" t="n">
-        <v>0.3865464915925877</v>
+        <v>0.3617252437792244</v>
       </c>
       <c r="I76" t="n">
-        <v>0.007562961158985318</v>
+        <v>0.004177321304808725</v>
       </c>
     </row>
     <row r="77">
@@ -2655,28 +2655,28 @@
         <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>0.01254806717795134</v>
+        <v>0.006866594294071197</v>
       </c>
       <c r="C77" t="n">
-        <v>0.00777451138781663</v>
+        <v>0.0002892176453135908</v>
       </c>
       <c r="D77" t="n">
-        <v>0.3654071422920227</v>
+        <v>0.3871905950565338</v>
       </c>
       <c r="E77" t="n">
-        <v>0.002946519724220038</v>
+        <v>0.004641423765271902</v>
       </c>
       <c r="F77" t="n">
-        <v>0.006210133017665216</v>
+        <v>0.008780499067686218</v>
       </c>
       <c r="G77" t="n">
-        <v>0.0004340196602604068</v>
+        <v>0.0002294248068178388</v>
       </c>
       <c r="H77" t="n">
-        <v>0.3605490900700088</v>
+        <v>0.3993206801150012</v>
       </c>
       <c r="I77" t="n">
-        <v>0.003973367943156505</v>
+        <v>0.006554470762677284</v>
       </c>
     </row>
     <row r="78">
@@ -2684,28 +2684,28 @@
         <v>76</v>
       </c>
       <c r="B78" t="n">
-        <v>0.006372008220314979</v>
+        <v>0.006748205712616443</v>
       </c>
       <c r="C78" t="n">
-        <v>0.0002750241818353534</v>
+        <v>0.0002660407032370567</v>
       </c>
       <c r="D78" t="n">
-        <v>0.3729135250053406</v>
+        <v>0.3956806162872314</v>
       </c>
       <c r="E78" t="n">
-        <v>0.004232416413724422</v>
+        <v>0.00450376195988059</v>
       </c>
       <c r="F78" t="n">
-        <v>0.009702867365474122</v>
+        <v>0.006819074516067643</v>
       </c>
       <c r="G78" t="n">
-        <v>0.000247044913796632</v>
+        <v>0.0001911125208057849</v>
       </c>
       <c r="H78" t="n">
-        <v>0.3568841825535014</v>
+        <v>0.4069883188785192</v>
       </c>
       <c r="I78" t="n">
-        <v>0.007671401674872899</v>
+        <v>0.004593020457026912</v>
       </c>
     </row>
     <row r="79">
@@ -2713,28 +2713,28 @@
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>0.00655369932860136</v>
+        <v>0.01194986085939407</v>
       </c>
       <c r="C79" t="n">
-        <v>0.00029071366122365</v>
+        <v>0.006149631175888702</v>
       </c>
       <c r="D79" t="n">
-        <v>0.3845837658424378</v>
+        <v>0.3943762530899048</v>
       </c>
       <c r="E79" t="n">
-        <v>0.004340066902726889</v>
+        <v>0.003828348408997059</v>
       </c>
       <c r="F79" t="n">
-        <v>0.007698332960147648</v>
+        <v>0.006628854043332049</v>
       </c>
       <c r="G79" t="n">
-        <v>0.0001281078748048327</v>
+        <v>0.0002621673195786945</v>
       </c>
       <c r="H79" t="n">
-        <v>0.3772927359266732</v>
+        <v>0.3731849385571908</v>
       </c>
       <c r="I79" t="n">
-        <v>0.005683761341421338</v>
+        <v>0.004500762072147203</v>
       </c>
     </row>
     <row r="80">
@@ -2742,28 +2742,28 @@
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>0.006420779295444489</v>
+        <v>0.006584639558076859</v>
       </c>
       <c r="C80" t="n">
-        <v>0.000231164015153423</v>
+        <v>0.0002832186604021117</v>
       </c>
       <c r="D80" t="n">
-        <v>0.3911458119926453</v>
+        <v>0.3989703905220032</v>
       </c>
       <c r="E80" t="n">
-        <v>0.004233886247575283</v>
+        <v>0.004306569032266736</v>
       </c>
       <c r="F80" t="n">
-        <v>0.01062591402191322</v>
+        <v>0.01126227650712404</v>
       </c>
       <c r="G80" t="n">
-        <v>0.000490164263739872</v>
+        <v>0.000430084340035806</v>
       </c>
       <c r="H80" t="n">
-        <v>0.3810043068052699</v>
+        <v>0.3996307068003332</v>
       </c>
       <c r="I80" t="n">
-        <v>0.008230728241045265</v>
+        <v>0.008834038651252065</v>
       </c>
     </row>
     <row r="81">
@@ -2771,28 +2771,28 @@
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>0.006531746512651444</v>
+        <v>0.006675384088695049</v>
       </c>
       <c r="C81" t="n">
-        <v>0.0002661094696763903</v>
+        <v>0.0002418454033322632</v>
       </c>
       <c r="D81" t="n">
-        <v>0.397585360994339</v>
+        <v>0.4095233779335022</v>
       </c>
       <c r="E81" t="n">
-        <v>0.004277710266798735</v>
+        <v>0.004385921883165837</v>
       </c>
       <c r="F81" t="n">
-        <v>0.006428549479857258</v>
+        <v>0.006764044907995382</v>
       </c>
       <c r="G81" t="n">
-        <v>0.0001596246261322843</v>
+        <v>0.0003652108961611464</v>
       </c>
       <c r="H81" t="n">
-        <v>0.3939538902559638</v>
+        <v>0.3972780249947241</v>
       </c>
       <c r="I81" t="n">
-        <v>0.004299155602787681</v>
+        <v>0.004412443890596389</v>
       </c>
     </row>
     <row r="82">
@@ -2800,28 +2800,28 @@
         <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>0.006587409238696098</v>
+        <v>0.01042527387663722</v>
       </c>
       <c r="C82" t="n">
-        <v>0.0002545739750303328</v>
+        <v>0.004978245093649253</v>
       </c>
       <c r="D82" t="n">
-        <v>0.4058548760604858</v>
+        <v>0.3968225051822662</v>
       </c>
       <c r="E82" t="n">
-        <v>0.004303560886412859</v>
+        <v>0.003462916485369206</v>
       </c>
       <c r="F82" t="n">
-        <v>0.008962482760674025</v>
+        <v>0.006992772780966506</v>
       </c>
       <c r="G82" t="n">
-        <v>0.0002688342445039268</v>
+        <v>0.0001299834442805411</v>
       </c>
       <c r="H82" t="n">
-        <v>0.4783026104533458</v>
+        <v>0.3776446422958841</v>
       </c>
       <c r="I82" t="n">
-        <v>0.006302135462096329</v>
+        <v>0.004974566086166543</v>
       </c>
     </row>
     <row r="83">
@@ -2829,28 +2829,28 @@
         <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>0.009437107357919217</v>
+        <v>0.006361640383243561</v>
       </c>
       <c r="C83" t="n">
-        <v>0.004136290587843395</v>
+        <v>0.0002379596773572266</v>
       </c>
       <c r="D83" t="n">
-        <v>0.4036476549530029</v>
+        <v>0.4033000237789154</v>
       </c>
       <c r="E83" t="n">
-        <v>0.003282578435957432</v>
+        <v>0.004107180536448956</v>
       </c>
       <c r="F83" t="n">
-        <v>0.007525155651603398</v>
+        <v>0.009662251474539373</v>
       </c>
       <c r="G83" t="n">
-        <v>0.0003449470584670486</v>
+        <v>0.0003666842081827122</v>
       </c>
       <c r="H83" t="n">
-        <v>0.4024568479776771</v>
+        <v>0.3962732197623852</v>
       </c>
       <c r="I83" t="n">
-        <v>0.005167924488179058</v>
+        <v>0.007314201422631254</v>
       </c>
     </row>
     <row r="84">
@@ -2858,28 +2858,28 @@
         <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>0.008336193061947822</v>
+        <v>0.006310417168140412</v>
       </c>
       <c r="C84" t="n">
-        <v>0.00305752200461179</v>
+        <v>0.0002418984187413007</v>
       </c>
       <c r="D84" t="n">
-        <v>0.3957221261711121</v>
+        <v>0.4089775412788391</v>
       </c>
       <c r="E84" t="n">
-        <v>0.003300060650512576</v>
+        <v>0.004023631088614464</v>
       </c>
       <c r="F84" t="n">
-        <v>0.007395735163405708</v>
+        <v>0.006556259234622728</v>
       </c>
       <c r="G84" t="n">
-        <v>9.253597777246818e-05</v>
+        <v>0.0002172700151422047</v>
       </c>
       <c r="H84" t="n">
-        <v>0.3716594451831177</v>
+        <v>0.4378902727122408</v>
       </c>
       <c r="I84" t="n">
-        <v>0.005444902007636685</v>
+        <v>0.004149537848257027</v>
       </c>
     </row>
     <row r="85">
@@ -2887,28 +2887,28 @@
         <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>0.00597481056112051</v>
+        <v>0.006401490494191647</v>
       </c>
       <c r="C85" t="n">
-        <v>0.000260439062576741</v>
+        <v>0.0002314906732169911</v>
       </c>
       <c r="D85" t="n">
-        <v>0.3955785991649627</v>
+        <v>0.4225269370555877</v>
       </c>
       <c r="E85" t="n">
-        <v>0.003736478530332446</v>
+        <v>0.004057365164011717</v>
       </c>
       <c r="F85" t="n">
-        <v>0.006638432414670509</v>
+        <v>0.008770808706008396</v>
       </c>
       <c r="G85" t="n">
-        <v>0.0001573005667659735</v>
+        <v>0.0003642884732739086</v>
       </c>
       <c r="H85" t="n">
-        <v>0.3876594769449063</v>
+        <v>0.3939373860293073</v>
       </c>
       <c r="I85" t="n">
-        <v>0.004542834545268417</v>
+        <v>0.006436833352926164</v>
       </c>
     </row>
     <row r="86">
@@ -2916,28 +2916,28 @@
         <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>0.00607014486926794</v>
+        <v>0.006349431177794933</v>
       </c>
       <c r="C86" t="n">
-        <v>0.0002133660694705322</v>
+        <v>0.0002319692440740764</v>
       </c>
       <c r="D86" t="n">
-        <v>0.4045368320121765</v>
+        <v>0.434302187620163</v>
       </c>
       <c r="E86" t="n">
-        <v>0.003834094747081399</v>
+        <v>0.003945950968116522</v>
       </c>
       <c r="F86" t="n">
-        <v>0.00737592587189758</v>
+        <v>0.007027127389502856</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0002311366291596671</v>
+        <v>0.0001616035112919329</v>
       </c>
       <c r="H86" t="n">
-        <v>0.4119175644683216</v>
+        <v>0.425300077336064</v>
       </c>
       <c r="I86" t="n">
-        <v>0.005085201504416946</v>
+        <v>0.004739023544149531</v>
       </c>
     </row>
     <row r="87">
@@ -2945,28 +2945,28 @@
         <v>85</v>
       </c>
       <c r="B87" t="n">
-        <v>0.006014097784042358</v>
+        <v>0.006242050343930721</v>
       </c>
       <c r="C87" t="n">
-        <v>0.0002341150112543255</v>
+        <v>0.0002234137913072482</v>
       </c>
       <c r="D87" t="n">
-        <v>0.4129687613334656</v>
+        <v>0.4344998486118317</v>
       </c>
       <c r="E87" t="n">
-        <v>0.003715138947278261</v>
+        <v>0.00384613737398386</v>
       </c>
       <c r="F87" t="n">
-        <v>0.006509337979710705</v>
+        <v>0.006115025736111996</v>
       </c>
       <c r="G87" t="n">
-        <v>0.0002689017995878246</v>
+        <v>0.0001585883307462516</v>
       </c>
       <c r="H87" t="n">
-        <v>0.4313400379460165</v>
+        <v>0.404022128704516</v>
       </c>
       <c r="I87" t="n">
-        <v>0.004083736017711011</v>
+        <v>0.003936326837358574</v>
       </c>
     </row>
     <row r="88">
@@ -2974,28 +2974,28 @@
         <v>86</v>
       </c>
       <c r="B88" t="n">
-        <v>0.005959961331248284</v>
+        <v>0.00620437611758709</v>
       </c>
       <c r="C88" t="n">
-        <v>0.0002754791794968769</v>
+        <v>0.0002328976411186159</v>
       </c>
       <c r="D88" t="n">
-        <v>0.4163020330886841</v>
+        <v>0.4300520828762054</v>
       </c>
       <c r="E88" t="n">
-        <v>0.003602972067832947</v>
+        <v>0.003821218132257461</v>
       </c>
       <c r="F88" t="n">
-        <v>0.006322091699837666</v>
+        <v>0.007175905691037414</v>
       </c>
       <c r="G88" t="n">
-        <v>0.0001780416297095449</v>
+        <v>0.000176227141829165</v>
       </c>
       <c r="H88" t="n">
-        <v>0.4157794023901953</v>
+        <v>0.447848110562631</v>
       </c>
       <c r="I88" t="n">
-        <v>0.004065153091207</v>
+        <v>0.004760438029974894</v>
       </c>
     </row>
     <row r="89">
@@ -3003,28 +3003,28 @@
         <v>87</v>
       </c>
       <c r="B89" t="n">
-        <v>0.005542060127437114</v>
+        <v>0.00612716324236989</v>
       </c>
       <c r="C89" t="n">
-        <v>0.0002171720254151151</v>
+        <v>0.0002559107983577997</v>
       </c>
       <c r="D89" t="n">
-        <v>0.4063556631145477</v>
+        <v>0.4416574279518127</v>
       </c>
       <c r="E89" t="n">
-        <v>0.003293109844982624</v>
+        <v>0.003662965344980359</v>
       </c>
       <c r="F89" t="n">
-        <v>0.005679434403886511</v>
+        <v>0.007618164749083764</v>
       </c>
       <c r="G89" t="n">
-        <v>0.0002677398414839497</v>
+        <v>0.000386705511438753</v>
       </c>
       <c r="H89" t="n">
-        <v>0.3923368803886955</v>
+        <v>0.4848322229925999</v>
       </c>
       <c r="I89" t="n">
-        <v>0.003450010183615212</v>
+        <v>0.004807298214860005</v>
       </c>
     </row>
     <row r="90">
@@ -3032,28 +3032,28 @@
         <v>88</v>
       </c>
       <c r="B90" t="n">
-        <v>0.005792288636386395</v>
+        <v>0.0072689852283597</v>
       </c>
       <c r="C90" t="n">
-        <v>0.0002364875742774457</v>
+        <v>0.002165507658592425</v>
       </c>
       <c r="D90" t="n">
-        <v>0.4074967306041717</v>
+        <v>0.4379613857555389</v>
       </c>
       <c r="E90" t="n">
-        <v>0.003518317500963807</v>
+        <v>0.002913670657232404</v>
       </c>
       <c r="F90" t="n">
-        <v>0.009235771162401988</v>
+        <v>0.008658908670722562</v>
       </c>
       <c r="G90" t="n">
-        <v>0.0003261008235222552</v>
+        <v>0.0001785156178173456</v>
       </c>
       <c r="H90" t="n">
-        <v>0.4172476679174196</v>
+        <v>0.3914020226168983</v>
       </c>
       <c r="I90" t="n">
-        <v>0.00682343190535903</v>
+        <v>0.006523382880863221</v>
       </c>
     </row>
     <row r="91">
@@ -3061,28 +3061,28 @@
         <v>89</v>
       </c>
       <c r="B91" t="n">
-        <v>0.005759876083135605</v>
+        <v>0.005832277586430311</v>
       </c>
       <c r="C91" t="n">
-        <v>0.000222265748122707</v>
+        <v>0.0002112197225466371</v>
       </c>
       <c r="D91" t="n">
-        <v>0.4175904434642791</v>
+        <v>0.4276014323158264</v>
       </c>
       <c r="E91" t="n">
-        <v>0.003449658139079809</v>
+        <v>0.003483050690829754</v>
       </c>
       <c r="F91" t="n">
-        <v>0.006296120226097583</v>
+        <v>0.005817748908968384</v>
       </c>
       <c r="G91" t="n">
-        <v>0.000302220945435289</v>
+        <v>0.000318120345744862</v>
       </c>
       <c r="H91" t="n">
-        <v>0.4156409430990017</v>
+        <v>0.4514315486207094</v>
       </c>
       <c r="I91" t="n">
-        <v>0.003915694570913304</v>
+        <v>0.003242470968186515</v>
       </c>
     </row>
     <row r="92">
@@ -3090,28 +3090,28 @@
         <v>90</v>
       </c>
       <c r="B92" t="n">
-        <v>0.005622182466000319</v>
+        <v>0.00548817262661457</v>
       </c>
       <c r="C92" t="n">
-        <v>0.0002218189721247181</v>
+        <v>0.0002018865762799978</v>
       </c>
       <c r="D92" t="n">
-        <v>0.4188323447189331</v>
+        <v>0.4350103282318115</v>
       </c>
       <c r="E92" t="n">
-        <v>0.003306201826252043</v>
+        <v>0.003111234456628561</v>
       </c>
       <c r="F92" t="n">
-        <v>0.007306056251813207</v>
+        <v>0.01587314770883633</v>
       </c>
       <c r="G92" t="n">
-        <v>0.0002576939730778136</v>
+        <v>0.0003606735677348198</v>
       </c>
       <c r="H92" t="n">
-        <v>0.4038276982093519</v>
+        <v>0.3808525648980506</v>
       </c>
       <c r="I92" t="n">
-        <v>0.00502922384907016</v>
+        <v>0.01360821136521087</v>
       </c>
     </row>
     <row r="93">
@@ -3119,28 +3119,28 @@
         <v>91</v>
       </c>
       <c r="B93" t="n">
-        <v>0.005720057344734669</v>
+        <v>0.005992748743891716</v>
       </c>
       <c r="C93" t="n">
-        <v>0.0002370888247508556</v>
+        <v>0.001271692791272886</v>
       </c>
       <c r="D93" t="n">
-        <v>0.4251523258457184</v>
+        <v>0.4308281885547638</v>
       </c>
       <c r="E93" t="n">
-        <v>0.003357206913888454</v>
+        <v>0.002566915112286806</v>
       </c>
       <c r="F93" t="n">
-        <v>0.007090330207978677</v>
+        <v>0.008773893138931586</v>
       </c>
       <c r="G93" t="n">
-        <v>0.0001612107604819914</v>
+        <v>0.0002975944518628204</v>
       </c>
       <c r="H93" t="n">
-        <v>0.4330498256943938</v>
+        <v>0.4061470174167129</v>
       </c>
       <c r="I93" t="n">
-        <v>0.004763870333605499</v>
+        <v>0.006445563667823012</v>
       </c>
     </row>
     <row r="94">
@@ -3148,28 +3148,28 @@
         <v>92</v>
       </c>
       <c r="B94" t="n">
-        <v>0.005578384403318167</v>
+        <v>0.005385600072830916</v>
       </c>
       <c r="C94" t="n">
-        <v>0.0002498639942323789</v>
+        <v>0.0002186173798022792</v>
       </c>
       <c r="D94" t="n">
-        <v>0.4237177386417389</v>
+        <v>0.4224148859424591</v>
       </c>
       <c r="E94" t="n">
-        <v>0.003209931771725416</v>
+        <v>0.003054908332869411</v>
       </c>
       <c r="F94" t="n">
-        <v>0.009211239723540343</v>
+        <v>0.00550973919826464</v>
       </c>
       <c r="G94" t="n">
-        <v>0.0003549563011829096</v>
+        <v>0.0002920004546693199</v>
       </c>
       <c r="H94" t="n">
-        <v>0.4979409819248256</v>
+        <v>0.41591393617588</v>
       </c>
       <c r="I94" t="n">
-        <v>0.006366578584102394</v>
+        <v>0.003138169119648064</v>
       </c>
     </row>
     <row r="95">
@@ -3177,28 +3177,28 @@
         <v>93</v>
       </c>
       <c r="B95" t="n">
-        <v>0.005391786670386791</v>
+        <v>0.005161166418224573</v>
       </c>
       <c r="C95" t="n">
-        <v>0.0002018012126218528</v>
+        <v>0.000224393563291058</v>
       </c>
       <c r="D95" t="n">
-        <v>0.4262702366104126</v>
+        <v>0.4195509503097534</v>
       </c>
       <c r="E95" t="n">
-        <v>0.003058634306073189</v>
+        <v>0.002839018137127161</v>
       </c>
       <c r="F95" t="n">
-        <v>0.005795655962031146</v>
+        <v>0.007591701929243267</v>
       </c>
       <c r="G95" t="n">
-        <v>0.0003079140451463277</v>
+        <v>0.0005266212956025758</v>
       </c>
       <c r="H95" t="n">
-        <v>0.4167809180489955</v>
+        <v>0.4055449247826954</v>
       </c>
       <c r="I95" t="n">
-        <v>0.003403837359441994</v>
+        <v>0.005037355976692761</v>
       </c>
     </row>
     <row r="96">
@@ -3206,28 +3206,28 @@
         <v>94</v>
       </c>
       <c r="B96" t="n">
-        <v>0.005418943568944931</v>
+        <v>0.00504146523964405</v>
       </c>
       <c r="C96" t="n">
-        <v>0.0002310177855025977</v>
+        <v>0.000215526028862223</v>
       </c>
       <c r="D96" t="n">
-        <v>0.4277703075180054</v>
+        <v>0.4194543288650513</v>
       </c>
       <c r="E96" t="n">
-        <v>0.003049074256762862</v>
+        <v>0.002728667640149593</v>
       </c>
       <c r="F96" t="n">
-        <v>0.006961289324279613</v>
+        <v>0.005960009694524826</v>
       </c>
       <c r="G96" t="n">
-        <v>0.0001938146612309542</v>
+        <v>0.0002795424349708589</v>
       </c>
       <c r="H96" t="n">
-        <v>0.5073595141625521</v>
+        <v>0.4221923915110832</v>
       </c>
       <c r="I96" t="n">
-        <v>0.004230677183614178</v>
+        <v>0.003569505379959139</v>
       </c>
     </row>
     <row r="97">
@@ -3235,28 +3235,28 @@
         <v>95</v>
       </c>
       <c r="B97" t="n">
-        <v>0.00519309367454052</v>
+        <v>0.004794131984472275</v>
       </c>
       <c r="C97" t="n">
-        <v>0.0002046124011557549</v>
+        <v>0.0002180394433420151</v>
       </c>
       <c r="D97" t="n">
-        <v>0.4289170125102997</v>
+        <v>0.4141395960922241</v>
       </c>
       <c r="E97" t="n">
-        <v>0.002843896260753274</v>
+        <v>0.0025053945979774</v>
       </c>
       <c r="F97" t="n">
-        <v>0.006054323739470947</v>
+        <v>0.006564209979592684</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0002300293419840951</v>
+        <v>0.0002177156195916968</v>
       </c>
       <c r="H97" t="n">
-        <v>0.4376312393757103</v>
+        <v>0.4305358485588242</v>
       </c>
       <c r="I97" t="n">
-        <v>0.003636138122027427</v>
+        <v>0.004193815228941001</v>
       </c>
     </row>
     <row r="98">
@@ -3264,28 +3264,28 @@
         <v>96</v>
       </c>
       <c r="B98" t="n">
-        <v>0.005139428501546383</v>
+        <v>0.004927290092945099</v>
       </c>
       <c r="C98" t="n">
-        <v>0.0002223655865285546</v>
+        <v>0.0002161911700814962</v>
       </c>
       <c r="D98" t="n">
-        <v>0.4217920155963898</v>
+        <v>0.417099165517807</v>
       </c>
       <c r="E98" t="n">
-        <v>0.002808102911449969</v>
+        <v>0.002625603173092008</v>
       </c>
       <c r="F98" t="n">
-        <v>0.004725958431355327</v>
+        <v>0.006495618867835251</v>
       </c>
       <c r="G98" t="n">
-        <v>0.0002273805593993123</v>
+        <v>0.0002452733526503907</v>
       </c>
       <c r="H98" t="n">
-        <v>0.4250158430721009</v>
+        <v>0.3991697298060817</v>
       </c>
       <c r="I98" t="n">
-        <v>0.002373498692291183</v>
+        <v>0.004254496959850897</v>
       </c>
     </row>
     <row r="99">
@@ -3293,28 +3293,28 @@
         <v>97</v>
       </c>
       <c r="B99" t="n">
-        <v>0.004854069976270199</v>
+        <v>0.004594383007884026</v>
       </c>
       <c r="C99" t="n">
-        <v>0.0002200420509250835</v>
+        <v>0.000233944700951688</v>
       </c>
       <c r="D99" t="n">
-        <v>0.4041110252399445</v>
+        <v>0.3964169399108887</v>
       </c>
       <c r="E99" t="n">
-        <v>0.002613472865149379</v>
+        <v>0.002378353693455458</v>
       </c>
       <c r="F99" t="n">
-        <v>0.007054895933984884</v>
+        <v>0.007267488611445779</v>
       </c>
       <c r="G99" t="n">
-        <v>0.000272282057807919</v>
+        <v>0.0002651411966081909</v>
       </c>
       <c r="H99" t="n">
-        <v>0.3939104348333586</v>
+        <v>0.3877698983628832</v>
       </c>
       <c r="I99" t="n">
-        <v>0.004813061759884653</v>
+        <v>0.005063498009415571</v>
       </c>
     </row>
     <row r="100">
@@ -3322,28 +3322,28 @@
         <v>98</v>
       </c>
       <c r="B100" t="n">
-        <v>0.004827433312743902</v>
+        <v>0.004636563656508923</v>
       </c>
       <c r="C100" t="n">
-        <v>0.0002004837747700513</v>
+        <v>0.0002070082978485152</v>
       </c>
       <c r="D100" t="n">
-        <v>0.4148339009304047</v>
+        <v>0.4154215338401794</v>
       </c>
       <c r="E100" t="n">
-        <v>0.002552780085414648</v>
+        <v>0.002352447707720101</v>
       </c>
       <c r="F100" t="n">
-        <v>0.005704908681817681</v>
+        <v>0.005198611330854756</v>
       </c>
       <c r="G100" t="n">
-        <v>0.0002152720860140641</v>
+        <v>0.0001598454748181973</v>
       </c>
       <c r="H100" t="n">
-        <v>0.3993730106828263</v>
+        <v>0.383347627332899</v>
       </c>
       <c r="I100" t="n">
-        <v>0.003492771613853718</v>
+        <v>0.003122027781252638</v>
       </c>
     </row>
     <row r="101">
@@ -3351,28 +3351,28 @@
         <v>99</v>
       </c>
       <c r="B101" t="n">
-        <v>0.004676808278739453</v>
+        <v>0.004424597056895494</v>
       </c>
       <c r="C101" t="n">
-        <v>0.000220300780531019</v>
+        <v>0.0002173733287081123</v>
       </c>
       <c r="D101" t="n">
-        <v>0.4120461357059479</v>
+        <v>0.3939766111793518</v>
       </c>
       <c r="E101" t="n">
-        <v>0.002396276884302497</v>
+        <v>0.002237340749710798</v>
       </c>
       <c r="F101" t="n">
-        <v>0.00684611137002269</v>
+        <v>0.005398769649368564</v>
       </c>
       <c r="G101" t="n">
-        <v>0.0001611729159232967</v>
+        <v>0.0002839694379260657</v>
       </c>
       <c r="H101" t="n">
-        <v>0.4022798934768502</v>
+        <v>0.3804458382487492</v>
       </c>
       <c r="I101" t="n">
-        <v>0.004673539033375352</v>
+        <v>0.00321257099354272</v>
       </c>
     </row>
     <row r="102">
@@ -3380,28 +3380,28 @@
         <v>100</v>
       </c>
       <c r="B102" t="n">
-        <v>0.004558179395854473</v>
+        <v>0.004513971802651882</v>
       </c>
       <c r="C102" t="n">
-        <v>0.0002237975428346544</v>
+        <v>0.0001920954231824726</v>
       </c>
       <c r="D102" t="n">
-        <v>0.404259274646759</v>
+        <v>0.408064654794693</v>
       </c>
       <c r="E102" t="n">
-        <v>0.002313085557378829</v>
+        <v>0.002281553134575486</v>
       </c>
       <c r="F102" t="n">
-        <v>0.005891975194313009</v>
+        <v>0.006243158201147691</v>
       </c>
       <c r="G102" t="n">
-        <v>0.0004563702489868517</v>
+        <v>0.0002809018426047574</v>
       </c>
       <c r="H102" t="n">
-        <v>0.4038174973440404</v>
+        <v>0.4295359581251907</v>
       </c>
       <c r="I102" t="n">
-        <v>0.003416517521763679</v>
+        <v>0.003814576583873438</v>
       </c>
     </row>
     <row r="103">
@@ -3409,28 +3409,28 @@
         <v>101</v>
       </c>
       <c r="B103" t="n">
-        <v>0.004398775418132544</v>
+        <v>0.004289641090333461</v>
       </c>
       <c r="C103" t="n">
-        <v>0.000215642283320427</v>
+        <v>0.0002017551861740649</v>
       </c>
       <c r="D103" t="n">
-        <v>0.3986917233371735</v>
+        <v>0.3995845439414978</v>
       </c>
       <c r="E103" t="n">
-        <v>0.002189674543201924</v>
+        <v>0.002089963253550231</v>
       </c>
       <c r="F103" t="n">
-        <v>0.008048263232103666</v>
+        <v>0.005333953473966137</v>
       </c>
       <c r="G103" t="n">
-        <v>0.0002215236708927113</v>
+        <v>0.0003580231726364055</v>
       </c>
       <c r="H103" t="n">
-        <v>0.3505904541377337</v>
+        <v>0.4092798801619699</v>
       </c>
       <c r="I103" t="n">
-        <v>0.006073787433306457</v>
+        <v>0.002929530941727791</v>
       </c>
     </row>
     <row r="104">
@@ -3438,28 +3438,28 @@
         <v>102</v>
       </c>
       <c r="B104" t="n">
-        <v>0.006206808269172906</v>
+        <v>0.004307831486612558</v>
       </c>
       <c r="C104" t="n">
-        <v>0.00247796243922133</v>
+        <v>0.0002217171155940741</v>
       </c>
       <c r="D104" t="n">
-        <v>0.3928969783649445</v>
+        <v>0.4028453926162719</v>
       </c>
       <c r="E104" t="n">
-        <v>0.001764360945656896</v>
+        <v>0.00207188745123148</v>
       </c>
       <c r="F104" t="n">
-        <v>0.005797367917516589</v>
+        <v>0.006362979965281428</v>
       </c>
       <c r="G104" t="n">
-        <v>0.0001634026989458527</v>
+        <v>0.0001638488214159898</v>
       </c>
       <c r="H104" t="n">
-        <v>0.3618027927863851</v>
+        <v>0.3819606462855129</v>
       </c>
       <c r="I104" t="n">
-        <v>0.003824951359136167</v>
+        <v>0.004289327962749423</v>
       </c>
     </row>
     <row r="105">
@@ -3467,28 +3467,28 @@
         <v>103</v>
       </c>
       <c r="B105" t="n">
-        <v>0.004062692779928446</v>
+        <v>0.004879034337222576</v>
       </c>
       <c r="C105" t="n">
-        <v>0.0002029266103804111</v>
+        <v>0.001467653876995668</v>
       </c>
       <c r="D105" t="n">
-        <v>0.3832508982219696</v>
+        <v>0.379215808795929</v>
       </c>
       <c r="E105" t="n">
-        <v>0.001943511729516089</v>
+        <v>0.001515301391169429</v>
       </c>
       <c r="F105" t="n">
-        <v>0.004783572523260632</v>
+        <v>0.004882503073923837</v>
       </c>
       <c r="G105" t="n">
-        <v>0.0001963880245540015</v>
+        <v>0.0003250917852882806</v>
       </c>
       <c r="H105" t="n">
-        <v>0.3465128400041851</v>
+        <v>0.4250075698598952</v>
       </c>
       <c r="I105" t="n">
-        <v>0.002854620275933897</v>
+        <v>0.002432373531077659</v>
       </c>
     </row>
     <row r="106">
@@ -3496,28 +3496,28 @@
         <v>104</v>
       </c>
       <c r="B106" t="n">
-        <v>0.004005489618659019</v>
+        <v>0.004019562400341034</v>
       </c>
       <c r="C106" t="n">
-        <v>0.0002040225568655878</v>
+        <v>0.0001766240065945312</v>
       </c>
       <c r="D106" t="n">
-        <v>0.3698506170558929</v>
+        <v>0.3900491350955963</v>
       </c>
       <c r="E106" t="n">
-        <v>0.00195221402990818</v>
+        <v>0.001892692719250917</v>
       </c>
       <c r="F106" t="n">
-        <v>0.004763808052069211</v>
+        <v>0.005466223998302153</v>
       </c>
       <c r="G106" t="n">
-        <v>0.0002070374319359864</v>
+        <v>0.000258001713568366</v>
       </c>
       <c r="H106" t="n">
-        <v>0.3481253710248147</v>
+        <v>0.3895966879092461</v>
       </c>
       <c r="I106" t="n">
-        <v>0.002816143824216009</v>
+        <v>0.003260238895566487</v>
       </c>
     </row>
     <row r="107">
@@ -3525,28 +3525,28 @@
         <v>105</v>
       </c>
       <c r="B107" t="n">
-        <v>0.003832227320760489</v>
+        <v>0.003820815147459507</v>
       </c>
       <c r="C107" t="n">
-        <v>0.0002064903566185385</v>
+        <v>0.0002036984895803034</v>
       </c>
       <c r="D107" t="n">
-        <v>0.3598400216121674</v>
+        <v>0.3776123695220947</v>
       </c>
       <c r="E107" t="n">
-        <v>0.001826536909282207</v>
+        <v>0.001729054851263762</v>
       </c>
       <c r="F107" t="n">
-        <v>0.005608915097640788</v>
+        <v>0.004654555124144083</v>
       </c>
       <c r="G107" t="n">
-        <v>0.0003866539264745785</v>
+        <v>0.0001546488593164968</v>
       </c>
       <c r="H107" t="n">
-        <v>0.3639200372427556</v>
+        <v>0.3805136638811712</v>
       </c>
       <c r="I107" t="n">
-        <v>0.003402661081041904</v>
+        <v>0.002597337950121301</v>
       </c>
     </row>
     <row r="108">
@@ -3554,28 +3554,28 @@
         <v>106</v>
       </c>
       <c r="B108" t="n">
-        <v>0.00361642725738883</v>
+        <v>0.003796112544924021</v>
       </c>
       <c r="C108" t="n">
-        <v>0.0002274341019559652</v>
+        <v>0.0001941330467881635</v>
       </c>
       <c r="D108" t="n">
-        <v>0.3503635440196991</v>
+        <v>0.3749094352016449</v>
       </c>
       <c r="E108" t="n">
-        <v>0.001637175474569201</v>
+        <v>0.001727432377949357</v>
       </c>
       <c r="F108" t="n">
-        <v>0.006333461067841356</v>
+        <v>0.004933324655575669</v>
       </c>
       <c r="G108" t="n">
-        <v>0.0001955461305213658</v>
+        <v>0.000191532948915049</v>
       </c>
       <c r="H108" t="n">
-        <v>0.3263449607704436</v>
+        <v>0.3492368823260701</v>
       </c>
       <c r="I108" t="n">
-        <v>0.00450619017295114</v>
+        <v>0.002995607354883317</v>
       </c>
     </row>
     <row r="109">
@@ -3583,28 +3583,28 @@
         <v>107</v>
       </c>
       <c r="B109" t="n">
-        <v>0.003575435487568379</v>
+        <v>0.003681967573866248</v>
       </c>
       <c r="C109" t="n">
-        <v>0.0002016175924306735</v>
+        <v>0.0006750655231010169</v>
       </c>
       <c r="D109" t="n">
-        <v>0.3523489148921967</v>
+        <v>0.3534081648330689</v>
       </c>
       <c r="E109" t="n">
-        <v>0.001612073385998607</v>
+        <v>0.001239861265331507</v>
       </c>
       <c r="F109" t="n">
-        <v>0.004801589827619942</v>
+        <v>0.004510231969200476</v>
       </c>
       <c r="G109" t="n">
-        <v>0.0003645868269197922</v>
+        <v>0.0001356203766725046</v>
       </c>
       <c r="H109" t="n">
-        <v>0.3701613598643858</v>
+        <v>0.3899203284276835</v>
       </c>
       <c r="I109" t="n">
-        <v>0.002586196273698989</v>
+        <v>0.002425009957917314</v>
       </c>
     </row>
     <row r="110">
@@ -3612,28 +3612,28 @@
         <v>108</v>
       </c>
       <c r="B110" t="n">
-        <v>0.004969390057295561</v>
+        <v>0.003585508725225926</v>
       </c>
       <c r="C110" t="n">
-        <v>0.001911642998951487</v>
+        <v>0.0005826402286998927</v>
       </c>
       <c r="D110" t="n">
-        <v>0.3475983284416199</v>
+        <v>0.350970393491745</v>
       </c>
       <c r="E110" t="n">
-        <v>0.001319755351372063</v>
+        <v>0.001248016548983753</v>
       </c>
       <c r="F110" t="n">
-        <v>0.004178153719467401</v>
+        <v>0.004000730131180018</v>
       </c>
       <c r="G110" t="n">
-        <v>0.0001450649469904374</v>
+        <v>0.0001394246847917239</v>
       </c>
       <c r="H110" t="n">
-        <v>0.3221329209018882</v>
+        <v>0.3485871041093331</v>
       </c>
       <c r="I110" t="n">
-        <v>0.002422424254431518</v>
+        <v>0.002118369964244631</v>
       </c>
     </row>
     <row r="111">
@@ -3641,28 +3641,28 @@
         <v>109</v>
       </c>
       <c r="B111" t="n">
-        <v>0.003363452359497547</v>
+        <v>0.00342915560592711</v>
       </c>
       <c r="C111" t="n">
-        <v>0.0002027328745331615</v>
+        <v>0.0001976635144948959</v>
       </c>
       <c r="D111" t="n">
-        <v>0.3339800325012207</v>
+        <v>0.3419237055644989</v>
       </c>
       <c r="E111" t="n">
-        <v>0.001490819373846054</v>
+        <v>0.001521873584106565</v>
       </c>
       <c r="F111" t="n">
-        <v>0.004939110579962734</v>
+        <v>0.004048209020360502</v>
       </c>
       <c r="G111" t="n">
-        <v>0.0003516585918046157</v>
+        <v>0.0001281734081135218</v>
       </c>
       <c r="H111" t="n">
-        <v>0.349691789764759</v>
+        <v>0.396849364588739</v>
       </c>
       <c r="I111" t="n">
-        <v>0.002838993127264848</v>
+        <v>0.001935788798480193</v>
       </c>
     </row>
     <row r="112">
@@ -3670,28 +3670,28 @@
         <v>110</v>
       </c>
       <c r="B112" t="n">
-        <v>0.003286565446674824</v>
+        <v>0.003278266334697604</v>
       </c>
       <c r="C112" t="n">
-        <v>0.0002022758515896276</v>
+        <v>0.0001752737846551463</v>
       </c>
       <c r="D112" t="n">
-        <v>0.3362822742519379</v>
+        <v>0.3455478877124786</v>
       </c>
       <c r="E112" t="n">
-        <v>0.001402878270857036</v>
+        <v>0.001375253148812801</v>
       </c>
       <c r="F112" t="n">
-        <v>0.008019312633168055</v>
+        <v>0.003675235114903546</v>
       </c>
       <c r="G112" t="n">
-        <v>0.0003098958937187647</v>
+        <v>0.000214989023928061</v>
       </c>
       <c r="H112" t="n">
-        <v>0.2957923672969345</v>
+        <v>0.3115105097562221</v>
       </c>
       <c r="I112" t="n">
-        <v>0.006230454915590572</v>
+        <v>0.001902693623728552</v>
       </c>
     </row>
     <row r="113">
@@ -3699,28 +3699,28 @@
         <v>111</v>
       </c>
       <c r="B113" t="n">
-        <v>0.003432939292818308</v>
+        <v>0.003262753168746829</v>
       </c>
       <c r="C113" t="n">
-        <v>0.0007299973356565461</v>
+        <v>0.0001959857679978013</v>
       </c>
       <c r="D113" t="n">
-        <v>0.3169686407794952</v>
+        <v>0.3360073075580597</v>
       </c>
       <c r="E113" t="n">
-        <v>0.001118098797731102</v>
+        <v>0.001386730898931623</v>
       </c>
       <c r="F113" t="n">
-        <v>0.004274656638065521</v>
+        <v>0.005118421991500049</v>
       </c>
       <c r="G113" t="n">
-        <v>0.0002102585055038856</v>
+        <v>0.0001403453070055055</v>
       </c>
       <c r="H113" t="n">
-        <v>0.3195487288238563</v>
+        <v>0.3802267779261603</v>
       </c>
       <c r="I113" t="n">
-        <v>0.002466654487039292</v>
+        <v>0.00307694279218053</v>
       </c>
     </row>
     <row r="114">
@@ -3728,28 +3728,28 @@
         <v>112</v>
       </c>
       <c r="B114" t="n">
-        <v>0.00310937838947773</v>
+        <v>0.003184198330104351</v>
       </c>
       <c r="C114" t="n">
-        <v>0.0001991533712940291</v>
+        <v>0.0001847277103923261</v>
       </c>
       <c r="D114" t="n">
-        <v>0.318460222826004</v>
+        <v>0.3370940292510987</v>
       </c>
       <c r="E114" t="n">
-        <v>0.001317923928320408</v>
+        <v>0.001314000544160604</v>
       </c>
       <c r="F114" t="n">
-        <v>0.007441580303827662</v>
+        <v>0.004001382639172804</v>
       </c>
       <c r="G114" t="n">
-        <v>0.0003087083825846864</v>
+        <v>0.0002156084650241714</v>
       </c>
       <c r="H114" t="n">
-        <v>0.28464476977437</v>
+        <v>0.3694620567492132</v>
       </c>
       <c r="I114" t="n">
-        <v>0.005709648175076939</v>
+        <v>0.001938463986530706</v>
       </c>
     </row>
     <row r="115">
@@ -3757,28 +3757,28 @@
         <v>113</v>
       </c>
       <c r="B115" t="n">
-        <v>0.003033657508045435</v>
+        <v>0.003085521350622177</v>
       </c>
       <c r="C115" t="n">
-        <v>0.000192820446357131</v>
+        <v>0.0001872208577049896</v>
       </c>
       <c r="D115" t="n">
-        <v>0.3154116307125092</v>
+        <v>0.3328279680309296</v>
       </c>
       <c r="E115" t="n">
-        <v>0.001263778947301209</v>
+        <v>0.001234160697810352</v>
       </c>
       <c r="F115" t="n">
-        <v>0.004631220432998063</v>
+        <v>0.004574193405823062</v>
       </c>
       <c r="G115" t="n">
-        <v>0.00015952609280021</v>
+        <v>0.0001484599110722043</v>
       </c>
       <c r="H115" t="n">
-        <v>0.3050268684845375</v>
+        <v>0.3802230864461834</v>
       </c>
       <c r="I115" t="n">
-        <v>0.002946560040730102</v>
+        <v>0.002524618071809314</v>
       </c>
     </row>
     <row r="116">
@@ -3786,28 +3786,28 @@
         <v>114</v>
       </c>
       <c r="B116" t="n">
-        <v>0.002968891037940979</v>
+        <v>0.002980625254899263</v>
       </c>
       <c r="C116" t="n">
-        <v>0.0001928741661757231</v>
+        <v>0.0001873836351735517</v>
       </c>
       <c r="D116" t="n">
-        <v>0.307847413028717</v>
+        <v>0.3256909590435028</v>
       </c>
       <c r="E116" t="n">
-        <v>0.001236779816538096</v>
+        <v>0.001164786856748164</v>
       </c>
       <c r="F116" t="n">
-        <v>0.005081524643469693</v>
+        <v>0.00401390151012853</v>
       </c>
       <c r="G116" t="n">
-        <v>0.0001817404423030564</v>
+        <v>0.0002407574129955946</v>
       </c>
       <c r="H116" t="n">
-        <v>0.2921028042811943</v>
+        <v>0.3160997171911485</v>
       </c>
       <c r="I116" t="n">
-        <v>0.003439270207524713</v>
+        <v>0.002192645584192084</v>
       </c>
     </row>
     <row r="117">
@@ -3815,28 +3815,28 @@
         <v>115</v>
       </c>
       <c r="B117" t="n">
-        <v>0.0029208856023103</v>
+        <v>0.002925928274229169</v>
       </c>
       <c r="C117" t="n">
-        <v>0.0001945997707117349</v>
+        <v>0.0001997446920964867</v>
       </c>
       <c r="D117" t="n">
-        <v>0.3075315844612121</v>
+        <v>0.3161029982852936</v>
       </c>
       <c r="E117" t="n">
-        <v>0.001188627945452928</v>
+        <v>0.001145668625246733</v>
       </c>
       <c r="F117" t="n">
-        <v>0.004211076663208435</v>
+        <v>0.004299072501649184</v>
       </c>
       <c r="G117" t="n">
-        <v>0.00020154822071111</v>
+        <v>0.0001543925256689792</v>
       </c>
       <c r="H117" t="n">
-        <v>0.3282066114186074</v>
+        <v>0.3353326916169576</v>
       </c>
       <c r="I117" t="n">
-        <v>0.002368495362411218</v>
+        <v>0.002468016492537121</v>
       </c>
     </row>
     <row r="118">
@@ -3844,28 +3844,28 @@
         <v>116</v>
       </c>
       <c r="B118" t="n">
-        <v>0.002836606024131179</v>
+        <v>0.00285677932049334</v>
       </c>
       <c r="C118" t="n">
-        <v>0.0001886735297366977</v>
+        <v>0.0001895042410753667</v>
       </c>
       <c r="D118" t="n">
-        <v>0.3036114943199158</v>
+        <v>0.3152071721782684</v>
       </c>
       <c r="E118" t="n">
-        <v>0.001129875046037137</v>
+        <v>0.001091239235505462</v>
       </c>
       <c r="F118" t="n">
-        <v>0.004018123151998827</v>
+        <v>0.005485016351738917</v>
       </c>
       <c r="G118" t="n">
-        <v>0.0001579763740158699</v>
+        <v>0.0002565366418942578</v>
       </c>
       <c r="H118" t="n">
-        <v>0.3204757912512899</v>
+        <v>0.2796031214090195</v>
       </c>
       <c r="I118" t="n">
-        <v>0.002257767817838084</v>
+        <v>0.003830464169212889</v>
       </c>
     </row>
     <row r="119">
@@ -3873,28 +3873,28 @@
         <v>117</v>
       </c>
       <c r="B119" t="n">
-        <v>0.002809085574150085</v>
+        <v>0.002804665904939175</v>
       </c>
       <c r="C119" t="n">
-        <v>0.0001867166792135686</v>
+        <v>0.0001928206311510876</v>
       </c>
       <c r="D119" t="n">
-        <v>0.3031143878746033</v>
+        <v>0.3129248449649811</v>
       </c>
       <c r="E119" t="n">
-        <v>0.001106796998552978</v>
+        <v>0.001047221066810191</v>
       </c>
       <c r="F119" t="n">
-        <v>0.004181854826159665</v>
+        <v>0.003845013581143409</v>
       </c>
       <c r="G119" t="n">
-        <v>0.0002048444254432089</v>
+        <v>0.0001751991486910664</v>
       </c>
       <c r="H119" t="n">
-        <v>0.2868935301564451</v>
+        <v>0.3217639547887867</v>
       </c>
       <c r="I119" t="n">
-        <v>0.002542542802917408</v>
+        <v>0.002060994708084093</v>
       </c>
     </row>
     <row r="120">
@@ -3902,28 +3902,28 @@
         <v>118</v>
       </c>
       <c r="B120" t="n">
-        <v>0.002686575601756573</v>
+        <v>0.002742121260434389</v>
       </c>
       <c r="C120" t="n">
-        <v>0.0002051276117665693</v>
+        <v>0.0001944978868691251</v>
       </c>
       <c r="D120" t="n">
-        <v>0.2891968407325745</v>
+        <v>0.3055156697559357</v>
       </c>
       <c r="E120" t="n">
-        <v>0.0010354638318941</v>
+        <v>0.00102004507445544</v>
       </c>
       <c r="F120" t="n">
-        <v>0.003781230094831978</v>
+        <v>0.003900205844262733</v>
       </c>
       <c r="G120" t="n">
-        <v>0.0002316283628575847</v>
+        <v>0.0002316163032984917</v>
       </c>
       <c r="H120" t="n">
-        <v>0.2943498964896988</v>
+        <v>0.3276885354013272</v>
       </c>
       <c r="I120" t="n">
-        <v>0.002077852291682489</v>
+        <v>0.002030146925392611</v>
       </c>
     </row>
     <row r="121">
@@ -3931,28 +3931,28 @@
         <v>119</v>
       </c>
       <c r="B121" t="n">
-        <v>0.002569623611837625</v>
+        <v>0.002788992847368121</v>
       </c>
       <c r="C121" t="n">
-        <v>0.000195624529725872</v>
+        <v>0.0001956803382318467</v>
       </c>
       <c r="D121" t="n">
-        <v>0.2859541724510193</v>
+        <v>0.3027223091945648</v>
       </c>
       <c r="E121" t="n">
-        <v>0.0009442282643653452</v>
+        <v>0.001079701013643295</v>
       </c>
       <c r="F121" t="n">
-        <v>0.00417737937552116</v>
+        <v>0.003527779993472004</v>
       </c>
       <c r="G121" t="n">
-        <v>0.0002390731035083757</v>
+        <v>0.0001350763426762421</v>
       </c>
       <c r="H121" t="n">
-        <v>0.274632700510554</v>
+        <v>0.3295718559802648</v>
       </c>
       <c r="I121" t="n">
-        <v>0.002565142814234069</v>
+        <v>0.001744844396940477</v>
       </c>
     </row>
     <row r="122">
@@ -3960,28 +3960,28 @@
         <v>120</v>
       </c>
       <c r="B122" t="n">
-        <v>0.002552041552469134</v>
+        <v>0.002582692042991519</v>
       </c>
       <c r="C122" t="n">
-        <v>0.0002032043177187443</v>
+        <v>0.0001737109650559723</v>
       </c>
       <c r="D122" t="n">
-        <v>0.2809618196983337</v>
+        <v>0.3043875686798096</v>
       </c>
       <c r="E122" t="n">
-        <v>0.0009440281695798039</v>
+        <v>0.0008870432831794024</v>
       </c>
       <c r="F122" t="n">
-        <v>0.003922836312304022</v>
+        <v>0.003548549336227809</v>
       </c>
       <c r="G122" t="n">
-        <v>0.0002397531988311917</v>
+        <v>0.0002176835179299672</v>
       </c>
       <c r="H122" t="n">
-        <v>0.2772044495307213</v>
+        <v>0.3091800877456758</v>
       </c>
       <c r="I122" t="n">
-        <v>0.00229706095028699</v>
+        <v>0.001784965403128847</v>
       </c>
     </row>
     <row r="123">
@@ -3989,28 +3989,28 @@
         <v>121</v>
       </c>
       <c r="B123" t="n">
-        <v>0.002477040715068579</v>
+        <v>0.002508059695184231</v>
       </c>
       <c r="C123" t="n">
-        <v>0.0001941661214763299</v>
+        <v>0.0001874957078872249</v>
       </c>
       <c r="D123" t="n">
-        <v>0.2777221542301178</v>
+        <v>0.2958898703651428</v>
       </c>
       <c r="E123" t="n">
-        <v>0.0008942638395875692</v>
+        <v>0.0008411146978363395</v>
       </c>
       <c r="F123" t="n">
-        <v>0.004111691096989016</v>
+        <v>0.003945348671049512</v>
       </c>
       <c r="G123" t="n">
-        <v>0.0002593687716411916</v>
+        <v>0.0001917383341366717</v>
       </c>
       <c r="H123" t="n">
-        <v>0.2754449168173368</v>
+        <v>0.2730173941634802</v>
       </c>
       <c r="I123" t="n">
-        <v>0.002475097822344468</v>
+        <v>0.002388523356232422</v>
       </c>
     </row>
     <row r="124">
@@ -4018,28 +4018,28 @@
         <v>122</v>
       </c>
       <c r="B124" t="n">
-        <v>0.002428248527139425</v>
+        <v>0.002528122895494104</v>
       </c>
       <c r="C124" t="n">
-        <v>0.0002006906822100282</v>
+        <v>0.0001853464328972623</v>
       </c>
       <c r="D124" t="n">
-        <v>0.2718883795776367</v>
+        <v>0.2916715577201843</v>
       </c>
       <c r="E124" t="n">
-        <v>0.0008681159783117473</v>
+        <v>0.0008844187153540552</v>
       </c>
       <c r="F124" t="n">
-        <v>0.003811389225463688</v>
+        <v>0.003773498092740045</v>
       </c>
       <c r="G124" t="n">
-        <v>0.0001589171909455584</v>
+        <v>0.0002082659680488235</v>
       </c>
       <c r="H124" t="n">
-        <v>0.2893167686365168</v>
+        <v>0.2841060776811634</v>
       </c>
       <c r="I124" t="n">
-        <v>0.002205888250900423</v>
+        <v>0.002144701741802921</v>
       </c>
     </row>
     <row r="125">
@@ -4047,28 +4047,28 @@
         <v>123</v>
       </c>
       <c r="B125" t="n">
-        <v>0.002382205844461918</v>
+        <v>0.002505533180564642</v>
       </c>
       <c r="C125" t="n">
-        <v>0.0001893628823673353</v>
+        <v>0.0001850002805804834</v>
       </c>
       <c r="D125" t="n">
-        <v>0.2693806278839112</v>
+        <v>0.2891132642059326</v>
       </c>
       <c r="E125" t="n">
-        <v>0.0008459398546814919</v>
+        <v>0.0008749665881097316</v>
       </c>
       <c r="F125" t="n">
-        <v>0.003631944666171468</v>
+        <v>0.004087790235889191</v>
       </c>
       <c r="G125" t="n">
-        <v>0.0002142760730716954</v>
+        <v>0.0001916770421638538</v>
       </c>
       <c r="H125" t="n">
-        <v>0.2571977799421034</v>
+        <v>0.2751169772210362</v>
       </c>
       <c r="I125" t="n">
-        <v>0.002131679710137489</v>
+        <v>0.002520528355579926</v>
       </c>
     </row>
     <row r="126">
@@ -4076,28 +4076,28 @@
         <v>124</v>
       </c>
       <c r="B126" t="n">
-        <v>0.002380362125635147</v>
+        <v>0.002406318188995123</v>
       </c>
       <c r="C126" t="n">
-        <v>0.0001872593555534258</v>
+        <v>0.0001860847528427839</v>
       </c>
       <c r="D126" t="n">
-        <v>0.2675971659812927</v>
+        <v>0.2833536572170258</v>
       </c>
       <c r="E126" t="n">
-        <v>0.0008551169689521193</v>
+        <v>0.0008034651973843574</v>
       </c>
       <c r="F126" t="n">
-        <v>0.003786829764701025</v>
+        <v>0.00398565239715124</v>
       </c>
       <c r="G126" t="n">
-        <v>0.0001482620481339011</v>
+        <v>0.0002480462424781441</v>
       </c>
       <c r="H126" t="n">
-        <v>0.2939097036350804</v>
+        <v>0.2832861539512435</v>
       </c>
       <c r="I126" t="n">
-        <v>0.002169019201372372</v>
+        <v>0.002321175355965585</v>
       </c>
     </row>
     <row r="127">
@@ -4105,28 +4105,28 @@
         <v>125</v>
       </c>
       <c r="B127" t="n">
-        <v>0.002274952660262585</v>
+        <v>0.002367890428364277</v>
       </c>
       <c r="C127" t="n">
-        <v>0.0001933660555221141</v>
+        <v>0.0001853119558561593</v>
       </c>
       <c r="D127" t="n">
-        <v>0.2651685304403305</v>
+        <v>0.2813305552825928</v>
       </c>
       <c r="E127" t="n">
-        <v>0.0007557439687326551</v>
+        <v>0.0007759257196858525</v>
       </c>
       <c r="F127" t="n">
-        <v>0.003672435183068935</v>
+        <v>0.003589770123423313</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0002022638187721314</v>
+        <v>0.0001604868598046088</v>
       </c>
       <c r="H127" t="n">
-        <v>0.278121018242486</v>
+        <v>0.2826222141026284</v>
       </c>
       <c r="I127" t="n">
-        <v>0.00207956628257114</v>
+        <v>0.002016172223826217</v>
       </c>
     </row>
     <row r="128">
@@ -4134,28 +4134,28 @@
         <v>126</v>
       </c>
       <c r="B128" t="n">
-        <v>0.002251164650410414</v>
+        <v>0.002278579451471567</v>
       </c>
       <c r="C128" t="n">
-        <v>0.0001902818800844252</v>
+        <v>0.0001889295768681914</v>
       </c>
       <c r="D128" t="n">
-        <v>0.262863616815567</v>
+        <v>0.274116225730896</v>
       </c>
       <c r="E128" t="n">
-        <v>0.0007465647140257061</v>
+        <v>0.0007190687797106803</v>
       </c>
       <c r="F128" t="n">
-        <v>0.004457246116278952</v>
+        <v>0.003672241171606213</v>
       </c>
       <c r="G128" t="n">
-        <v>0.0002093715059237105</v>
+        <v>0.0001795980691807998</v>
       </c>
       <c r="H128" t="n">
-        <v>0.2435355758453077</v>
+        <v>0.266422724562407</v>
       </c>
       <c r="I128" t="n">
-        <v>0.003030196713970376</v>
+        <v>0.002160529510116548</v>
       </c>
     </row>
     <row r="129">
@@ -4163,28 +4163,28 @@
         <v>127</v>
       </c>
       <c r="B129" t="n">
-        <v>0.002205959901049733</v>
+        <v>0.002229558469608426</v>
       </c>
       <c r="C129" t="n">
-        <v>0.0001885984297981486</v>
+        <v>0.0001918034290615469</v>
       </c>
       <c r="D129" t="n">
-        <v>0.2588528165493011</v>
+        <v>0.2673437436885834</v>
       </c>
       <c r="E129" t="n">
-        <v>0.0007230974362380803</v>
+        <v>0.0007010363360717893</v>
       </c>
       <c r="F129" t="n">
-        <v>0.003695910581969466</v>
+        <v>0.004326986536371475</v>
       </c>
       <c r="G129" t="n">
-        <v>0.0001979325350269912</v>
+        <v>0.0001805247908234399</v>
       </c>
       <c r="H129" t="n">
-        <v>0.2442494832351196</v>
+        <v>0.2631629669841312</v>
       </c>
       <c r="I129" t="n">
-        <v>0.002276730630759508</v>
+        <v>0.002830646901815327</v>
       </c>
     </row>
     <row r="130">
@@ -4192,28 +4192,28 @@
         <v>128</v>
       </c>
       <c r="B130" t="n">
-        <v>0.002145427782252431</v>
+        <v>0.002212909524410963</v>
       </c>
       <c r="C130" t="n">
-        <v>0.0001936442039730027</v>
+        <v>0.0001794975242558867</v>
       </c>
       <c r="D130" t="n">
-        <v>0.2539977362289429</v>
+        <v>0.2677124106035232</v>
       </c>
       <c r="E130" t="n">
-        <v>0.0006817949202172458</v>
+        <v>0.0006948499702587724</v>
       </c>
       <c r="F130" t="n">
-        <v>0.003538693209888252</v>
+        <v>0.003569066428517099</v>
       </c>
       <c r="G130" t="n">
-        <v>0.0002140418333630039</v>
+        <v>0.0001802575470633549</v>
       </c>
       <c r="H130" t="n">
-        <v>0.2414121245064121</v>
+        <v>0.2770009655898003</v>
       </c>
       <c r="I130" t="n">
-        <v>0.00211759072871268</v>
+        <v>0.002003804101285085</v>
       </c>
     </row>
     <row r="131">
@@ -4221,28 +4221,28 @@
         <v>129</v>
       </c>
       <c r="B131" t="n">
-        <v>0.002097844501718879</v>
+        <v>0.002149638507172465</v>
       </c>
       <c r="C131" t="n">
-        <v>0.0001913380782622844</v>
+        <v>0.0001802087225345895</v>
       </c>
       <c r="D131" t="n">
-        <v>0.249676489988327</v>
+        <v>0.2660137482357025</v>
       </c>
       <c r="E131" t="n">
-        <v>0.0006581240151040256</v>
+        <v>0.000639361056830734</v>
       </c>
       <c r="F131" t="n">
-        <v>0.004292991395863487</v>
+        <v>0.00377962966928134</v>
       </c>
       <c r="G131" t="n">
-        <v>0.000239508635049031</v>
+        <v>0.0002171567659857371</v>
       </c>
       <c r="H131" t="n">
-        <v>0.2301594373384463</v>
+        <v>0.249589172653234</v>
       </c>
       <c r="I131" t="n">
-        <v>0.002902685554020508</v>
+        <v>0.002314527066026436</v>
       </c>
     </row>
     <row r="132">
@@ -4250,28 +4250,28 @@
         <v>130</v>
       </c>
       <c r="B132" t="n">
-        <v>0.002073852465413511</v>
+        <v>0.002138953747496009</v>
       </c>
       <c r="C132" t="n">
-        <v>0.0001924763446692377</v>
+        <v>0.0001861132218213752</v>
       </c>
       <c r="D132" t="n">
-        <v>0.2457611491584778</v>
+        <v>0.2593394840660095</v>
       </c>
       <c r="E132" t="n">
-        <v>0.0006525703964754939</v>
+        <v>0.0006561431561671197</v>
       </c>
       <c r="F132" t="n">
-        <v>0.003425808826728829</v>
+        <v>0.003617909065862513</v>
       </c>
       <c r="G132" t="n">
-        <v>0.0001973454566753346</v>
+        <v>0.0001503915072199972</v>
       </c>
       <c r="H132" t="n">
-        <v>0.2350467988649356</v>
+        <v>0.2853984964866234</v>
       </c>
       <c r="I132" t="n">
-        <v>0.00205322937905442</v>
+        <v>0.002040525096116153</v>
       </c>
     </row>
     <row r="133">
@@ -4279,28 +4279,28 @@
         <v>131</v>
       </c>
       <c r="B133" t="n">
-        <v>0.002048922405064106</v>
+        <v>0.002081318688496947</v>
       </c>
       <c r="C133" t="n">
-        <v>0.0001893858482204378</v>
+        <v>0.000181507184702903</v>
       </c>
       <c r="D133" t="n">
-        <v>0.2440920597953797</v>
+        <v>0.2587538403511047</v>
       </c>
       <c r="E133" t="n">
-        <v>0.0006390762879475952</v>
+        <v>0.0006060423294752836</v>
       </c>
       <c r="F133" t="n">
-        <v>0.003738269064040645</v>
+        <v>0.003245867478188741</v>
       </c>
       <c r="G133" t="n">
-        <v>0.0001765715196923555</v>
+        <v>0.0001799868697890796</v>
       </c>
       <c r="H133" t="n">
-        <v>0.2436228156089783</v>
+        <v>0.2682629088457024</v>
       </c>
       <c r="I133" t="n">
-        <v>0.002343583513859532</v>
+        <v>0.001724566117226834</v>
       </c>
     </row>
     <row r="134">
@@ -4308,28 +4308,28 @@
         <v>132</v>
       </c>
       <c r="B134" t="n">
-        <v>0.001987287518180907</v>
+        <v>0.002029111183553934</v>
       </c>
       <c r="C134" t="n">
-        <v>0.0001902803227007389</v>
+        <v>0.0001864956149458885</v>
       </c>
       <c r="D134" t="n">
-        <v>0.2413131402606964</v>
+        <v>0.2552549568824768</v>
       </c>
       <c r="E134" t="n">
-        <v>0.0005904415243174881</v>
+        <v>0.0005663408086188138</v>
       </c>
       <c r="F134" t="n">
-        <v>0.003169653562807628</v>
+        <v>0.00397483643536345</v>
       </c>
       <c r="G134" t="n">
-        <v>0.0001822519743303065</v>
+        <v>0.0001488378372977352</v>
       </c>
       <c r="H134" t="n">
-        <v>0.2345910878603455</v>
+        <v>0.2738175285893202</v>
       </c>
       <c r="I134" t="n">
-        <v>0.001814446183214751</v>
+        <v>0.002456910965955082</v>
       </c>
     </row>
     <row r="135">
@@ -4337,28 +4337,28 @@
         <v>133</v>
       </c>
       <c r="B135" t="n">
-        <v>0.001943177119851112</v>
+        <v>0.002025562911689282</v>
       </c>
       <c r="C135" t="n">
-        <v>0.0001916196555774659</v>
+        <v>0.000184984187150374</v>
       </c>
       <c r="D135" t="n">
-        <v>0.2371973859643936</v>
+        <v>0.2520564913330078</v>
       </c>
       <c r="E135" t="n">
-        <v>0.0005655705427452922</v>
+        <v>0.0005802962820418179</v>
       </c>
       <c r="F135" t="n">
-        <v>0.003856868725178876</v>
+        <v>0.003507559719582074</v>
       </c>
       <c r="G135" t="n">
-        <v>0.0002097716344815571</v>
+        <v>0.0001887456621706173</v>
       </c>
       <c r="H135" t="n">
-        <v>0.220397733427572</v>
+        <v>0.2443797661760309</v>
       </c>
       <c r="I135" t="n">
-        <v>0.002545108429109146</v>
+        <v>0.00209691526132771</v>
       </c>
     </row>
     <row r="136">
@@ -4366,28 +4366,28 @@
         <v>134</v>
       </c>
       <c r="B136" t="n">
-        <v>0.001912712977491319</v>
+        <v>0.001979316491544247</v>
       </c>
       <c r="C136" t="n">
-        <v>0.0001913114076759666</v>
+        <v>0.0001828440698934719</v>
       </c>
       <c r="D136" t="n">
-        <v>0.2349838671150208</v>
+        <v>0.2492477273483276</v>
       </c>
       <c r="E136" t="n">
-        <v>0.0005464822559971362</v>
+        <v>0.0005502338123917579</v>
       </c>
       <c r="F136" t="n">
-        <v>0.003311935469939649</v>
+        <v>0.003181875269513632</v>
       </c>
       <c r="G136" t="n">
-        <v>0.0002189335728747478</v>
+        <v>0.000183426923411754</v>
       </c>
       <c r="H136" t="n">
-        <v>0.2248598303277574</v>
+        <v>0.241030444198487</v>
       </c>
       <c r="I136" t="n">
-        <v>0.001968702781128091</v>
+        <v>0.0017932961833759</v>
       </c>
     </row>
     <row r="137">
@@ -4395,28 +4395,28 @@
         <v>135</v>
       </c>
       <c r="B137" t="n">
-        <v>0.001879837794795632</v>
+        <v>0.001935504269376397</v>
       </c>
       <c r="C137" t="n">
-        <v>0.000188108375637792</v>
+        <v>0.0001846121277948841</v>
       </c>
       <c r="D137" t="n">
-        <v>0.230637568698883</v>
+        <v>0.2452891908941269</v>
       </c>
       <c r="E137" t="n">
-        <v>0.0005385415992103517</v>
+        <v>0.0005244461957737804</v>
       </c>
       <c r="F137" t="n">
-        <v>0.003050061837537594</v>
+        <v>0.003137602880825008</v>
       </c>
       <c r="G137" t="n">
-        <v>0.0002139813778722555</v>
+        <v>0.0001729908898844251</v>
       </c>
       <c r="H137" t="n">
-        <v>0.2230318210642256</v>
+        <v>0.2560452246452039</v>
       </c>
       <c r="I137" t="n">
-        <v>0.001720921373842542</v>
+        <v>0.001684385872610083</v>
       </c>
     </row>
     <row r="138">
@@ -4424,28 +4424,28 @@
         <v>136</v>
       </c>
       <c r="B138" t="n">
-        <v>0.001840287525296211</v>
+        <v>0.001900679159075022</v>
       </c>
       <c r="C138" t="n">
-        <v>0.0001907389734080061</v>
+        <v>0.0001798348639085889</v>
       </c>
       <c r="D138" t="n">
-        <v>0.2287447709331512</v>
+        <v>0.2453925614843369</v>
       </c>
       <c r="E138" t="n">
-        <v>0.0005058247329257429</v>
+        <v>0.0004938815209306777</v>
       </c>
       <c r="F138" t="n">
-        <v>0.003640915310560296</v>
+        <v>0.00361535095766211</v>
       </c>
       <c r="G138" t="n">
-        <v>0.0001746147317493936</v>
+        <v>0.0001691947557226957</v>
       </c>
       <c r="H138" t="n">
-        <v>0.2449957954786341</v>
+        <v>0.2486014152817781</v>
       </c>
       <c r="I138" t="n">
-        <v>0.002241321594240129</v>
+        <v>0.00220314914125153</v>
       </c>
     </row>
     <row r="139">
@@ -4453,28 +4453,28 @@
         <v>137</v>
       </c>
       <c r="B139" t="n">
-        <v>0.001793340487599373</v>
+        <v>0.001873713387876749</v>
       </c>
       <c r="C139" t="n">
-        <v>0.000191896440461278</v>
+        <v>0.0001860211678892374</v>
       </c>
       <c r="D139" t="n">
-        <v>0.2241630438613892</v>
+        <v>0.2390368322124481</v>
       </c>
       <c r="E139" t="n">
-        <v>0.0004806288397554308</v>
+        <v>0.0004925080877654255</v>
       </c>
       <c r="F139" t="n">
-        <v>0.003499479657510025</v>
+        <v>0.003454082323022515</v>
       </c>
       <c r="G139" t="n">
-        <v>0.0001815372830648796</v>
+        <v>0.0002143148544461346</v>
       </c>
       <c r="H139" t="n">
-        <v>0.220012861004078</v>
+        <v>0.232117623640118</v>
       </c>
       <c r="I139" t="n">
-        <v>0.002217878081940637</v>
+        <v>0.002079179366688938</v>
       </c>
     </row>
     <row r="140">
@@ -4482,28 +4482,28 @@
         <v>138</v>
       </c>
       <c r="B140" t="n">
-        <v>0.001761620531238616</v>
+        <v>0.001830790981382131</v>
       </c>
       <c r="C140" t="n">
-        <v>0.0001914237676570192</v>
+        <v>0.0001871972282789647</v>
       </c>
       <c r="D140" t="n">
-        <v>0.2214478074836731</v>
+        <v>0.2346199057893753</v>
       </c>
       <c r="E140" t="n">
-        <v>0.000462957749562338</v>
+        <v>0.0004704942408502102</v>
       </c>
       <c r="F140" t="n">
-        <v>0.003358407904915086</v>
+        <v>0.003129665821617496</v>
       </c>
       <c r="G140" t="n">
-        <v>0.0001938168826460957</v>
+        <v>0.0001877126060836442</v>
       </c>
       <c r="H140" t="n">
-        <v>0.2153337673660592</v>
+        <v>0.2290993712212872</v>
       </c>
       <c r="I140" t="n">
-        <v>0.002087922244960196</v>
+        <v>0.001796456414356913</v>
       </c>
     </row>
     <row r="141">
@@ -4511,28 +4511,28 @@
         <v>139</v>
       </c>
       <c r="B141" t="n">
-        <v>0.00171657507584244</v>
+        <v>0.001821356427833438</v>
       </c>
       <c r="C141" t="n">
-        <v>0.0001956629210971296</v>
+        <v>0.0001858302196320146</v>
       </c>
       <c r="D141" t="n">
-        <v>0.2159333045549393</v>
+        <v>0.2331584167509079</v>
       </c>
       <c r="E141" t="n">
-        <v>0.000441245644679293</v>
+        <v>0.0004697341682426632</v>
       </c>
       <c r="F141" t="n">
-        <v>0.00334160688150899</v>
+        <v>0.003162468692248301</v>
       </c>
       <c r="G141" t="n">
-        <v>0.0002069683025874422</v>
+        <v>0.0001559109124355018</v>
       </c>
       <c r="H141" t="n">
-        <v>0.2130422461110655</v>
+        <v>0.2447308385790269</v>
       </c>
       <c r="I141" t="n">
-        <v>0.002069427376266624</v>
+        <v>0.00178290363374587</v>
       </c>
     </row>
     <row r="142">
@@ -4540,28 +4540,28 @@
         <v>140</v>
       </c>
       <c r="B142" t="n">
-        <v>0.00168070122089237</v>
+        <v>0.001779359949506819</v>
       </c>
       <c r="C142" t="n">
-        <v>0.0001945175581080839</v>
+        <v>0.0001831323355324566</v>
       </c>
       <c r="D142" t="n">
-        <v>0.211959212562561</v>
+        <v>0.2308709399833679</v>
       </c>
       <c r="E142" t="n">
-        <v>0.0004263876212071627</v>
+        <v>0.0004418729210225865</v>
       </c>
       <c r="F142" t="n">
-        <v>0.003146481662137862</v>
+        <v>0.003029896703535056</v>
       </c>
       <c r="G142" t="n">
-        <v>0.0002049898144819046</v>
+        <v>0.0001666234037886354</v>
       </c>
       <c r="H142" t="n">
-        <v>0.2074348019950736</v>
+        <v>0.2322615252029254</v>
       </c>
       <c r="I142" t="n">
-        <v>0.001904317839268662</v>
+        <v>0.001701965674387251</v>
       </c>
     </row>
     <row r="143">
@@ -4569,28 +4569,28 @@
         <v>141</v>
       </c>
       <c r="B143" t="n">
-        <v>0.001652855472803116</v>
+        <v>0.001733379944950342</v>
       </c>
       <c r="C143" t="n">
-        <v>0.0001932163633564487</v>
+        <v>0.0001849192496938631</v>
       </c>
       <c r="D143" t="n">
-        <v>0.2098479572076797</v>
+        <v>0.2272257350568771</v>
       </c>
       <c r="E143" t="n">
-        <v>0.0004103993483148515</v>
+        <v>0.0004123320486843586</v>
       </c>
       <c r="F143" t="n">
-        <v>0.003303459793949108</v>
+        <v>0.003027463965710453</v>
       </c>
       <c r="G143" t="n">
-        <v>0.0001964217900470595</v>
+        <v>0.000193171132101258</v>
       </c>
       <c r="H143" t="n">
-        <v>0.1999487702142551</v>
+        <v>0.2370374393550646</v>
       </c>
       <c r="I143" t="n">
-        <v>0.002107294178590616</v>
+        <v>0.001649105639089063</v>
       </c>
     </row>
     <row r="144">
@@ -4598,28 +4598,28 @@
         <v>142</v>
       </c>
       <c r="B144" t="n">
-        <v>0.001626700262412429</v>
+        <v>0.001708363584086299</v>
       </c>
       <c r="C144" t="n">
-        <v>0.0001899434741521254</v>
+        <v>0.000185394379674457</v>
       </c>
       <c r="D144" t="n">
-        <v>0.2078576446828842</v>
+        <v>0.2256432500925064</v>
       </c>
       <c r="E144" t="n">
-        <v>0.0003974685824904591</v>
+        <v>0.0003947529871277511</v>
       </c>
       <c r="F144" t="n">
-        <v>0.003065749630787779</v>
+        <v>0.00296010597245874</v>
       </c>
       <c r="G144" t="n">
-        <v>0.0001969771430680307</v>
+        <v>0.0001913484476611541</v>
       </c>
       <c r="H144" t="n">
-        <v>0.2024163447313169</v>
+        <v>0.2174057741373243</v>
       </c>
       <c r="I144" t="n">
-        <v>0.001856690784931475</v>
+        <v>0.001681728646999338</v>
       </c>
     </row>
     <row r="145">
@@ -4627,28 +4627,28 @@
         <v>143</v>
       </c>
       <c r="B145" t="n">
-        <v>0.001596200342766941</v>
+        <v>0.001676802398189902</v>
       </c>
       <c r="C145" t="n">
-        <v>0.0001913270433954895</v>
+        <v>0.0001840153901511803</v>
       </c>
       <c r="D145" t="n">
-        <v>0.2052546759147644</v>
+        <v>0.2217932047319412</v>
       </c>
       <c r="E145" t="n">
-        <v>0.0003785999447330832</v>
+        <v>0.0003838210223652423</v>
       </c>
       <c r="F145" t="n">
-        <v>0.002918204769300719</v>
+        <v>0.002963389349132047</v>
       </c>
       <c r="G145" t="n">
-        <v>0.0002005072587228959</v>
+        <v>0.0001741899043877288</v>
       </c>
       <c r="H145" t="n">
-        <v>0.2001083702636582</v>
+        <v>0.2278517585642769</v>
       </c>
       <c r="I145" t="n">
-        <v>0.001717155654519663</v>
+        <v>0.001649940675139719</v>
       </c>
     </row>
     <row r="146">
@@ -4656,28 +4656,28 @@
         <v>144</v>
       </c>
       <c r="B146" t="n">
-        <v>0.00157075402302295</v>
+        <v>0.001628780058771372</v>
       </c>
       <c r="C146" t="n">
-        <v>0.0001880422606607899</v>
+        <v>0.0001842959546288476</v>
       </c>
       <c r="D146" t="n">
-        <v>0.2039810313234329</v>
+        <v>0.2183196369018555</v>
       </c>
       <c r="E146" t="n">
-        <v>0.0003628066134732217</v>
+        <v>0.000352885934907943</v>
       </c>
       <c r="F146" t="n">
-        <v>0.003401880508735411</v>
+        <v>0.003627309564358234</v>
       </c>
       <c r="G146" t="n">
-        <v>0.0001759046104909065</v>
+        <v>0.0001836437128796083</v>
       </c>
       <c r="H146" t="n">
-        <v>0.2111388963315071</v>
+        <v>0.2175372575031408</v>
       </c>
       <c r="I146" t="n">
-        <v>0.002170281422508312</v>
+        <v>0.002355979542608022</v>
       </c>
     </row>
     <row r="147">
@@ -4685,28 +4685,28 @@
         <v>145</v>
       </c>
       <c r="B147" t="n">
-        <v>0.001543449325025082</v>
+        <v>0.00161916970718652</v>
       </c>
       <c r="C147" t="n">
-        <v>0.0001897921180101112</v>
+        <v>0.0001855920907976106</v>
       </c>
       <c r="D147" t="n">
-        <v>0.2025001835775375</v>
+        <v>0.2160112706308365</v>
       </c>
       <c r="E147" t="n">
-        <v>0.000341156298706308</v>
+        <v>0.000353521271398291</v>
       </c>
       <c r="F147" t="n">
-        <v>0.003313475666114936</v>
+        <v>0.002959326052898465</v>
       </c>
       <c r="G147" t="n">
-        <v>0.0001983715182895351</v>
+        <v>0.0001843000973601784</v>
       </c>
       <c r="H147" t="n">
-        <v>0.1988382519224923</v>
+        <v>0.2148576560660249</v>
       </c>
       <c r="I147" t="n">
-        <v>0.00212091296801851</v>
+        <v>0.001700737711359697</v>
       </c>
     </row>
     <row r="148">
@@ -4714,28 +4714,28 @@
         <v>146</v>
       </c>
       <c r="B148" t="n">
-        <v>0.001523404421687126</v>
+        <v>0.001590588296800852</v>
       </c>
       <c r="C148" t="n">
-        <v>0.0001899171167528257</v>
+        <v>0.0001861323318285868</v>
       </c>
       <c r="D148" t="n">
-        <v>0.1990922994165421</v>
+        <v>0.2134737090797424</v>
       </c>
       <c r="E148" t="n">
-        <v>0.0003380258213505149</v>
+        <v>0.0003370874494779855</v>
       </c>
       <c r="F148" t="n">
-        <v>0.002945498617739701</v>
+        <v>0.003045664624406745</v>
       </c>
       <c r="G148" t="n">
-        <v>0.0001926259160213488</v>
+        <v>0.0001908376311162049</v>
       </c>
       <c r="H148" t="n">
-        <v>0.2036462276648931</v>
+        <v>0.2095041766048061</v>
       </c>
       <c r="I148" t="n">
-        <v>0.001734641545473448</v>
+        <v>0.001807306158123918</v>
       </c>
     </row>
     <row r="149">
@@ -4743,28 +4743,28 @@
         <v>147</v>
       </c>
       <c r="B149" t="n">
-        <v>0.001501452365934849</v>
+        <v>0.001565303563408554</v>
       </c>
       <c r="C149" t="n">
-        <v>0.0001903841765103862</v>
+        <v>0.0001865813995013014</v>
       </c>
       <c r="D149" t="n">
-        <v>0.1972323651885986</v>
+        <v>0.2110089990701675</v>
       </c>
       <c r="E149" t="n">
-        <v>0.0003249063891097903</v>
+        <v>0.0003236771803256124</v>
       </c>
       <c r="F149" t="n">
-        <v>0.003092593773865243</v>
+        <v>0.003146874854131488</v>
       </c>
       <c r="G149" t="n">
-        <v>0.0001895058131615326</v>
+        <v>0.0001843099836655095</v>
       </c>
       <c r="H149" t="n">
-        <v>0.1955162132009985</v>
+        <v>0.2073165548849261</v>
       </c>
       <c r="I149" t="n">
-        <v>0.001925506903470887</v>
+        <v>0.001925982157403503</v>
       </c>
     </row>
     <row r="150">
@@ -4772,28 +4772,28 @@
         <v>148</v>
       </c>
       <c r="B150" t="n">
-        <v>0.001474258404158056</v>
+        <v>0.001532082826554775</v>
       </c>
       <c r="C150" t="n">
-        <v>0.0001904115297254175</v>
+        <v>0.0001856818969799206</v>
       </c>
       <c r="D150" t="n">
-        <v>0.1953329288578033</v>
+        <v>0.2074843972139359</v>
       </c>
       <c r="E150" t="n">
-        <v>0.0003071822418738157</v>
+        <v>0.0003089789773765951</v>
       </c>
       <c r="F150" t="n">
-        <v>0.003327189804591105</v>
+        <v>0.002942317939115776</v>
       </c>
       <c r="G150" t="n">
-        <v>0.000192501022712879</v>
+        <v>0.0002037788597433137</v>
       </c>
       <c r="H150" t="n">
-        <v>0.1885892573324736</v>
+        <v>0.2031301508330988</v>
       </c>
       <c r="I150" t="n">
-        <v>0.002191742464480694</v>
+        <v>0.001722888357665384</v>
       </c>
     </row>
     <row r="151">
@@ -4801,28 +4801,28 @@
         <v>149</v>
       </c>
       <c r="B151" t="n">
-        <v>0.001456260952740908</v>
+        <v>0.001512426717236638</v>
       </c>
       <c r="C151" t="n">
-        <v>0.000189720665386878</v>
+        <v>0.0001857299667447805</v>
       </c>
       <c r="D151" t="n">
-        <v>0.193491363612175</v>
+        <v>0.2057464736185074</v>
       </c>
       <c r="E151" t="n">
-        <v>0.0002990835018865764</v>
+        <v>0.000297964404899627</v>
       </c>
       <c r="F151" t="n">
-        <v>0.003252656740086308</v>
+        <v>0.00335736653761449</v>
       </c>
       <c r="G151" t="n">
-        <v>0.0001880610638300373</v>
+        <v>0.0001971778287189568</v>
       </c>
       <c r="H151" t="n">
-        <v>0.1915764977259115</v>
+        <v>0.2002892016217137</v>
       </c>
       <c r="I151" t="n">
-        <v>0.002106713219978778</v>
+        <v>0.002158742812211469</v>
       </c>
     </row>
     <row r="152">
@@ -4830,28 +4830,28 @@
         <v>150</v>
       </c>
       <c r="B152" t="n">
-        <v>0.001425097421035171</v>
+        <v>0.001490293523177505</v>
       </c>
       <c r="C152" t="n">
-        <v>0.000190230729945004</v>
+        <v>0.0001846191483503208</v>
       </c>
       <c r="D152" t="n">
-        <v>0.1909645058031082</v>
+        <v>0.2038776588058472</v>
       </c>
       <c r="E152" t="n">
-        <v>0.0002800442043896764</v>
+        <v>0.0002862861201511696</v>
       </c>
       <c r="F152" t="n">
-        <v>0.002882384518419695</v>
+        <v>0.002880335411430621</v>
       </c>
       <c r="G152" t="n">
-        <v>0.000184102616900332</v>
+        <v>0.0001945758192466882</v>
       </c>
       <c r="H152" t="n">
-        <v>0.1912468098077261</v>
+        <v>0.2013191414355843</v>
       </c>
       <c r="I152" t="n">
-        <v>0.001742047900394772</v>
+        <v>0.001679163921341835</v>
       </c>
     </row>
     <row r="153">
@@ -4859,28 +4859,28 @@
         <v>151</v>
       </c>
       <c r="B153" t="n">
-        <v>0.00141569473913312</v>
+        <v>0.001478691934503615</v>
       </c>
       <c r="C153" t="n">
-        <v>0.000190037046642974</v>
+        <v>0.0001848850297154859</v>
       </c>
       <c r="D153" t="n">
-        <v>0.1893198398246765</v>
+        <v>0.2022535441646576</v>
       </c>
       <c r="E153" t="n">
-        <v>0.0002790585165210068</v>
+        <v>0.0002825392039492726</v>
       </c>
       <c r="F153" t="n">
-        <v>0.002809506828257082</v>
+        <v>0.003052528170142536</v>
       </c>
       <c r="G153" t="n">
-        <v>0.0001944816992669419</v>
+        <v>0.0001799795481075911</v>
       </c>
       <c r="H153" t="n">
-        <v>0.1901890987653717</v>
+        <v>0.2031138736836089</v>
       </c>
       <c r="I153" t="n">
-        <v>0.001664079656941455</v>
+        <v>0.001856979282502978</v>
       </c>
     </row>
     <row r="154">
@@ -4888,28 +4888,28 @@
         <v>152</v>
       </c>
       <c r="B154" t="n">
-        <v>0.001392757603108883</v>
+        <v>0.001452445312410593</v>
       </c>
       <c r="C154" t="n">
-        <v>0.0001891073995390907</v>
+        <v>0.0001853345626937225</v>
       </c>
       <c r="D154" t="n">
-        <v>0.1879501434421539</v>
+        <v>0.1998514995422363</v>
       </c>
       <c r="E154" t="n">
-        <v>0.0002638994975006208</v>
+        <v>0.0002678532795934006</v>
       </c>
       <c r="F154" t="n">
-        <v>0.003078507184161885</v>
+        <v>0.002845670362633652</v>
       </c>
       <c r="G154" t="n">
-        <v>0.0001938907109091946</v>
+        <v>0.0001840530097023865</v>
       </c>
       <c r="H154" t="n">
-        <v>0.1839272033293134</v>
+        <v>0.1970498745904272</v>
       </c>
       <c r="I154" t="n">
-        <v>0.001964980517232982</v>
+        <v>0.001676368001866691</v>
       </c>
     </row>
     <row r="155">
@@ -4917,28 +4917,28 @@
         <v>153</v>
       </c>
       <c r="B155" t="n">
-        <v>0.00137663903850317</v>
+        <v>0.001428612229973078</v>
       </c>
       <c r="C155" t="n">
-        <v>0.0001891193973533809</v>
+        <v>0.0001834681593766436</v>
       </c>
       <c r="D155" t="n">
-        <v>0.1857341040344238</v>
+        <v>0.1984022178907394</v>
       </c>
       <c r="E155" t="n">
-        <v>0.0002588491329951212</v>
+        <v>0.000253133005304262</v>
       </c>
       <c r="F155" t="n">
-        <v>0.00282613843896686</v>
+        <v>0.003140036498058168</v>
       </c>
       <c r="G155" t="n">
-        <v>0.0001906627838810918</v>
+        <v>0.0002074035159211536</v>
       </c>
       <c r="H155" t="n">
-        <v>0.1878966032457196</v>
+        <v>0.1923465993062124</v>
       </c>
       <c r="I155" t="n">
-        <v>0.001695992656159982</v>
+        <v>0.0019709000142434</v>
       </c>
     </row>
     <row r="156">
@@ -4946,28 +4946,28 @@
         <v>154</v>
       </c>
       <c r="B156" t="n">
-        <v>0.001361669377356768</v>
+        <v>0.001408127386853099</v>
       </c>
       <c r="C156" t="n">
-        <v>0.0001895711250221357</v>
+        <v>0.0001872189550679177</v>
       </c>
       <c r="D156" t="n">
-        <v>0.1842004565706253</v>
+        <v>0.1958076721982956</v>
       </c>
       <c r="E156" t="n">
-        <v>0.0002510959898605943</v>
+        <v>0.0002418700941391289</v>
       </c>
       <c r="F156" t="n">
-        <v>0.003029322786162475</v>
+        <v>0.002881656350631747</v>
       </c>
       <c r="G156" t="n">
-        <v>0.0001824445811605087</v>
+        <v>0.0001848730164039561</v>
       </c>
       <c r="H156" t="n">
-        <v>0.1842492529336624</v>
+        <v>0.1950564764568895</v>
       </c>
       <c r="I156" t="n">
-        <v>0.001925631994700597</v>
+        <v>0.001721500950397507</v>
       </c>
     </row>
     <row r="157">
@@ -4975,28 +4975,28 @@
         <v>155</v>
       </c>
       <c r="B157" t="n">
-        <v>0.001341747354455292</v>
+        <v>0.001392617625311017</v>
       </c>
       <c r="C157" t="n">
-        <v>0.0001894174769427627</v>
+        <v>0.0001866349565479904</v>
       </c>
       <c r="D157" t="n">
-        <v>0.1825534786376953</v>
+        <v>0.1935829254598617</v>
       </c>
       <c r="E157" t="n">
-        <v>0.0002395625047702342</v>
+        <v>0.0002380680676288903</v>
       </c>
       <c r="F157" t="n">
-        <v>0.002932241849166753</v>
+        <v>0.002877187576527794</v>
       </c>
       <c r="G157" t="n">
-        <v>0.0001854586741487461</v>
+        <v>0.0001875132988822353</v>
       </c>
       <c r="H157" t="n">
-        <v>0.1836050274866051</v>
+        <v>0.1920519498996983</v>
       </c>
       <c r="I157" t="n">
-        <v>0.001828758052715859</v>
+        <v>0.001729414598009022</v>
       </c>
     </row>
     <row r="158">
@@ -5004,28 +5004,28 @@
         <v>156</v>
       </c>
       <c r="B158" t="n">
-        <v>0.001323427399545908</v>
+        <v>0.001376119865991175</v>
       </c>
       <c r="C158" t="n">
-        <v>0.0001894759627999738</v>
+        <v>0.0001862582663409412</v>
       </c>
       <c r="D158" t="n">
-        <v>0.1810126514482498</v>
+        <v>0.1919647179479599</v>
       </c>
       <c r="E158" t="n">
-        <v>0.000228888216059655</v>
+        <v>0.0002300380125194788</v>
       </c>
       <c r="F158" t="n">
-        <v>0.003082095716561861</v>
+        <v>0.003079365777401755</v>
       </c>
       <c r="G158" t="n">
-        <v>0.0001835321242918016</v>
+        <v>0.0001756858497850071</v>
       </c>
       <c r="H158" t="n">
-        <v>0.1812821834248781</v>
+        <v>0.1956214530151003</v>
       </c>
       <c r="I158" t="n">
-        <v>0.001992152728501944</v>
+        <v>0.001925572637897015</v>
       </c>
     </row>
     <row r="159">
@@ -5033,28 +5033,28 @@
         <v>157</v>
       </c>
       <c r="B159" t="n">
-        <v>0.001310119575917721</v>
+        <v>0.001352062054142356</v>
       </c>
       <c r="C159" t="n">
-        <v>0.000188663774356246</v>
+        <v>0.0001857171495920047</v>
       </c>
       <c r="D159" t="n">
-        <v>0.1799942101621628</v>
+        <v>0.1903220994691849</v>
       </c>
       <c r="E159" t="n">
-        <v>0.0002214847716726363</v>
+        <v>0.0002147344312481582</v>
       </c>
       <c r="F159" t="n">
-        <v>0.002886383817857815</v>
+        <v>0.002868687244691259</v>
       </c>
       <c r="G159" t="n">
-        <v>0.0001911673697659694</v>
+        <v>0.000186298960533265</v>
       </c>
       <c r="H159" t="n">
-        <v>0.1810328692956227</v>
+        <v>0.1889682954442832</v>
       </c>
       <c r="I159" t="n">
-        <v>0.00179005209131692</v>
+        <v>0.001737546826314734</v>
       </c>
     </row>
     <row r="160">
@@ -5062,28 +5062,28 @@
         <v>158</v>
       </c>
       <c r="B160" t="n">
-        <v>0.001286874698549509</v>
+        <v>0.001338516561463475</v>
       </c>
       <c r="C160" t="n">
-        <v>0.0001890483352029696</v>
+        <v>0.0001855912526613101</v>
       </c>
       <c r="D160" t="n">
-        <v>0.1784821861686706</v>
+        <v>0.1883526851291656</v>
       </c>
       <c r="E160" t="n">
-        <v>0.0002054154580254108</v>
+        <v>0.0002111619071569294</v>
       </c>
       <c r="F160" t="n">
-        <v>0.002763946322788033</v>
+        <v>0.002829543068992858</v>
       </c>
       <c r="G160" t="n">
-        <v>0.0001879449224877771</v>
+        <v>0.0001915869749186114</v>
       </c>
       <c r="H160" t="n">
-        <v>0.180351836197139</v>
+        <v>0.1876607583290601</v>
       </c>
       <c r="I160" t="n">
-        <v>0.00167424221482845</v>
+        <v>0.00169965234737035</v>
       </c>
     </row>
     <row r="161">
@@ -5091,28 +5091,28 @@
         <v>159</v>
       </c>
       <c r="B161" t="n">
-        <v>0.001280738786771894</v>
+        <v>0.001320061274409294</v>
       </c>
       <c r="C161" t="n">
-        <v>0.0001892754880003631</v>
+        <v>0.0001869546360485256</v>
       </c>
       <c r="D161" t="n">
-        <v>0.1770894615316391</v>
+        <v>0.1864561812076569</v>
       </c>
       <c r="E161" t="n">
-        <v>0.0002060160122476518</v>
+        <v>0.0002008257537484169</v>
       </c>
       <c r="F161" t="n">
-        <v>0.00285143773220358</v>
+        <v>0.003041934381143401</v>
       </c>
       <c r="G161" t="n">
-        <v>0.0001905855279616012</v>
+        <v>0.0001971271055719024</v>
       </c>
       <c r="H161" t="n">
-        <v>0.1751175192392281</v>
+        <v>0.1831775430326166</v>
       </c>
       <c r="I161" t="n">
-        <v>0.001785264641827437</v>
+        <v>0.001928919601621833</v>
       </c>
     </row>
     <row r="162">
@@ -5120,28 +5120,28 @@
         <v>160</v>
       </c>
       <c r="B162" t="n">
-        <v>0.001267761787571013</v>
+        <v>0.001308518606342375</v>
       </c>
       <c r="C162" t="n">
-        <v>0.0001884643245032057</v>
+        <v>0.0001862980369599536</v>
       </c>
       <c r="D162" t="n">
-        <v>0.1755035364904404</v>
+        <v>0.185043981962204</v>
       </c>
       <c r="E162" t="n">
-        <v>0.000201779788793996</v>
+        <v>0.0001970006939340383</v>
       </c>
       <c r="F162" t="n">
-        <v>0.002896569613959841</v>
+        <v>0.002721264984482994</v>
       </c>
       <c r="G162" t="n">
-        <v>0.0001868398447933517</v>
+        <v>0.0001891242772833403</v>
       </c>
       <c r="H162" t="n">
-        <v>0.1756852951689607</v>
+        <v>0.1838445095632827</v>
       </c>
       <c r="I162" t="n">
-        <v>0.001831303316937246</v>
+        <v>0.001612918175601964</v>
       </c>
     </row>
     <row r="163">
@@ -5149,28 +5149,28 @@
         <v>161</v>
       </c>
       <c r="B163" t="n">
-        <v>0.001257213935866952</v>
+        <v>0.001289319466136396</v>
       </c>
       <c r="C163" t="n">
-        <v>0.0001887948228204623</v>
+        <v>0.0001871906206570566</v>
       </c>
       <c r="D163" t="n">
-        <v>0.1744323412008285</v>
+        <v>0.1835421571531296</v>
       </c>
       <c r="E163" t="n">
-        <v>0.0001962574287680909</v>
+        <v>0.0001844180832831189</v>
       </c>
       <c r="F163" t="n">
-        <v>0.002887716269649286</v>
+        <v>0.002921958009774689</v>
       </c>
       <c r="G163" t="n">
-        <v>0.0001944684019774885</v>
+        <v>0.0001940323768491624</v>
       </c>
       <c r="H163" t="n">
-        <v>0.1727147659362821</v>
+        <v>0.1808682026530557</v>
       </c>
       <c r="I163" t="n">
-        <v>0.001829674053727535</v>
+        <v>0.001823584654225647</v>
       </c>
     </row>
     <row r="164">
@@ -5178,28 +5178,28 @@
         <v>162</v>
       </c>
       <c r="B164" t="n">
-        <v>0.001244671656936407</v>
+        <v>0.001279426801927388</v>
       </c>
       <c r="C164" t="n">
-        <v>0.0001885696182250977</v>
+        <v>0.0001865466208672151</v>
       </c>
       <c r="D164" t="n">
-        <v>0.1734188770103454</v>
+        <v>0.1818256524343491</v>
       </c>
       <c r="E164" t="n">
-        <v>0.0001890076751150191</v>
+        <v>0.0001837519488157705</v>
       </c>
       <c r="F164" t="n">
-        <v>0.002779242081315443</v>
+        <v>0.002843602445693671</v>
       </c>
       <c r="G164" t="n">
-        <v>0.0001857944226113101</v>
+        <v>0.0001828712955993474</v>
       </c>
       <c r="H164" t="n">
-        <v>0.1741147428021734</v>
+        <v>0.1822601194366156</v>
       </c>
       <c r="I164" t="n">
-        <v>0.001722873940685579</v>
+        <v>0.001749430573507414</v>
       </c>
     </row>
     <row r="165">
@@ -5207,28 +5207,28 @@
         <v>163</v>
       </c>
       <c r="B165" t="n">
-        <v>0.001231637114703655</v>
+        <v>0.001262370618127286</v>
       </c>
       <c r="C165" t="n">
-        <v>0.0001882205495955423</v>
+        <v>0.0001870275173326954</v>
       </c>
       <c r="D165" t="n">
-        <v>0.172384810667038</v>
+        <v>0.1805595424938202</v>
       </c>
       <c r="E165" t="n">
-        <v>0.0001814925360353664</v>
+        <v>0.0001725454088104889</v>
       </c>
       <c r="F165" t="n">
-        <v>0.002861053068251585</v>
+        <v>0.002952005608314208</v>
       </c>
       <c r="G165" t="n">
-        <v>0.0001916499615443314</v>
+        <v>0.0001927823530431065</v>
       </c>
       <c r="H165" t="n">
-        <v>0.1710668075347219</v>
+        <v>0.1776750898876548</v>
       </c>
       <c r="I165" t="n">
-        <v>0.001814069084414444</v>
+        <v>0.001870847827098583</v>
       </c>
     </row>
     <row r="166">
@@ -5236,28 +5236,28 @@
         <v>164</v>
       </c>
       <c r="B166" t="n">
-        <v>0.001220502858288586</v>
+        <v>0.001251588410459459</v>
       </c>
       <c r="C166" t="n">
-        <v>0.0001884343076562509</v>
+        <v>0.0001867713160458952</v>
       </c>
       <c r="D166" t="n">
-        <v>0.1712438534069061</v>
+        <v>0.1791454628601074</v>
       </c>
       <c r="E166" t="n">
-        <v>0.0001758493015896529</v>
+        <v>0.0001690898051308468</v>
       </c>
       <c r="F166" t="n">
-        <v>0.002764038428737133</v>
+        <v>0.002712366283593204</v>
       </c>
       <c r="G166" t="n">
-        <v>0.0001894293058077542</v>
+        <v>0.000185416918508116</v>
       </c>
       <c r="H166" t="n">
-        <v>0.1705293444134477</v>
+        <v>0.1785683409288696</v>
       </c>
       <c r="I166" t="n">
-        <v>0.001721962397169097</v>
+        <v>0.00163410769359985</v>
       </c>
     </row>
     <row r="167">
@@ -5265,28 +5265,28 @@
         <v>165</v>
       </c>
       <c r="B167" t="n">
-        <v>0.00121214165583998</v>
+        <v>0.001237613188445568</v>
       </c>
       <c r="C167" t="n">
-        <v>0.0001883309300933033</v>
+        <v>0.0001872304430585355</v>
       </c>
       <c r="D167" t="n">
-        <v>0.1701745536832809</v>
+        <v>0.177755094865799</v>
       </c>
       <c r="E167" t="n">
-        <v>0.0001729379766527563</v>
+        <v>0.000161607290212065</v>
       </c>
       <c r="F167" t="n">
-        <v>0.002717285258558748</v>
+        <v>0.002732228930693175</v>
       </c>
       <c r="G167" t="n">
-        <v>0.0001859265484742298</v>
+        <v>0.0001860502290892298</v>
       </c>
       <c r="H167" t="n">
-        <v>0.1713015735567491</v>
+        <v>0.1777098384873902</v>
       </c>
       <c r="I167" t="n">
-        <v>0.001674850849354211</v>
+        <v>0.001657629527248819</v>
       </c>
     </row>
     <row r="168">
@@ -5294,28 +5294,28 @@
         <v>166</v>
       </c>
       <c r="B168" t="n">
-        <v>0.00120374443860352</v>
+        <v>0.001230167891055346</v>
       </c>
       <c r="C168" t="n">
-        <v>0.0001881949940482154</v>
+        <v>0.0001869594273185358</v>
       </c>
       <c r="D168" t="n">
-        <v>0.1692726508140564</v>
+        <v>0.1766409371652603</v>
       </c>
       <c r="E168" t="n">
-        <v>0.0001691862091608346</v>
+        <v>0.0001600038008708507</v>
       </c>
       <c r="F168" t="n">
-        <v>0.00278774954092979</v>
+        <v>0.002773106858745023</v>
       </c>
       <c r="G168" t="n">
-        <v>0.0001872116517547904</v>
+        <v>0.0001981651952665308</v>
       </c>
       <c r="H168" t="n">
-        <v>0.1687842486927599</v>
+        <v>0.1755091833951617</v>
       </c>
       <c r="I168" t="n">
-        <v>0.001756616656472496</v>
+        <v>0.001697395748396512</v>
       </c>
     </row>
     <row r="169">
@@ -5323,28 +5323,28 @@
         <v>167</v>
       </c>
       <c r="B169" t="n">
-        <v>0.001191939586900175</v>
+        <v>0.001221516292318702</v>
       </c>
       <c r="C169" t="n">
-        <v>0.0001883861956736073</v>
+        <v>0.0001862676919288933</v>
       </c>
       <c r="D169" t="n">
-        <v>0.1682708317222595</v>
+        <v>0.1756571407785416</v>
       </c>
       <c r="E169" t="n">
-        <v>0.0001621992368903011</v>
+        <v>0.0001569629233283922</v>
       </c>
       <c r="F169" t="n">
-        <v>0.002708704695470182</v>
+        <v>0.00274495071356244</v>
       </c>
       <c r="G169" t="n">
-        <v>0.0001859403560815461</v>
+        <v>0.0001912760873477857</v>
       </c>
       <c r="H169" t="n">
-        <v>0.1686110785190277</v>
+        <v>0.1741901046232143</v>
       </c>
       <c r="I169" t="n">
-        <v>0.001679708944522695</v>
+        <v>0.001682724086377849</v>
       </c>
     </row>
     <row r="170">
@@ -5352,28 +5352,28 @@
         <v>168</v>
       </c>
       <c r="B170" t="n">
-        <v>0.001185663446061313</v>
+        <v>0.001207905823819339</v>
       </c>
       <c r="C170" t="n">
-        <v>0.0001876875241147354</v>
+        <v>0.0001860499101635069</v>
       </c>
       <c r="D170" t="n">
-        <v>0.1676316466217041</v>
+        <v>0.1746037768678665</v>
       </c>
       <c r="E170" t="n">
-        <v>0.0001598176894951612</v>
+        <v>0.0001488370448667556</v>
       </c>
       <c r="F170" t="n">
-        <v>0.002740215118594626</v>
+        <v>0.002736614613230135</v>
       </c>
       <c r="G170" t="n">
-        <v>0.0001903764489929148</v>
+        <v>0.0001898579091146257</v>
       </c>
       <c r="H170" t="n">
-        <v>0.1666217360469295</v>
+        <v>0.1739950375640567</v>
       </c>
       <c r="I170" t="n">
-        <v>0.001716730003587014</v>
+        <v>0.001676781515767084</v>
       </c>
     </row>
     <row r="171">
@@ -5381,28 +5381,28 @@
         <v>169</v>
       </c>
       <c r="B171" t="n">
-        <v>0.001178385325983167</v>
+        <v>0.001198982189424336</v>
       </c>
       <c r="C171" t="n">
-        <v>0.0001890335186906159</v>
+        <v>0.0001870632116133347</v>
       </c>
       <c r="D171" t="n">
-        <v>0.1664196501197815</v>
+        <v>0.1734129156560898</v>
       </c>
       <c r="E171" t="n">
-        <v>0.0001572535854242742</v>
+        <v>0.0001448544315621257</v>
       </c>
       <c r="F171" t="n">
-        <v>0.002737525150751114</v>
+        <v>0.002731400047463849</v>
       </c>
       <c r="G171" t="n">
-        <v>0.0001868000206528809</v>
+        <v>0.0001886930371912692</v>
       </c>
       <c r="H171" t="n">
-        <v>0.1674761405105887</v>
+        <v>0.1725670960628189</v>
       </c>
       <c r="I171" t="n">
-        <v>0.001713344437825276</v>
+        <v>0.001679871535060857</v>
       </c>
     </row>
     <row r="172">
@@ -5410,28 +5410,28 @@
         <v>170</v>
       </c>
       <c r="B172" t="n">
-        <v>0.001167167995467782</v>
+        <v>0.001192497455567121</v>
       </c>
       <c r="C172" t="n">
-        <v>0.0001889013267317787</v>
+        <v>0.0001866905724350363</v>
       </c>
       <c r="D172" t="n">
-        <v>0.1654498818683624</v>
+        <v>0.1725080472774506</v>
       </c>
       <c r="E172" t="n">
-        <v>0.0001510172765199095</v>
+        <v>0.0001432666531316936</v>
       </c>
       <c r="F172" t="n">
-        <v>0.002752376603263432</v>
+        <v>0.002801984044044092</v>
       </c>
       <c r="G172" t="n">
-        <v>0.0001916429072895375</v>
+        <v>0.0001900194283146761</v>
       </c>
       <c r="H172" t="n">
-        <v>0.1650757168721997</v>
+        <v>0.1710599351571007</v>
       </c>
       <c r="I172" t="n">
-        <v>0.001735355184507688</v>
+        <v>0.001756664958712607</v>
       </c>
     </row>
     <row r="173">
@@ -5439,28 +5439,28 @@
         <v>171</v>
       </c>
       <c r="B173" t="n">
-        <v>0.001160822174623608</v>
+        <v>0.001182154015116394</v>
       </c>
       <c r="C173" t="n">
-        <v>0.0001885414319643751</v>
+        <v>0.0001870754977958277</v>
       </c>
       <c r="D173" t="n">
-        <v>0.1646867562446594</v>
+        <v>0.1713538118638992</v>
       </c>
       <c r="E173" t="n">
-        <v>0.0001488469794653356</v>
+        <v>0.0001383094831313938</v>
       </c>
       <c r="F173" t="n">
-        <v>0.002756341662908164</v>
+        <v>0.002784592585750593</v>
       </c>
       <c r="G173" t="n">
-        <v>0.0001879971437984211</v>
+        <v>0.000191191559681953</v>
       </c>
       <c r="H173" t="n">
-        <v>0.164396679685322</v>
+        <v>0.1701374215801622</v>
       </c>
       <c r="I173" t="n">
-        <v>0.001746361094829284</v>
+        <v>0.001742713985505831</v>
       </c>
     </row>
     <row r="174">
@@ -5468,28 +5468,28 @@
         <v>172</v>
       </c>
       <c r="B174" t="n">
-        <v>0.001153713349968195</v>
+        <v>0.001175409937314689</v>
       </c>
       <c r="C174" t="n">
-        <v>0.0001883924251133576</v>
+        <v>0.000186396223125048</v>
       </c>
       <c r="D174" t="n">
-        <v>0.1639023066720963</v>
+        <v>0.1707179239702225</v>
       </c>
       <c r="E174" t="n">
-        <v>0.0001458094184640795</v>
+        <v>0.0001354241182738915</v>
       </c>
       <c r="F174" t="n">
-        <v>0.002733764884291524</v>
+        <v>0.00264990010035952</v>
       </c>
       <c r="G174" t="n">
-        <v>0.0001907688275947757</v>
+        <v>0.0001860290538429603</v>
       </c>
       <c r="H174" t="n">
-        <v>0.162866057501726</v>
+        <v>0.1710185587571457</v>
       </c>
       <c r="I174" t="n">
-        <v>0.001728665812759923</v>
+        <v>0.001608778274615051</v>
       </c>
     </row>
     <row r="175">
@@ -5497,28 +5497,28 @@
         <v>173</v>
       </c>
       <c r="B175" t="n">
-        <v>0.001146169589847326</v>
+        <v>0.001167580272175372</v>
       </c>
       <c r="C175" t="n">
-        <v>0.0001883365764711052</v>
+        <v>0.0001867421332113445</v>
       </c>
       <c r="D175" t="n">
-        <v>0.1632982085151672</v>
+        <v>0.1698479326143265</v>
       </c>
       <c r="E175" t="n">
-        <v>0.0001413419985640794</v>
+        <v>0.0001315985059663653</v>
       </c>
       <c r="F175" t="n">
-        <v>0.002754019717465582</v>
+        <v>0.002694700574304841</v>
       </c>
       <c r="G175" t="n">
-        <v>0.0001903596078976229</v>
+        <v>0.0001884234183183818</v>
       </c>
       <c r="H175" t="n">
-        <v>0.1622267162731771</v>
+        <v>0.1690114618990977</v>
       </c>
       <c r="I175" t="n">
-        <v>0.001752526528751979</v>
+        <v>0.001661219872043545</v>
       </c>
     </row>
     <row r="176">
@@ -5526,28 +5526,28 @@
         <v>174</v>
       </c>
       <c r="B176" t="n">
-        <v>0.001138008123628795</v>
+        <v>0.001158673214778304</v>
       </c>
       <c r="C176" t="n">
-        <v>0.0001887636558534577</v>
+        <v>0.0001872512792311609</v>
       </c>
       <c r="D176" t="n">
-        <v>0.1623660344543457</v>
+        <v>0.1688378613452911</v>
       </c>
       <c r="E176" t="n">
-        <v>0.0001374143263399601</v>
+        <v>0.0001272326592057943</v>
       </c>
       <c r="F176" t="n">
-        <v>0.002706684906910771</v>
+        <v>0.002642665827315647</v>
       </c>
       <c r="G176" t="n">
-        <v>0.0001870836727803521</v>
+        <v>0.0001838380269775377</v>
       </c>
       <c r="H176" t="n">
-        <v>0.1627666197729344</v>
+        <v>0.1693869925935739</v>
       </c>
       <c r="I176" t="n">
-        <v>0.001705768163153388</v>
+        <v>0.001611892833430654</v>
       </c>
     </row>
     <row r="177">
@@ -5555,28 +5555,28 @@
         <v>175</v>
       </c>
       <c r="B177" t="n">
-        <v>0.001133281866632402</v>
+        <v>0.001155525302127004</v>
       </c>
       <c r="C177" t="n">
-        <v>0.0001886979701537639</v>
+        <v>0.0001868697123415768</v>
       </c>
       <c r="D177" t="n">
-        <v>0.1616077143793106</v>
+        <v>0.1682482149076462</v>
       </c>
       <c r="E177" t="n">
-        <v>0.000136545352563262</v>
+        <v>0.0001274145452547818</v>
       </c>
       <c r="F177" t="n">
-        <v>0.002666269319062083</v>
+        <v>0.002617926484894548</v>
       </c>
       <c r="G177" t="n">
-        <v>0.0001855945330835593</v>
+        <v>0.0001837854173059498</v>
       </c>
       <c r="H177" t="n">
-        <v>0.162632023131089</v>
+        <v>0.1685276083368656</v>
       </c>
       <c r="I177" t="n">
-        <v>0.001667514704008318</v>
+        <v>0.001591503031819232</v>
       </c>
     </row>
     <row r="178">
@@ -5584,28 +5584,28 @@
         <v>176</v>
       </c>
       <c r="B178" t="n">
-        <v>0.001130824242681265</v>
+        <v>0.00114742081374675</v>
       </c>
       <c r="C178" t="n">
-        <v>0.0001884183059707284</v>
+        <v>0.0001870725339492783</v>
       </c>
       <c r="D178" t="n">
-        <v>0.1612237686166763</v>
+        <v>0.1674710176858902</v>
       </c>
       <c r="E178" t="n">
-        <v>0.0001362870956771076</v>
+        <v>0.0001229932232769206</v>
       </c>
       <c r="F178" t="n">
-        <v>0.002726840841147873</v>
+        <v>0.002601274704229433</v>
       </c>
       <c r="G178" t="n">
-        <v>0.0001879671226940414</v>
+        <v>0.0001829701891732227</v>
       </c>
       <c r="H178" t="n">
-        <v>0.1608324853125443</v>
+        <v>0.1681382959847738</v>
       </c>
       <c r="I178" t="n">
-        <v>0.001734711308249532</v>
+        <v>0.00157761304321749</v>
       </c>
     </row>
     <row r="179">
@@ -5613,28 +5613,28 @@
         <v>177</v>
       </c>
       <c r="B179" t="n">
-        <v>0.001122585649855435</v>
+        <v>0.00114460074082762</v>
       </c>
       <c r="C179" t="n">
-        <v>0.0001880848966250196</v>
+        <v>0.0001868255294207483</v>
       </c>
       <c r="D179" t="n">
-        <v>0.1606131196527481</v>
+        <v>0.1668459907798767</v>
       </c>
       <c r="E179" t="n">
-        <v>0.0001314351742267609</v>
+        <v>0.000123545273758471</v>
       </c>
       <c r="F179" t="n">
-        <v>0.002670126123381186</v>
+        <v>0.002715536020878477</v>
       </c>
       <c r="G179" t="n">
-        <v>0.0001869441812801392</v>
+        <v>0.0001881936292377108</v>
       </c>
       <c r="H179" t="n">
-        <v>0.1608180941580559</v>
+        <v>0.1664736803777844</v>
       </c>
       <c r="I179" t="n">
-        <v>0.001679091444094688</v>
+        <v>0.001694974011383027</v>
       </c>
     </row>
     <row r="180">
@@ -5642,28 +5642,28 @@
         <v>178</v>
       </c>
       <c r="B180" t="n">
-        <v>0.00111829639454186</v>
+        <v>0.001136405915543437</v>
       </c>
       <c r="C180" t="n">
-        <v>0.0001883816136606038</v>
+        <v>0.0001874175110775977</v>
       </c>
       <c r="D180" t="n">
-        <v>0.1600236581783295</v>
+        <v>0.1661273351507187</v>
       </c>
       <c r="E180" t="n">
-        <v>0.0001297965039033443</v>
+        <v>0.0001183517492692918</v>
       </c>
       <c r="F180" t="n">
-        <v>0.002756305694045289</v>
+        <v>0.002608020471676358</v>
       </c>
       <c r="G180" t="n">
-        <v>0.000191368361863613</v>
+        <v>0.0001846161293117314</v>
       </c>
       <c r="H180" t="n">
-        <v>0.1590225120780908</v>
+        <v>0.1664465554026951</v>
       </c>
       <c r="I180" t="n">
-        <v>0.001769824791859173</v>
+        <v>0.00159117159646363</v>
       </c>
     </row>
     <row r="181">
@@ -5671,28 +5671,28 @@
         <v>179</v>
       </c>
       <c r="B181" t="n">
-        <v>0.001116434732675552</v>
+        <v>0.001133692457363009</v>
       </c>
       <c r="C181" t="n">
-        <v>0.0001880571871120483</v>
+        <v>0.0001875169008690864</v>
       </c>
       <c r="D181" t="n">
-        <v>0.1596184848136902</v>
+        <v>0.1654796146697998</v>
       </c>
       <c r="E181" t="n">
-        <v>0.0001302851486029103</v>
+        <v>0.0001187775153908878</v>
       </c>
       <c r="F181" t="n">
-        <v>0.002670686940873744</v>
+        <v>0.002598780376812349</v>
       </c>
       <c r="G181" t="n">
-        <v>0.0001877145817038811</v>
+        <v>0.0001853553238801497</v>
       </c>
       <c r="H181" t="n">
-        <v>0.1595745238598564</v>
+        <v>0.1658001949405981</v>
       </c>
       <c r="I181" t="n">
-        <v>0.001685099753727422</v>
+        <v>0.001584424115178064</v>
       </c>
     </row>
     <row r="182">
@@ -5700,28 +5700,28 @@
         <v>180</v>
       </c>
       <c r="B182" t="n">
-        <v>0.001112097905151546</v>
+        <v>0.001128528032027185</v>
       </c>
       <c r="C182" t="n">
-        <v>0.0001884291720474139</v>
+        <v>0.0001868818369889632</v>
       </c>
       <c r="D182" t="n">
-        <v>0.1591152774887085</v>
+        <v>0.1651204657554627</v>
       </c>
       <c r="E182" t="n">
-        <v>0.0001280923774810508</v>
+        <v>0.0001160438910378143</v>
       </c>
       <c r="F182" t="n">
-        <v>0.002732175905014378</v>
+        <v>0.002647237518063912</v>
       </c>
       <c r="G182" t="n">
-        <v>0.0001901577008258761</v>
+        <v>0.0001861125757487804</v>
       </c>
       <c r="H182" t="n">
-        <v>0.15826529621689</v>
+        <v>0.1651738227920859</v>
       </c>
       <c r="I182" t="n">
-        <v>0.001750691759978918</v>
+        <v>0.001635255909230116</v>
       </c>
     </row>
     <row r="183">
@@ -5729,28 +5729,28 @@
         <v>181</v>
       </c>
       <c r="B183" t="n">
-        <v>0.001108193236112595</v>
+        <v>0.001126030018240213</v>
       </c>
       <c r="C183" t="n">
-        <v>0.0001886836315728724</v>
+        <v>0.0001868006208091974</v>
       </c>
       <c r="D183" t="n">
-        <v>0.1585843959379196</v>
+        <v>0.1647077594022751</v>
       </c>
       <c r="E183" t="n">
-        <v>0.0001265876361811534</v>
+        <v>0.0001156906254785135</v>
       </c>
       <c r="F183" t="n">
-        <v>0.002735810653134864</v>
+        <v>0.002616166636761017</v>
       </c>
       <c r="G183" t="n">
-        <v>0.0001889618452855646</v>
+        <v>0.000185805509446324</v>
       </c>
       <c r="H183" t="n">
-        <v>0.1582811878293412</v>
+        <v>0.1646850161655498</v>
       </c>
       <c r="I183" t="n">
-        <v>0.001755442899738425</v>
+        <v>0.001606936062835035</v>
       </c>
     </row>
     <row r="184">
@@ -5758,28 +5758,28 @@
         <v>182</v>
       </c>
       <c r="B184" t="n">
-        <v>0.001107023480974138</v>
+        <v>0.001121587539382279</v>
       </c>
       <c r="C184" t="n">
-        <v>0.0001881272972133011</v>
+        <v>0.0001872167269950732</v>
       </c>
       <c r="D184" t="n">
-        <v>0.1584062900676727</v>
+        <v>0.1641879819259643</v>
       </c>
       <c r="E184" t="n">
-        <v>0.0001268647563168779</v>
+        <v>0.0001134309228095226</v>
       </c>
       <c r="F184" t="n">
-        <v>0.00267954660154162</v>
+        <v>0.002617067173943774</v>
       </c>
       <c r="G184" t="n">
-        <v>0.0001886426521898938</v>
+        <v>0.0001867576027609982</v>
       </c>
       <c r="H184" t="n">
-        <v>0.1581040998491144</v>
+        <v>0.1641247819483183</v>
       </c>
       <c r="I184" t="n">
-        <v>0.00170038344615806</v>
+        <v>0.001609685696277093</v>
       </c>
     </row>
     <row r="185">
@@ -5787,28 +5787,28 @@
         <v>183</v>
       </c>
       <c r="B185" t="n">
-        <v>0.001102084036156535</v>
+        <v>0.001120394416488707</v>
       </c>
       <c r="C185" t="n">
-        <v>0.0001885839346712455</v>
+        <v>0.0001871881567984819</v>
       </c>
       <c r="D185" t="n">
-        <v>0.1579727679786682</v>
+        <v>0.1637955913143158</v>
       </c>
       <c r="E185" t="n">
-        <v>0.0001236362991286442</v>
+        <v>0.0001142283129869029</v>
       </c>
       <c r="F185" t="n">
-        <v>0.002709625418834254</v>
+        <v>0.002677659642097174</v>
       </c>
       <c r="G185" t="n">
-        <v>0.0001892299175210796</v>
+        <v>0.0001873561805269877</v>
       </c>
       <c r="H185" t="n">
-        <v>0.1576384224899441</v>
+        <v>0.1635904921968065</v>
       </c>
       <c r="I185" t="n">
-        <v>0.001732203451495733</v>
+        <v>0.001672351049118011</v>
       </c>
     </row>
     <row r="186">
@@ -5816,28 +5816,28 @@
         <v>184</v>
       </c>
       <c r="B186" t="n">
-        <v>0.00109984846021235</v>
+        <v>0.001116291334584355</v>
       </c>
       <c r="C186" t="n">
-        <v>0.0001882871002629399</v>
+        <v>0.0001873712192168459</v>
       </c>
       <c r="D186" t="n">
-        <v>0.157724378364563</v>
+        <v>0.1634421269369125</v>
       </c>
       <c r="E186" t="n">
-        <v>0.0001229394934987649</v>
+        <v>0.0001117095080660656</v>
       </c>
       <c r="F186" t="n">
-        <v>0.002708286692860854</v>
+        <v>0.002627907028014591</v>
       </c>
       <c r="G186" t="n">
-        <v>0.0001882924519017412</v>
+        <v>0.0001882413311954132</v>
       </c>
       <c r="H186" t="n">
-        <v>0.1577140789251732</v>
+        <v>0.1631819725493623</v>
       </c>
       <c r="I186" t="n">
-        <v>0.001731423866011348</v>
+        <v>0.001623755862896876</v>
       </c>
     </row>
     <row r="187">
@@ -5845,28 +5845,28 @@
         <v>185</v>
       </c>
       <c r="B187" t="n">
-        <v>0.001097224173642695</v>
+        <v>0.001113449941292405</v>
       </c>
       <c r="C187" t="n">
-        <v>0.0001885825527058914</v>
+        <v>0.0001871870726663619</v>
       </c>
       <c r="D187" t="n">
-        <v>0.1573839439210892</v>
+        <v>0.1631687992963791</v>
       </c>
       <c r="E187" t="n">
-        <v>0.0001217219150038436</v>
+        <v>0.0001104188916040584</v>
       </c>
       <c r="F187" t="n">
-        <v>0.002693028784027326</v>
+        <v>0.002615538281806384</v>
       </c>
       <c r="G187" t="n">
-        <v>0.0001879050467798766</v>
+        <v>0.000185220179559745</v>
       </c>
       <c r="H187" t="n">
-        <v>0.1574288318917569</v>
+        <v>0.1634260741765892</v>
       </c>
       <c r="I187" t="n">
-        <v>0.001717979594856975</v>
+        <v>0.001613187801516744</v>
       </c>
     </row>
     <row r="188">
@@ -5874,28 +5874,28 @@
         <v>186</v>
       </c>
       <c r="B188" t="n">
-        <v>0.001094552015706897</v>
+        <v>0.001112061766982078</v>
       </c>
       <c r="C188" t="n">
-        <v>0.0001882058090874925</v>
+        <v>0.000187062602121383</v>
       </c>
       <c r="D188" t="n">
-        <v>0.157266368727684</v>
+        <v>0.1628834072780609</v>
       </c>
       <c r="E188" t="n">
-        <v>0.0001200143796512857</v>
+        <v>0.0001105821693078615</v>
       </c>
       <c r="F188" t="n">
-        <v>0.002716400774293025</v>
+        <v>0.002629740865259974</v>
       </c>
       <c r="G188" t="n">
-        <v>0.0001903745189883031</v>
+        <v>0.0001861540578067573</v>
       </c>
       <c r="H188" t="n">
-        <v>0.1565082079619412</v>
+        <v>0.1629514935685604</v>
       </c>
       <c r="I188" t="n">
-        <v>0.001743485213463995</v>
+        <v>0.001628829367796102</v>
       </c>
     </row>
     <row r="189">
@@ -5903,28 +5903,28 @@
         <v>187</v>
       </c>
       <c r="B189" t="n">
-        <v>0.001094278132177889</v>
+        <v>0.001110552376516163</v>
       </c>
       <c r="C189" t="n">
-        <v>0.0001884865683699027</v>
+        <v>0.0001871150009492412</v>
       </c>
       <c r="D189" t="n">
-        <v>0.1569633809604645</v>
+        <v>0.1626527071962356</v>
       </c>
       <c r="E189" t="n">
-        <v>0.0001209746584352106</v>
+        <v>0.0001101738390196115</v>
       </c>
       <c r="F189" t="n">
-        <v>0.002701795745206477</v>
+        <v>0.00262215593203805</v>
       </c>
       <c r="G189" t="n">
-        <v>0.0001873076077105119</v>
+        <v>0.000186768958427097</v>
       </c>
       <c r="H189" t="n">
-        <v>0.1572445534716617</v>
+        <v>0.1626268242379775</v>
       </c>
       <c r="I189" t="n">
-        <v>0.001728265415018707</v>
+        <v>0.001622252904006309</v>
       </c>
     </row>
     <row r="190">
@@ -5932,28 +5932,28 @@
         <v>188</v>
       </c>
       <c r="B190" t="n">
-        <v>0.001092350556440651</v>
+        <v>0.001108648489870131</v>
       </c>
       <c r="C190" t="n">
-        <v>0.0001877827186333015</v>
+        <v>0.0001873714032322168</v>
       </c>
       <c r="D190" t="n">
-        <v>0.1570047031011581</v>
+        <v>0.162416881319046</v>
       </c>
       <c r="E190" t="n">
-        <v>0.0001195443334924057</v>
+        <v>0.0001091926982095465</v>
       </c>
       <c r="F190" t="n">
-        <v>0.002683380935857677</v>
+        <v>0.002626533251389448</v>
       </c>
       <c r="G190" t="n">
-        <v>0.0001881504005757821</v>
+        <v>0.0001865237538013789</v>
       </c>
       <c r="H190" t="n">
-        <v>0.1567356547513949</v>
+        <v>0.1624463699672973</v>
       </c>
       <c r="I190" t="n">
-        <v>0.001711552251482817</v>
+        <v>0.001627777690329205</v>
       </c>
     </row>
     <row r="191">
@@ -5961,28 +5961,28 @@
         <v>189</v>
       </c>
       <c r="B191" t="n">
-        <v>0.001090240418329835</v>
+        <v>0.001106616075754166</v>
       </c>
       <c r="C191" t="n">
-        <v>0.0001880890536634251</v>
+        <v>0.0001871179311936721</v>
       </c>
       <c r="D191" t="n">
-        <v>0.1567613756484985</v>
+        <v>0.1622652247753143</v>
       </c>
       <c r="E191" t="n">
-        <v>0.000118344511216972</v>
+        <v>0.0001081720383181237</v>
       </c>
       <c r="F191" t="n">
-        <v>0.002687896017082412</v>
+        <v>0.002651799384407322</v>
       </c>
       <c r="G191" t="n">
-        <v>0.0001876000942055403</v>
+        <v>0.0001884089688647791</v>
       </c>
       <c r="H191" t="n">
-        <v>0.1568214298072491</v>
+        <v>0.1618823057850656</v>
       </c>
       <c r="I191" t="n">
-        <v>0.001716188755992429</v>
+        <v>0.001653978945611449</v>
       </c>
     </row>
     <row r="192">
@@ -5990,28 +5990,28 @@
         <v>190</v>
       </c>
       <c r="B192" t="n">
-        <v>0.001089856919966638</v>
+        <v>0.001105697324827313</v>
       </c>
       <c r="C192" t="n">
-        <v>0.0001877051599770784</v>
+        <v>0.0001873175744600594</v>
       </c>
       <c r="D192" t="n">
-        <v>0.1567498516807556</v>
+        <v>0.1620602808923721</v>
       </c>
       <c r="E192" t="n">
-        <v>0.0001184025217052549</v>
+        <v>0.0001080783642940223</v>
       </c>
       <c r="F192" t="n">
-        <v>0.002694010167180592</v>
+        <v>0.002626587966241271</v>
       </c>
       <c r="G192" t="n">
-        <v>0.0001879785392569381</v>
+        <v>0.000186467287194274</v>
       </c>
       <c r="H192" t="n">
-        <v>0.1566390959094438</v>
+        <v>0.1622007138596857</v>
       </c>
       <c r="I192" t="n">
-        <v>0.001722836140436872</v>
+        <v>0.001629117140645195</v>
       </c>
     </row>
     <row r="193">
@@ -6019,28 +6019,28 @@
         <v>191</v>
       </c>
       <c r="B193" t="n">
-        <v>0.001088448993861675</v>
+        <v>0.001106335166364908</v>
       </c>
       <c r="C193" t="n">
-        <v>0.0001881726908348501</v>
+        <v>0.0001870411896733567</v>
       </c>
       <c r="D193" t="n">
-        <v>0.1565226121845245</v>
+        <v>0.1620450385112762</v>
       </c>
       <c r="E193" t="n">
-        <v>0.000117663253470324</v>
+        <v>0.0001090687999753281</v>
       </c>
       <c r="F193" t="n">
-        <v>0.002681022317104686</v>
+        <v>0.002609045145088172</v>
       </c>
       <c r="G193" t="n">
-        <v>0.0001874777029918318</v>
+        <v>0.0001864269706939057</v>
       </c>
       <c r="H193" t="n">
-        <v>0.1566368926718807</v>
+        <v>0.1620739039521038</v>
       </c>
       <c r="I193" t="n">
-        <v>0.001710360195278076</v>
+        <v>0.001612248658119028</v>
       </c>
     </row>
     <row r="194">
@@ -6048,28 +6048,28 @@
         <v>192</v>
       </c>
       <c r="B194" t="n">
-        <v>0.00108812488874793</v>
+        <v>0.001104231614798307</v>
       </c>
       <c r="C194" t="n">
-        <v>0.0001880952524803579</v>
+        <v>0.000187280292218551</v>
       </c>
       <c r="D194" t="n">
-        <v>0.1564487626371384</v>
+        <v>0.1618887696304321</v>
       </c>
       <c r="E194" t="n">
-        <v>0.0001177858421048149</v>
+        <v>0.0001075074874702841</v>
       </c>
       <c r="F194" t="n">
-        <v>0.002687904003515329</v>
+        <v>0.002625963094493839</v>
       </c>
       <c r="G194" t="n">
-        <v>0.000188392468370713</v>
+        <v>0.0001869350841016696</v>
       </c>
       <c r="H194" t="n">
-        <v>0.156322602741481</v>
+        <v>0.161876005889152</v>
       </c>
       <c r="I194" t="n">
-        <v>0.001717898521380921</v>
+        <v>0.001629647982008998</v>
       </c>
     </row>
     <row r="195">
@@ -6077,28 +6077,28 @@
         <v>193</v>
       </c>
       <c r="B195" t="n">
-        <v>0.001088542557686567</v>
+        <v>0.001102952523171902</v>
       </c>
       <c r="C195" t="n">
-        <v>0.000188066529753618</v>
+        <v>0.0001871315787956119</v>
       </c>
       <c r="D195" t="n">
-        <v>0.156388773358345</v>
+        <v>0.1618355844106674</v>
       </c>
       <c r="E195" t="n">
-        <v>0.0001185321891261265</v>
+        <v>0.00010664303625701</v>
       </c>
       <c r="F195" t="n">
-        <v>0.002674902958254562</v>
+        <v>0.002644595548504474</v>
       </c>
       <c r="G195" t="n">
-        <v>0.0001880342958378795</v>
+        <v>0.0001875081785204767</v>
       </c>
       <c r="H195" t="n">
-        <v>0.1563840289168412</v>
+        <v>0.1616954079236331</v>
       </c>
       <c r="I195" t="n">
-        <v>0.001704948579400267</v>
+        <v>0.001648610340663783</v>
       </c>
     </row>
     <row r="196">
@@ -6106,28 +6106,28 @@
         <v>194</v>
       </c>
       <c r="B196" t="n">
-        <v>0.001087303304165602</v>
+        <v>0.001103126344121993</v>
       </c>
       <c r="C196" t="n">
-        <v>0.0001878946244018152</v>
+        <v>0.0001874031330766156</v>
       </c>
       <c r="D196" t="n">
-        <v>0.1563949583978653</v>
+        <v>0.1617064696369171</v>
       </c>
       <c r="E196" t="n">
-        <v>0.0001174338886542246</v>
+        <v>0.000107190884443</v>
       </c>
       <c r="F196" t="n">
-        <v>0.00267702259630767</v>
+        <v>0.002634714912732556</v>
       </c>
       <c r="G196" t="n">
-        <v>0.0001878689989416448</v>
+        <v>0.0001869628313090576</v>
       </c>
       <c r="H196" t="n">
-        <v>0.1563568364815455</v>
+        <v>0.1617488209273648</v>
       </c>
       <c r="I196" t="n">
-        <v>0.001707369439869049</v>
+        <v>0.001639008009289718</v>
       </c>
     </row>
     <row r="197">
@@ -6135,28 +6135,28 @@
         <v>195</v>
       </c>
       <c r="B197" t="n">
-        <v>0.001085650643266737</v>
+        <v>0.001102638271704316</v>
       </c>
       <c r="C197" t="n">
-        <v>0.0001877686311760917</v>
+        <v>0.0001871263982048258</v>
       </c>
       <c r="D197" t="n">
-        <v>0.1563677001419067</v>
+        <v>0.1617322265005112</v>
       </c>
       <c r="E197" t="n">
-        <v>0.0001160435290043242</v>
+        <v>0.0001068507557697594</v>
       </c>
       <c r="F197" t="n">
-        <v>0.002682937977631952</v>
+        <v>0.002640520914398486</v>
       </c>
       <c r="G197" t="n">
-        <v>0.0001880045118656231</v>
+        <v>0.0001874874112462901</v>
       </c>
       <c r="H197" t="n">
-        <v>0.156294277365795</v>
+        <v>0.1616093078882815</v>
       </c>
       <c r="I197" t="n">
-        <v>0.001713462103892051</v>
+        <v>0.001644987012639484</v>
       </c>
     </row>
     <row r="198">
@@ -6164,28 +6164,28 @@
         <v>196</v>
       </c>
       <c r="B198" t="n">
-        <v>0.001085953609324992</v>
+        <v>0.001102794274143875</v>
       </c>
       <c r="C198" t="n">
-        <v>0.0001879696452012286</v>
+        <v>0.0001874114848347381</v>
       </c>
       <c r="D198" t="n">
-        <v>0.1562929866399765</v>
+        <v>0.1616354058675766</v>
       </c>
       <c r="E198" t="n">
-        <v>0.0001165190574023873</v>
+        <v>0.0001072057829243131</v>
       </c>
       <c r="F198" t="n">
-        <v>0.002680901978134525</v>
+        <v>0.002634045669222539</v>
       </c>
       <c r="G198" t="n">
-        <v>0.0001877818047429844</v>
+        <v>0.0001871937889735659</v>
       </c>
       <c r="H198" t="n">
-        <v>0.1563224897678291</v>
+        <v>0.1616379223960842</v>
       </c>
       <c r="I198" t="n">
-        <v>0.001711507761390609</v>
+        <v>0.00163866231393458</v>
       </c>
     </row>
     <row r="199">
@@ -6193,28 +6193,28 @@
         <v>197</v>
       </c>
       <c r="B199" t="n">
-        <v>0.001085437921918929</v>
+        <v>0.001101369481898844</v>
       </c>
       <c r="C199" t="n">
-        <v>0.0001878995884843171</v>
+        <v>0.0001872365738051012</v>
       </c>
       <c r="D199" t="n">
-        <v>0.1563110670509338</v>
+        <v>0.1616689061555862</v>
       </c>
       <c r="E199" t="n">
-        <v>0.0001159830088736489</v>
+        <v>0.0001057884103944525</v>
       </c>
       <c r="F199" t="n">
-        <v>0.002687771049211163</v>
+        <v>0.00263744638316625</v>
       </c>
       <c r="G199" t="n">
-        <v>0.0001879064610304286</v>
+        <v>0.0001872317219708726</v>
       </c>
       <c r="H199" t="n">
-        <v>0.156254747828885</v>
+        <v>0.1616339831270557</v>
       </c>
       <c r="I199" t="n">
-        <v>0.001718590889584887</v>
+        <v>0.001642044736323103</v>
       </c>
     </row>
     <row r="200">
@@ -6222,28 +6222,28 @@
         <v>198</v>
       </c>
       <c r="B200" t="n">
-        <v>0.001085072541289031</v>
+        <v>0.001102675716541707</v>
       </c>
       <c r="C200" t="n">
-        <v>0.0001880539821907878</v>
+        <v>0.0001872463219510391</v>
       </c>
       <c r="D200" t="n">
-        <v>0.1562600316610336</v>
+        <v>0.16165421596241</v>
       </c>
       <c r="E200" t="n">
-        <v>0.0001157184136621654</v>
+        <v>0.0001071583339050412</v>
       </c>
       <c r="F200" t="n">
-        <v>0.002681889022270531</v>
+        <v>0.002633762962654306</v>
       </c>
       <c r="G200" t="n">
-        <v>0.0001879730840340078</v>
+        <v>0.0001871177520953137</v>
       </c>
       <c r="H200" t="n">
-        <v>0.156249371500622</v>
+        <v>0.1616554039522252</v>
       </c>
       <c r="I200" t="n">
-        <v>0.001712669082658994</v>
+        <v>0.001638368195489499</v>
       </c>
     </row>
     <row r="201">
@@ -6251,28 +6251,28 @@
         <v>199</v>
       </c>
       <c r="B201" t="n">
-        <v>0.00108630856603384</v>
+        <v>0.001101806347079575</v>
       </c>
       <c r="C201" t="n">
-        <v>0.000187984403966926</v>
+        <v>0.0001871530648488551</v>
       </c>
       <c r="D201" t="n">
-        <v>0.1562547646284103</v>
+        <v>0.1616642798175812</v>
       </c>
       <c r="E201" t="n">
-        <v>0.0001170503449449316</v>
+        <v>0.0001063318906533532</v>
       </c>
       <c r="F201" t="n">
-        <v>0.002689147912008387</v>
+        <v>0.00263766508900407</v>
       </c>
       <c r="G201" t="n">
-        <v>0.0001879767280785659</v>
+        <v>0.0001871264273669954</v>
       </c>
       <c r="H201" t="n">
-        <v>0.1562486033834408</v>
+        <v>0.1616509508600437</v>
       </c>
       <c r="I201" t="n">
-        <v>0.001719928196605544</v>
+        <v>0.001642283892310657</v>
       </c>
     </row>
   </sheetData>
